--- a/光伏配储项目/电价数据/2026/桑浦站.xlsx
+++ b/光伏配储项目/电价数据/2026/桑浦站.xlsx
@@ -16,10 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="yyyy/mm/dd"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -64,7 +63,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -430,13 +429,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CS116"/>
+  <dimension ref="A1:CS143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>日期</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -34613,6 +34612,7917 @@
       </c>
       <c r="CS116" t="n">
         <v>0.33817</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
+        <v>46138</v>
+      </c>
+      <c r="B117" t="n">
+        <v>0.38456</v>
+      </c>
+      <c r="C117" t="n">
+        <v>0.7367</v>
+      </c>
+      <c r="D117" t="n">
+        <v>0.35474</v>
+      </c>
+      <c r="E117" t="n">
+        <v>0.37471</v>
+      </c>
+      <c r="F117" t="n">
+        <v>0.34539</v>
+      </c>
+      <c r="G117" t="n">
+        <v>0.38409</v>
+      </c>
+      <c r="H117" t="n">
+        <v>0.3317</v>
+      </c>
+      <c r="I117" t="n">
+        <v>0.33295</v>
+      </c>
+      <c r="J117" t="n">
+        <v>0.33222</v>
+      </c>
+      <c r="K117" t="n">
+        <v>0.32167</v>
+      </c>
+      <c r="L117" t="n">
+        <v>0.32714</v>
+      </c>
+      <c r="M117" t="n">
+        <v>0.32076</v>
+      </c>
+      <c r="N117" t="n">
+        <v>0.32583</v>
+      </c>
+      <c r="O117" t="n">
+        <v>0.32147</v>
+      </c>
+      <c r="P117" t="n">
+        <v>0.3186</v>
+      </c>
+      <c r="Q117" t="n">
+        <v>0.31842</v>
+      </c>
+      <c r="R117" t="n">
+        <v>0.31455</v>
+      </c>
+      <c r="S117" t="n">
+        <v>0.31934</v>
+      </c>
+      <c r="T117" t="n">
+        <v>0.31681</v>
+      </c>
+      <c r="U117" t="n">
+        <v>0.318</v>
+      </c>
+      <c r="V117" t="n">
+        <v>0.3179</v>
+      </c>
+      <c r="W117" t="n">
+        <v>0.32949</v>
+      </c>
+      <c r="X117" t="n">
+        <v>0.32085</v>
+      </c>
+      <c r="Y117" t="n">
+        <v>0.33044</v>
+      </c>
+      <c r="Z117" t="n">
+        <v>0.32869</v>
+      </c>
+      <c r="AA117" t="n">
+        <v>0.33316</v>
+      </c>
+      <c r="AB117" t="n">
+        <v>0.33277</v>
+      </c>
+      <c r="AC117" t="n">
+        <v>0.33283</v>
+      </c>
+      <c r="AD117" t="n">
+        <v>0.31794</v>
+      </c>
+      <c r="AE117" t="n">
+        <v>0.30002</v>
+      </c>
+      <c r="AF117" t="n">
+        <v>0.31612</v>
+      </c>
+      <c r="AG117" t="n">
+        <v>0.30851</v>
+      </c>
+      <c r="AH117" t="n">
+        <v>0.33019</v>
+      </c>
+      <c r="AI117" t="n">
+        <v>0.32576</v>
+      </c>
+      <c r="AJ117" t="n">
+        <v>0.3167</v>
+      </c>
+      <c r="AK117" t="n">
+        <v>0.32964</v>
+      </c>
+      <c r="AL117" t="n">
+        <v>0.32279</v>
+      </c>
+      <c r="AM117" t="n">
+        <v>0.32227</v>
+      </c>
+      <c r="AN117" t="n">
+        <v>0.28151</v>
+      </c>
+      <c r="AO117" t="n">
+        <v>0.31972</v>
+      </c>
+      <c r="AP117" t="n">
+        <v>0.27264</v>
+      </c>
+      <c r="AQ117" t="n">
+        <v>0.31173</v>
+      </c>
+      <c r="AR117" t="n">
+        <v>0.29732</v>
+      </c>
+      <c r="AS117" t="n">
+        <v>0.2945</v>
+      </c>
+      <c r="AT117" t="n">
+        <v>0.33532</v>
+      </c>
+      <c r="AU117" t="n">
+        <v>0.34784</v>
+      </c>
+      <c r="AV117" t="n">
+        <v>0.35065</v>
+      </c>
+      <c r="AW117" t="n">
+        <v>0.3118</v>
+      </c>
+      <c r="AX117" t="n">
+        <v>0.07476999999999999</v>
+      </c>
+      <c r="AY117" t="n">
+        <v>0.65218</v>
+      </c>
+      <c r="AZ117" t="n">
+        <v>0.47666</v>
+      </c>
+      <c r="BA117" t="n">
+        <v>0.17251</v>
+      </c>
+      <c r="BB117" t="n">
+        <v>0.26812</v>
+      </c>
+      <c r="BC117" t="n">
+        <v>0.25379</v>
+      </c>
+      <c r="BD117" t="n">
+        <v>0.25839</v>
+      </c>
+      <c r="BE117" t="n">
+        <v>0.24308</v>
+      </c>
+      <c r="BF117" t="n">
+        <v>0.55401</v>
+      </c>
+      <c r="BG117" t="n">
+        <v>0.32844</v>
+      </c>
+      <c r="BH117" t="n">
+        <v>0.42563</v>
+      </c>
+      <c r="BI117" t="n">
+        <v>0.30531</v>
+      </c>
+      <c r="BJ117" t="n">
+        <v>0.32839</v>
+      </c>
+      <c r="BK117" t="n">
+        <v>0.34035</v>
+      </c>
+      <c r="BL117" t="n">
+        <v>0.30089</v>
+      </c>
+      <c r="BM117" t="n">
+        <v>0.31183</v>
+      </c>
+      <c r="BN117" t="n">
+        <v>0.33828</v>
+      </c>
+      <c r="BO117" t="n">
+        <v>0.33611</v>
+      </c>
+      <c r="BP117" t="n">
+        <v>0.57124</v>
+      </c>
+      <c r="BQ117" t="n">
+        <v>0.56264</v>
+      </c>
+      <c r="BR117" t="n">
+        <v>0.7085900000000001</v>
+      </c>
+      <c r="BS117" t="n">
+        <v>1.0835</v>
+      </c>
+      <c r="BT117" t="n">
+        <v>0.38388</v>
+      </c>
+      <c r="BU117" t="n">
+        <v>1.75496</v>
+      </c>
+      <c r="BV117" t="n">
+        <v>0.41659</v>
+      </c>
+      <c r="BW117" t="n">
+        <v>0.41967</v>
+      </c>
+      <c r="BX117" t="n">
+        <v>0.62936</v>
+      </c>
+      <c r="BY117" t="n">
+        <v>0.8212200000000001</v>
+      </c>
+      <c r="BZ117" t="n">
+        <v>0.51395</v>
+      </c>
+      <c r="CA117" t="n">
+        <v>1.1738</v>
+      </c>
+      <c r="CB117" t="n">
+        <v>1.38369</v>
+      </c>
+      <c r="CC117" t="n">
+        <v>1.01882</v>
+      </c>
+      <c r="CD117" t="n">
+        <v>0.99394</v>
+      </c>
+      <c r="CE117" t="n">
+        <v>1.20769</v>
+      </c>
+      <c r="CF117" t="n">
+        <v>1.27365</v>
+      </c>
+      <c r="CG117" t="n">
+        <v>0.4445</v>
+      </c>
+      <c r="CH117" t="n">
+        <v>0.66747</v>
+      </c>
+      <c r="CI117" t="n">
+        <v>0.71414</v>
+      </c>
+      <c r="CJ117" t="n">
+        <v>1.2967</v>
+      </c>
+      <c r="CK117" t="n">
+        <v>0.74414</v>
+      </c>
+      <c r="CL117" t="n">
+        <v>0.80163</v>
+      </c>
+      <c r="CM117" t="n">
+        <v>0.72463</v>
+      </c>
+      <c r="CN117" t="n">
+        <v>0.68635</v>
+      </c>
+      <c r="CO117" t="n">
+        <v>0.47583</v>
+      </c>
+      <c r="CP117" t="n">
+        <v>0.44777</v>
+      </c>
+      <c r="CQ117" t="n">
+        <v>0.4389</v>
+      </c>
+      <c r="CR117" t="n">
+        <v>0.39404</v>
+      </c>
+      <c r="CS117" t="n">
+        <v>0.40247</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
+        <v>46139</v>
+      </c>
+      <c r="B118" t="n">
+        <v>0.32887</v>
+      </c>
+      <c r="C118" t="n">
+        <v>0.69467</v>
+      </c>
+      <c r="D118" t="n">
+        <v>1.61172</v>
+      </c>
+      <c r="E118" t="n">
+        <v>0.84549</v>
+      </c>
+      <c r="F118" t="n">
+        <v>1.67552</v>
+      </c>
+      <c r="G118" t="n">
+        <v>0.86693</v>
+      </c>
+      <c r="H118" t="n">
+        <v>0.50152</v>
+      </c>
+      <c r="I118" t="n">
+        <v>0.51558</v>
+      </c>
+      <c r="J118" t="n">
+        <v>0.50806</v>
+      </c>
+      <c r="K118" t="n">
+        <v>0.5087699999999999</v>
+      </c>
+      <c r="L118" t="n">
+        <v>0.49198</v>
+      </c>
+      <c r="M118" t="n">
+        <v>0.40277</v>
+      </c>
+      <c r="N118" t="n">
+        <v>0.47344</v>
+      </c>
+      <c r="O118" t="n">
+        <v>0.38056</v>
+      </c>
+      <c r="P118" t="n">
+        <v>0.37746</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>0.32598</v>
+      </c>
+      <c r="R118" t="n">
+        <v>0.33629</v>
+      </c>
+      <c r="S118" t="n">
+        <v>0.34338</v>
+      </c>
+      <c r="T118" t="n">
+        <v>0.32629</v>
+      </c>
+      <c r="U118" t="n">
+        <v>0.32673</v>
+      </c>
+      <c r="V118" t="n">
+        <v>0.31892</v>
+      </c>
+      <c r="W118" t="n">
+        <v>0.32138</v>
+      </c>
+      <c r="X118" t="n">
+        <v>0.31881</v>
+      </c>
+      <c r="Y118" t="n">
+        <v>0.33677</v>
+      </c>
+      <c r="Z118" t="n">
+        <v>0.33875</v>
+      </c>
+      <c r="AA118" t="n">
+        <v>0.37221</v>
+      </c>
+      <c r="AB118" t="n">
+        <v>0.32721</v>
+      </c>
+      <c r="AC118" t="n">
+        <v>0.36359</v>
+      </c>
+      <c r="AD118" t="n">
+        <v>0.39879</v>
+      </c>
+      <c r="AE118" t="n">
+        <v>0.35246</v>
+      </c>
+      <c r="AF118" t="n">
+        <v>0.38075</v>
+      </c>
+      <c r="AG118" t="n">
+        <v>0.34896</v>
+      </c>
+      <c r="AH118" t="n">
+        <v>0.34468</v>
+      </c>
+      <c r="AI118" t="n">
+        <v>0.37247</v>
+      </c>
+      <c r="AJ118" t="n">
+        <v>0.48083</v>
+      </c>
+      <c r="AK118" t="n">
+        <v>0.34774</v>
+      </c>
+      <c r="AL118" t="n">
+        <v>0.35075</v>
+      </c>
+      <c r="AM118" t="n">
+        <v>0.35923</v>
+      </c>
+      <c r="AN118" t="n">
+        <v>0.37403</v>
+      </c>
+      <c r="AO118" t="n">
+        <v>0.32147</v>
+      </c>
+      <c r="AP118" t="n">
+        <v>0.30635</v>
+      </c>
+      <c r="AQ118" t="n">
+        <v>0.30176</v>
+      </c>
+      <c r="AR118" t="n">
+        <v>0.35896</v>
+      </c>
+      <c r="AS118" t="n">
+        <v>0.49093</v>
+      </c>
+      <c r="AT118" t="n">
+        <v>0.50031</v>
+      </c>
+      <c r="AU118" t="n">
+        <v>0.66372</v>
+      </c>
+      <c r="AV118" t="n">
+        <v>0.6247999999999999</v>
+      </c>
+      <c r="AW118" t="n">
+        <v>0.84672</v>
+      </c>
+      <c r="AX118" t="n">
+        <v>0.29969</v>
+      </c>
+      <c r="AY118" t="n">
+        <v>0.35489</v>
+      </c>
+      <c r="AZ118" t="n">
+        <v>0.32822</v>
+      </c>
+      <c r="BA118" t="n">
+        <v>0.33198</v>
+      </c>
+      <c r="BB118" t="n">
+        <v>0.30766</v>
+      </c>
+      <c r="BC118" t="n">
+        <v>0.33794</v>
+      </c>
+      <c r="BD118" t="n">
+        <v>0.7396</v>
+      </c>
+      <c r="BE118" t="n">
+        <v>0.6824</v>
+      </c>
+      <c r="BF118" t="n">
+        <v>0.51683</v>
+      </c>
+      <c r="BG118" t="n">
+        <v>0.42571</v>
+      </c>
+      <c r="BH118" t="n">
+        <v>0.37713</v>
+      </c>
+      <c r="BI118" t="n">
+        <v>0.37421</v>
+      </c>
+      <c r="BJ118" t="n">
+        <v>0.38784</v>
+      </c>
+      <c r="BK118" t="n">
+        <v>0.67745</v>
+      </c>
+      <c r="BL118" t="n">
+        <v>0.39062</v>
+      </c>
+      <c r="BM118" t="n">
+        <v>0.37841</v>
+      </c>
+      <c r="BN118" t="n">
+        <v>1.20414</v>
+      </c>
+      <c r="BO118" t="n">
+        <v>0.6498200000000001</v>
+      </c>
+      <c r="BP118" t="n">
+        <v>1.1101</v>
+      </c>
+      <c r="BQ118" t="n">
+        <v>1.46246</v>
+      </c>
+      <c r="BR118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BS118" t="n">
+        <v>1.52569</v>
+      </c>
+      <c r="BT118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BU118" t="n">
+        <v>1.19264</v>
+      </c>
+      <c r="BV118" t="n">
+        <v>0.987</v>
+      </c>
+      <c r="BW118" t="n">
+        <v>1.36211</v>
+      </c>
+      <c r="BX118" t="n">
+        <v>1.18269</v>
+      </c>
+      <c r="BY118" t="n">
+        <v>1.39885</v>
+      </c>
+      <c r="BZ118" t="n">
+        <v>1.03658</v>
+      </c>
+      <c r="CA118" t="n">
+        <v>1.1673</v>
+      </c>
+      <c r="CB118" t="n">
+        <v>0.93638</v>
+      </c>
+      <c r="CC118" t="n">
+        <v>1.15456</v>
+      </c>
+      <c r="CD118" t="n">
+        <v>0.9905</v>
+      </c>
+      <c r="CE118" t="n">
+        <v>1.0213</v>
+      </c>
+      <c r="CF118" t="n">
+        <v>0.88419</v>
+      </c>
+      <c r="CG118" t="n">
+        <v>1.12159</v>
+      </c>
+      <c r="CH118" t="n">
+        <v>0.94838</v>
+      </c>
+      <c r="CI118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CJ118" t="n">
+        <v>0.46309</v>
+      </c>
+      <c r="CK118" t="n">
+        <v>0.8666699999999999</v>
+      </c>
+      <c r="CL118" t="n">
+        <v>0.8697999999999999</v>
+      </c>
+      <c r="CM118" t="n">
+        <v>0.46148</v>
+      </c>
+      <c r="CN118" t="n">
+        <v>0.43845</v>
+      </c>
+      <c r="CO118" t="n">
+        <v>0.45552</v>
+      </c>
+      <c r="CP118" t="n">
+        <v>0.33398</v>
+      </c>
+      <c r="CQ118" t="n">
+        <v>0.37879</v>
+      </c>
+      <c r="CR118" t="n">
+        <v>0.35687</v>
+      </c>
+      <c r="CS118" t="n">
+        <v>0.33495</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="n">
+        <v>46140</v>
+      </c>
+      <c r="B119" t="n">
+        <v>0.32142</v>
+      </c>
+      <c r="C119" t="n">
+        <v>0.51815</v>
+      </c>
+      <c r="D119" t="n">
+        <v>0.49644</v>
+      </c>
+      <c r="E119" t="n">
+        <v>0.49222</v>
+      </c>
+      <c r="F119" t="n">
+        <v>0.37726</v>
+      </c>
+      <c r="G119" t="n">
+        <v>0.44919</v>
+      </c>
+      <c r="H119" t="n">
+        <v>0.41678</v>
+      </c>
+      <c r="I119" t="n">
+        <v>0.37076</v>
+      </c>
+      <c r="J119" t="n">
+        <v>0.39177</v>
+      </c>
+      <c r="K119" t="n">
+        <v>0.3853</v>
+      </c>
+      <c r="L119" t="n">
+        <v>0.36502</v>
+      </c>
+      <c r="M119" t="n">
+        <v>0.43198</v>
+      </c>
+      <c r="N119" t="n">
+        <v>0.44811</v>
+      </c>
+      <c r="O119" t="n">
+        <v>0.3366</v>
+      </c>
+      <c r="P119" t="n">
+        <v>0.37225</v>
+      </c>
+      <c r="Q119" t="n">
+        <v>0.39891</v>
+      </c>
+      <c r="R119" t="n">
+        <v>0.36922</v>
+      </c>
+      <c r="S119" t="n">
+        <v>0.36994</v>
+      </c>
+      <c r="T119" t="n">
+        <v>0.35749</v>
+      </c>
+      <c r="U119" t="n">
+        <v>0.36318</v>
+      </c>
+      <c r="V119" t="n">
+        <v>0.35323</v>
+      </c>
+      <c r="W119" t="n">
+        <v>0.33778</v>
+      </c>
+      <c r="X119" t="n">
+        <v>0.34584</v>
+      </c>
+      <c r="Y119" t="n">
+        <v>0.37775</v>
+      </c>
+      <c r="Z119" t="n">
+        <v>0.39454</v>
+      </c>
+      <c r="AA119" t="n">
+        <v>0.47804</v>
+      </c>
+      <c r="AB119" t="n">
+        <v>0.44676</v>
+      </c>
+      <c r="AC119" t="n">
+        <v>0.44204</v>
+      </c>
+      <c r="AD119" t="n">
+        <v>0.34794</v>
+      </c>
+      <c r="AE119" t="n">
+        <v>0.39813</v>
+      </c>
+      <c r="AF119" t="n">
+        <v>0.3545</v>
+      </c>
+      <c r="AG119" t="n">
+        <v>0.36719</v>
+      </c>
+      <c r="AH119" t="n">
+        <v>0.34935</v>
+      </c>
+      <c r="AI119" t="n">
+        <v>0.16029</v>
+      </c>
+      <c r="AJ119" t="n">
+        <v>0.1994</v>
+      </c>
+      <c r="AK119" t="n">
+        <v>0.27523</v>
+      </c>
+      <c r="AL119" t="n">
+        <v>0.35389</v>
+      </c>
+      <c r="AM119" t="n">
+        <v>0.37194</v>
+      </c>
+      <c r="AN119" t="n">
+        <v>0.11797</v>
+      </c>
+      <c r="AO119" t="n">
+        <v>0.83105</v>
+      </c>
+      <c r="AP119" t="n">
+        <v>0.6810700000000001</v>
+      </c>
+      <c r="AQ119" t="n">
+        <v>0.36339</v>
+      </c>
+      <c r="AR119" t="n">
+        <v>0.6681</v>
+      </c>
+      <c r="AS119" t="n">
+        <v>0.8839600000000001</v>
+      </c>
+      <c r="AT119" t="n">
+        <v>0.88186</v>
+      </c>
+      <c r="AU119" t="n">
+        <v>0.9321699999999999</v>
+      </c>
+      <c r="AV119" t="n">
+        <v>0.88488</v>
+      </c>
+      <c r="AW119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX119" t="n">
+        <v>0.76109</v>
+      </c>
+      <c r="AY119" t="n">
+        <v>0.7747999999999999</v>
+      </c>
+      <c r="AZ119" t="n">
+        <v>0.79649</v>
+      </c>
+      <c r="BA119" t="n">
+        <v>0.9625900000000001</v>
+      </c>
+      <c r="BB119" t="n">
+        <v>0.5621699999999999</v>
+      </c>
+      <c r="BC119" t="n">
+        <v>0.6152799999999999</v>
+      </c>
+      <c r="BD119" t="n">
+        <v>0.91926</v>
+      </c>
+      <c r="BE119" t="n">
+        <v>0.88136</v>
+      </c>
+      <c r="BF119" t="n">
+        <v>0.73691</v>
+      </c>
+      <c r="BG119" t="n">
+        <v>0.9180499999999999</v>
+      </c>
+      <c r="BH119" t="n">
+        <v>0.53714</v>
+      </c>
+      <c r="BI119" t="n">
+        <v>1.17842</v>
+      </c>
+      <c r="BJ119" t="n">
+        <v>0.71235</v>
+      </c>
+      <c r="BK119" t="n">
+        <v>0.45256</v>
+      </c>
+      <c r="BL119" t="n">
+        <v>0.45806</v>
+      </c>
+      <c r="BM119" t="n">
+        <v>0.5134299999999999</v>
+      </c>
+      <c r="BN119" t="n">
+        <v>0.54114</v>
+      </c>
+      <c r="BO119" t="n">
+        <v>0.73188</v>
+      </c>
+      <c r="BP119" t="n">
+        <v>0.78371</v>
+      </c>
+      <c r="BQ119" t="n">
+        <v>0.73141</v>
+      </c>
+      <c r="BR119" t="n">
+        <v>0.67189</v>
+      </c>
+      <c r="BS119" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BT119" t="n">
+        <v>0.6449900000000001</v>
+      </c>
+      <c r="BU119" t="n">
+        <v>0.7034600000000001</v>
+      </c>
+      <c r="BV119" t="n">
+        <v>0.51546</v>
+      </c>
+      <c r="BW119" t="n">
+        <v>0.52873</v>
+      </c>
+      <c r="BX119" t="n">
+        <v>0.7042999999999999</v>
+      </c>
+      <c r="BY119" t="n">
+        <v>0.99663</v>
+      </c>
+      <c r="BZ119" t="n">
+        <v>0.8382999999999999</v>
+      </c>
+      <c r="CA119" t="n">
+        <v>1.34699</v>
+      </c>
+      <c r="CB119" t="n">
+        <v>0.50213</v>
+      </c>
+      <c r="CC119" t="n">
+        <v>0.6696</v>
+      </c>
+      <c r="CD119" t="n">
+        <v>0.5299299999999999</v>
+      </c>
+      <c r="CE119" t="n">
+        <v>0.6947000000000001</v>
+      </c>
+      <c r="CF119" t="n">
+        <v>0.9049700000000001</v>
+      </c>
+      <c r="CG119" t="n">
+        <v>1.10711</v>
+      </c>
+      <c r="CH119" t="n">
+        <v>0.7305</v>
+      </c>
+      <c r="CI119" t="n">
+        <v>1.47637</v>
+      </c>
+      <c r="CJ119" t="n">
+        <v>0.9974299999999999</v>
+      </c>
+      <c r="CK119" t="n">
+        <v>0.62215</v>
+      </c>
+      <c r="CL119" t="n">
+        <v>0.56224</v>
+      </c>
+      <c r="CM119" t="n">
+        <v>0.68698</v>
+      </c>
+      <c r="CN119" t="n">
+        <v>0.44767</v>
+      </c>
+      <c r="CO119" t="n">
+        <v>0.46821</v>
+      </c>
+      <c r="CP119" t="n">
+        <v>0.4034700000000001</v>
+      </c>
+      <c r="CQ119" t="n">
+        <v>0.36193</v>
+      </c>
+      <c r="CR119" t="n">
+        <v>0.34931</v>
+      </c>
+      <c r="CS119" t="n">
+        <v>0.34245</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="n">
+        <v>46141</v>
+      </c>
+      <c r="B120" t="n">
+        <v>0.31894</v>
+      </c>
+      <c r="C120" t="n">
+        <v>0.49788</v>
+      </c>
+      <c r="D120" t="n">
+        <v>0.4788</v>
+      </c>
+      <c r="E120" t="n">
+        <v>0.43033</v>
+      </c>
+      <c r="F120" t="n">
+        <v>0.38775</v>
+      </c>
+      <c r="G120" t="n">
+        <v>0.38764</v>
+      </c>
+      <c r="H120" t="n">
+        <v>0.38419</v>
+      </c>
+      <c r="I120" t="n">
+        <v>0.36556</v>
+      </c>
+      <c r="J120" t="n">
+        <v>0.35869</v>
+      </c>
+      <c r="K120" t="n">
+        <v>0.384</v>
+      </c>
+      <c r="L120" t="n">
+        <v>0.38219</v>
+      </c>
+      <c r="M120" t="n">
+        <v>0.36186</v>
+      </c>
+      <c r="N120" t="n">
+        <v>0.43814</v>
+      </c>
+      <c r="O120" t="n">
+        <v>0.3623</v>
+      </c>
+      <c r="P120" t="n">
+        <v>0.35091</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>0.36551</v>
+      </c>
+      <c r="R120" t="n">
+        <v>0.35799</v>
+      </c>
+      <c r="S120" t="n">
+        <v>0.35897</v>
+      </c>
+      <c r="T120" t="n">
+        <v>0.33921</v>
+      </c>
+      <c r="U120" t="n">
+        <v>0.33669</v>
+      </c>
+      <c r="V120" t="n">
+        <v>0.33344</v>
+      </c>
+      <c r="W120" t="n">
+        <v>0.33632</v>
+      </c>
+      <c r="X120" t="n">
+        <v>0.33278</v>
+      </c>
+      <c r="Y120" t="n">
+        <v>0.3513</v>
+      </c>
+      <c r="Z120" t="n">
+        <v>0.34014</v>
+      </c>
+      <c r="AA120" t="n">
+        <v>0.35053</v>
+      </c>
+      <c r="AB120" t="n">
+        <v>0.38281</v>
+      </c>
+      <c r="AC120" t="n">
+        <v>0.3835</v>
+      </c>
+      <c r="AD120" t="n">
+        <v>0.35112</v>
+      </c>
+      <c r="AE120" t="n">
+        <v>0.374</v>
+      </c>
+      <c r="AF120" t="n">
+        <v>0.34545</v>
+      </c>
+      <c r="AG120" t="n">
+        <v>0.40078</v>
+      </c>
+      <c r="AH120" t="n">
+        <v>0.41626</v>
+      </c>
+      <c r="AI120" t="n">
+        <v>0.43815</v>
+      </c>
+      <c r="AJ120" t="n">
+        <v>0.35733</v>
+      </c>
+      <c r="AK120" t="n">
+        <v>0.44316</v>
+      </c>
+      <c r="AL120" t="n">
+        <v>0.34223</v>
+      </c>
+      <c r="AM120" t="n">
+        <v>0.37476</v>
+      </c>
+      <c r="AN120" t="n">
+        <v>0.35156</v>
+      </c>
+      <c r="AO120" t="n">
+        <v>0.32802</v>
+      </c>
+      <c r="AP120" t="n">
+        <v>0.5153</v>
+      </c>
+      <c r="AQ120" t="n">
+        <v>0.35424</v>
+      </c>
+      <c r="AR120" t="n">
+        <v>0.35388</v>
+      </c>
+      <c r="AS120" t="n">
+        <v>0.39249</v>
+      </c>
+      <c r="AT120" t="n">
+        <v>0.9920599999999999</v>
+      </c>
+      <c r="AU120" t="n">
+        <v>0.48069</v>
+      </c>
+      <c r="AV120" t="n">
+        <v>0.46532</v>
+      </c>
+      <c r="AW120" t="n">
+        <v>0.3761</v>
+      </c>
+      <c r="AX120" t="n">
+        <v>0.53806</v>
+      </c>
+      <c r="AY120" t="n">
+        <v>0.29168</v>
+      </c>
+      <c r="AZ120" t="n">
+        <v>0.7713</v>
+      </c>
+      <c r="BA120" t="n">
+        <v>0.40601</v>
+      </c>
+      <c r="BB120" t="n">
+        <v>0.37852</v>
+      </c>
+      <c r="BC120" t="n">
+        <v>0.32543</v>
+      </c>
+      <c r="BD120" t="n">
+        <v>0.43829</v>
+      </c>
+      <c r="BE120" t="n">
+        <v>1.04321</v>
+      </c>
+      <c r="BF120" t="n">
+        <v>0.3454700000000001</v>
+      </c>
+      <c r="BG120" t="n">
+        <v>0.31956</v>
+      </c>
+      <c r="BH120" t="n">
+        <v>0.31752</v>
+      </c>
+      <c r="BI120" t="n">
+        <v>0.34521</v>
+      </c>
+      <c r="BJ120" t="n">
+        <v>0.7738400000000001</v>
+      </c>
+      <c r="BK120" t="n">
+        <v>0.5560900000000001</v>
+      </c>
+      <c r="BL120" t="n">
+        <v>0.52076</v>
+      </c>
+      <c r="BM120" t="n">
+        <v>0.9274199999999999</v>
+      </c>
+      <c r="BN120" t="n">
+        <v>0.37631</v>
+      </c>
+      <c r="BO120" t="n">
+        <v>0.44728</v>
+      </c>
+      <c r="BP120" t="n">
+        <v>0.91576</v>
+      </c>
+      <c r="BQ120" t="n">
+        <v>1.3793</v>
+      </c>
+      <c r="BR120" t="n">
+        <v>1.06191</v>
+      </c>
+      <c r="BS120" t="n">
+        <v>0.82626</v>
+      </c>
+      <c r="BT120" t="n">
+        <v>0.45065</v>
+      </c>
+      <c r="BU120" t="n">
+        <v>0.63809</v>
+      </c>
+      <c r="BV120" t="n">
+        <v>0.45102</v>
+      </c>
+      <c r="BW120" t="n">
+        <v>0.6948099999999999</v>
+      </c>
+      <c r="BX120" t="n">
+        <v>0.8096100000000001</v>
+      </c>
+      <c r="BY120" t="n">
+        <v>1.06447</v>
+      </c>
+      <c r="BZ120" t="n">
+        <v>0.73978</v>
+      </c>
+      <c r="CA120" t="n">
+        <v>0.6651900000000001</v>
+      </c>
+      <c r="CB120" t="n">
+        <v>0.7819400000000001</v>
+      </c>
+      <c r="CC120" t="n">
+        <v>0.75825</v>
+      </c>
+      <c r="CD120" t="n">
+        <v>0.50248</v>
+      </c>
+      <c r="CE120" t="n">
+        <v>0.6247200000000001</v>
+      </c>
+      <c r="CF120" t="n">
+        <v>0.58088</v>
+      </c>
+      <c r="CG120" t="n">
+        <v>0.57192</v>
+      </c>
+      <c r="CH120" t="n">
+        <v>0.54976</v>
+      </c>
+      <c r="CI120" t="n">
+        <v>0.43054</v>
+      </c>
+      <c r="CJ120" t="n">
+        <v>0.43679</v>
+      </c>
+      <c r="CK120" t="n">
+        <v>0.35129</v>
+      </c>
+      <c r="CL120" t="n">
+        <v>0.3462</v>
+      </c>
+      <c r="CM120" t="n">
+        <v>0.32076</v>
+      </c>
+      <c r="CN120" t="n">
+        <v>0.32368</v>
+      </c>
+      <c r="CO120" t="n">
+        <v>0.32083</v>
+      </c>
+      <c r="CP120" t="n">
+        <v>0.3134</v>
+      </c>
+      <c r="CQ120" t="n">
+        <v>0.31873</v>
+      </c>
+      <c r="CR120" t="n">
+        <v>0.3229</v>
+      </c>
+      <c r="CS120" t="n">
+        <v>0.35061</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="n">
+        <v>46142</v>
+      </c>
+      <c r="B121" t="n">
+        <v>0.3051</v>
+      </c>
+      <c r="C121" t="n">
+        <v>0.37059</v>
+      </c>
+      <c r="D121" t="n">
+        <v>0.37577</v>
+      </c>
+      <c r="E121" t="n">
+        <v>0.37525</v>
+      </c>
+      <c r="F121" t="n">
+        <v>0.35391</v>
+      </c>
+      <c r="G121" t="n">
+        <v>0.34015</v>
+      </c>
+      <c r="H121" t="n">
+        <v>0.32789</v>
+      </c>
+      <c r="I121" t="n">
+        <v>0.32761</v>
+      </c>
+      <c r="J121" t="n">
+        <v>0.33115</v>
+      </c>
+      <c r="K121" t="n">
+        <v>0.32044</v>
+      </c>
+      <c r="L121" t="n">
+        <v>0.31885</v>
+      </c>
+      <c r="M121" t="n">
+        <v>0.31581</v>
+      </c>
+      <c r="N121" t="n">
+        <v>0.31824</v>
+      </c>
+      <c r="O121" t="n">
+        <v>0.31871</v>
+      </c>
+      <c r="P121" t="n">
+        <v>0.31513</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>0.3168</v>
+      </c>
+      <c r="R121" t="n">
+        <v>0.31194</v>
+      </c>
+      <c r="S121" t="n">
+        <v>0.31332</v>
+      </c>
+      <c r="T121" t="n">
+        <v>0.31818</v>
+      </c>
+      <c r="U121" t="n">
+        <v>0.3157799999999999</v>
+      </c>
+      <c r="V121" t="n">
+        <v>0.30995</v>
+      </c>
+      <c r="W121" t="n">
+        <v>0.30935</v>
+      </c>
+      <c r="X121" t="n">
+        <v>0.3133</v>
+      </c>
+      <c r="Y121" t="n">
+        <v>0.31452</v>
+      </c>
+      <c r="Z121" t="n">
+        <v>0.31646</v>
+      </c>
+      <c r="AA121" t="n">
+        <v>0.32452</v>
+      </c>
+      <c r="AB121" t="n">
+        <v>0.32434</v>
+      </c>
+      <c r="AC121" t="n">
+        <v>0.3326</v>
+      </c>
+      <c r="AD121" t="n">
+        <v>0.32612</v>
+      </c>
+      <c r="AE121" t="n">
+        <v>0.31932</v>
+      </c>
+      <c r="AF121" t="n">
+        <v>0.31972</v>
+      </c>
+      <c r="AG121" t="n">
+        <v>0.30782</v>
+      </c>
+      <c r="AH121" t="n">
+        <v>0.32041</v>
+      </c>
+      <c r="AI121" t="n">
+        <v>0.34421</v>
+      </c>
+      <c r="AJ121" t="n">
+        <v>0.30028</v>
+      </c>
+      <c r="AK121" t="n">
+        <v>0.28649</v>
+      </c>
+      <c r="AL121" t="n">
+        <v>0.31889</v>
+      </c>
+      <c r="AM121" t="n">
+        <v>0.3137799999999999</v>
+      </c>
+      <c r="AN121" t="n">
+        <v>0.33485</v>
+      </c>
+      <c r="AO121" t="n">
+        <v>0.31883</v>
+      </c>
+      <c r="AP121" t="n">
+        <v>0.30381</v>
+      </c>
+      <c r="AQ121" t="n">
+        <v>0.28927</v>
+      </c>
+      <c r="AR121" t="n">
+        <v>0.29631</v>
+      </c>
+      <c r="AS121" t="n">
+        <v>0.3195</v>
+      </c>
+      <c r="AT121" t="n">
+        <v>0.31921</v>
+      </c>
+      <c r="AU121" t="n">
+        <v>0.31758</v>
+      </c>
+      <c r="AV121" t="n">
+        <v>0.14344</v>
+      </c>
+      <c r="AW121" t="n">
+        <v>0.3165</v>
+      </c>
+      <c r="AX121" t="n">
+        <v>0.02476</v>
+      </c>
+      <c r="AY121" t="n">
+        <v>0.30495</v>
+      </c>
+      <c r="AZ121" t="n">
+        <v>0.29944</v>
+      </c>
+      <c r="BA121" t="n">
+        <v>0.29703</v>
+      </c>
+      <c r="BB121" t="n">
+        <v>0.32053</v>
+      </c>
+      <c r="BC121" t="n">
+        <v>0.32659</v>
+      </c>
+      <c r="BD121" t="n">
+        <v>0.31139</v>
+      </c>
+      <c r="BE121" t="n">
+        <v>0.40716</v>
+      </c>
+      <c r="BF121" t="n">
+        <v>0.52047</v>
+      </c>
+      <c r="BG121" t="n">
+        <v>0.26594</v>
+      </c>
+      <c r="BH121" t="n">
+        <v>0.25705</v>
+      </c>
+      <c r="BI121" t="n">
+        <v>0.24039</v>
+      </c>
+      <c r="BJ121" t="n">
+        <v>0.10534</v>
+      </c>
+      <c r="BK121" t="n">
+        <v>0.31338</v>
+      </c>
+      <c r="BL121" t="n">
+        <v>0.27647</v>
+      </c>
+      <c r="BM121" t="n">
+        <v>0.029</v>
+      </c>
+      <c r="BN121" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BO121" t="n">
+        <v>0.26346</v>
+      </c>
+      <c r="BP121" t="n">
+        <v>0.29737</v>
+      </c>
+      <c r="BQ121" t="n">
+        <v>0.29978</v>
+      </c>
+      <c r="BR121" t="n">
+        <v>0.3081</v>
+      </c>
+      <c r="BS121" t="n">
+        <v>0.30058</v>
+      </c>
+      <c r="BT121" t="n">
+        <v>0.30481</v>
+      </c>
+      <c r="BU121" t="n">
+        <v>0.31995</v>
+      </c>
+      <c r="BV121" t="n">
+        <v>0.32957</v>
+      </c>
+      <c r="BW121" t="n">
+        <v>0.31545</v>
+      </c>
+      <c r="BX121" t="n">
+        <v>0.33545</v>
+      </c>
+      <c r="BY121" t="n">
+        <v>0.33571</v>
+      </c>
+      <c r="BZ121" t="n">
+        <v>0.33584</v>
+      </c>
+      <c r="CA121" t="n">
+        <v>0.32631</v>
+      </c>
+      <c r="CB121" t="n">
+        <v>0.33558</v>
+      </c>
+      <c r="CC121" t="n">
+        <v>0.34598</v>
+      </c>
+      <c r="CD121" t="n">
+        <v>0.33745</v>
+      </c>
+      <c r="CE121" t="n">
+        <v>0.34915</v>
+      </c>
+      <c r="CF121" t="n">
+        <v>0.34758</v>
+      </c>
+      <c r="CG121" t="n">
+        <v>0.34753</v>
+      </c>
+      <c r="CH121" t="n">
+        <v>0.36148</v>
+      </c>
+      <c r="CI121" t="n">
+        <v>0.36557</v>
+      </c>
+      <c r="CJ121" t="n">
+        <v>0.42802</v>
+      </c>
+      <c r="CK121" t="n">
+        <v>0.35561</v>
+      </c>
+      <c r="CL121" t="n">
+        <v>0.36669</v>
+      </c>
+      <c r="CM121" t="n">
+        <v>0.36132</v>
+      </c>
+      <c r="CN121" t="n">
+        <v>0.42227</v>
+      </c>
+      <c r="CO121" t="n">
+        <v>0.34212</v>
+      </c>
+      <c r="CP121" t="n">
+        <v>0.35145</v>
+      </c>
+      <c r="CQ121" t="n">
+        <v>0.34277</v>
+      </c>
+      <c r="CR121" t="n">
+        <v>0.34935</v>
+      </c>
+      <c r="CS121" t="n">
+        <v>0.31747</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B122" t="n">
+        <v>0.38022</v>
+      </c>
+      <c r="C122" t="n">
+        <v>0.31679</v>
+      </c>
+      <c r="D122" t="n">
+        <v>0.30105</v>
+      </c>
+      <c r="E122" t="n">
+        <v>0.2424</v>
+      </c>
+      <c r="F122" t="n">
+        <v>0.24852</v>
+      </c>
+      <c r="G122" t="n">
+        <v>0.23821</v>
+      </c>
+      <c r="H122" t="n">
+        <v>0.34131</v>
+      </c>
+      <c r="I122" t="n">
+        <v>0.28834</v>
+      </c>
+      <c r="J122" t="n">
+        <v>0.32765</v>
+      </c>
+      <c r="K122" t="n">
+        <v>0.19254</v>
+      </c>
+      <c r="L122" t="n">
+        <v>0.29293</v>
+      </c>
+      <c r="M122" t="n">
+        <v>0.16057</v>
+      </c>
+      <c r="N122" t="n">
+        <v>0.24957</v>
+      </c>
+      <c r="O122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="P122" t="n">
+        <v>0.31745</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>0.32685</v>
+      </c>
+      <c r="R122" t="n">
+        <v>0.30528</v>
+      </c>
+      <c r="S122" t="n">
+        <v>0.1778</v>
+      </c>
+      <c r="T122" t="n">
+        <v>0.24884</v>
+      </c>
+      <c r="U122" t="n">
+        <v>0.21578</v>
+      </c>
+      <c r="V122" t="n">
+        <v>0.19368</v>
+      </c>
+      <c r="W122" t="n">
+        <v>0.28369</v>
+      </c>
+      <c r="X122" t="n">
+        <v>0.17525</v>
+      </c>
+      <c r="Y122" t="n">
+        <v>0.30558</v>
+      </c>
+      <c r="Z122" t="n">
+        <v>0.24983</v>
+      </c>
+      <c r="AA122" t="n">
+        <v>0.27117</v>
+      </c>
+      <c r="AB122" t="n">
+        <v>0.32227</v>
+      </c>
+      <c r="AC122" t="n">
+        <v>0.20228</v>
+      </c>
+      <c r="AD122" t="n">
+        <v>0.26749</v>
+      </c>
+      <c r="AE122" t="n">
+        <v>0.10251</v>
+      </c>
+      <c r="AF122" t="n">
+        <v>0.10092</v>
+      </c>
+      <c r="AG122" t="n">
+        <v>0.04244</v>
+      </c>
+      <c r="AH122" t="n">
+        <v>-0.04697999999999999</v>
+      </c>
+      <c r="AI122" t="n">
+        <v>-0.04574</v>
+      </c>
+      <c r="AJ122" t="n">
+        <v>-0.04621</v>
+      </c>
+      <c r="AK122" t="n">
+        <v>-0.04409</v>
+      </c>
+      <c r="AL122" t="n">
+        <v>-0.04621</v>
+      </c>
+      <c r="AM122" t="n">
+        <v>-0.04482999999999999</v>
+      </c>
+      <c r="AN122" t="n">
+        <v>-0.04398</v>
+      </c>
+      <c r="AO122" t="n">
+        <v>0.32176</v>
+      </c>
+      <c r="AP122" t="n">
+        <v>0.01002</v>
+      </c>
+      <c r="AQ122" t="n">
+        <v>0.20621</v>
+      </c>
+      <c r="AR122" t="n">
+        <v>0.04926</v>
+      </c>
+      <c r="AS122" t="n">
+        <v>0.27542</v>
+      </c>
+      <c r="AT122" t="n">
+        <v>0.19389</v>
+      </c>
+      <c r="AU122" t="n">
+        <v>0.32371</v>
+      </c>
+      <c r="AV122" t="n">
+        <v>-0.04392</v>
+      </c>
+      <c r="AW122" t="n">
+        <v>-0.04394</v>
+      </c>
+      <c r="AX122" t="n">
+        <v>-0.04574</v>
+      </c>
+      <c r="AY122" t="n">
+        <v>-0.0456</v>
+      </c>
+      <c r="AZ122" t="n">
+        <v>-0.04561</v>
+      </c>
+      <c r="BA122" t="n">
+        <v>-0.04369</v>
+      </c>
+      <c r="BB122" t="n">
+        <v>-0.04335</v>
+      </c>
+      <c r="BC122" t="n">
+        <v>-0.04549</v>
+      </c>
+      <c r="BD122" t="n">
+        <v>-0.04339</v>
+      </c>
+      <c r="BE122" t="n">
+        <v>0.01005</v>
+      </c>
+      <c r="BF122" t="n">
+        <v>-0.0453</v>
+      </c>
+      <c r="BG122" t="n">
+        <v>-0.04525</v>
+      </c>
+      <c r="BH122" t="n">
+        <v>-0.04538</v>
+      </c>
+      <c r="BI122" t="n">
+        <v>-0.04358</v>
+      </c>
+      <c r="BJ122" t="n">
+        <v>-0.04422</v>
+      </c>
+      <c r="BK122" t="n">
+        <v>0.06035</v>
+      </c>
+      <c r="BL122" t="n">
+        <v>0.05856</v>
+      </c>
+      <c r="BM122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN122" t="n">
+        <v>-0.04471</v>
+      </c>
+      <c r="BO122" t="n">
+        <v>-0.04997</v>
+      </c>
+      <c r="BP122" t="n">
+        <v>-0.04985</v>
+      </c>
+      <c r="BQ122" t="n">
+        <v>-0.0474</v>
+      </c>
+      <c r="BR122" t="n">
+        <v>-0.04790999999999999</v>
+      </c>
+      <c r="BS122" t="n">
+        <v>0.19975</v>
+      </c>
+      <c r="BT122" t="n">
+        <v>0.14272</v>
+      </c>
+      <c r="BU122" t="n">
+        <v>0.28993</v>
+      </c>
+      <c r="BV122" t="n">
+        <v>0.29465</v>
+      </c>
+      <c r="BW122" t="n">
+        <v>0.30454</v>
+      </c>
+      <c r="BX122" t="n">
+        <v>0.29982</v>
+      </c>
+      <c r="BY122" t="n">
+        <v>0.29492</v>
+      </c>
+      <c r="BZ122" t="n">
+        <v>0.29282</v>
+      </c>
+      <c r="CA122" t="n">
+        <v>0.29328</v>
+      </c>
+      <c r="CB122" t="n">
+        <v>0.29225</v>
+      </c>
+      <c r="CC122" t="n">
+        <v>0.29677</v>
+      </c>
+      <c r="CD122" t="n">
+        <v>0.29074</v>
+      </c>
+      <c r="CE122" t="n">
+        <v>0.29497</v>
+      </c>
+      <c r="CF122" t="n">
+        <v>0.26875</v>
+      </c>
+      <c r="CG122" t="n">
+        <v>0.29381</v>
+      </c>
+      <c r="CH122" t="n">
+        <v>0.29802</v>
+      </c>
+      <c r="CI122" t="n">
+        <v>0.30855</v>
+      </c>
+      <c r="CJ122" t="n">
+        <v>0.30375</v>
+      </c>
+      <c r="CK122" t="n">
+        <v>0.30221</v>
+      </c>
+      <c r="CL122" t="n">
+        <v>0.31434</v>
+      </c>
+      <c r="CM122" t="n">
+        <v>0.31839</v>
+      </c>
+      <c r="CN122" t="n">
+        <v>0.34718</v>
+      </c>
+      <c r="CO122" t="n">
+        <v>0.34001</v>
+      </c>
+      <c r="CP122" t="n">
+        <v>0.32558</v>
+      </c>
+      <c r="CQ122" t="n">
+        <v>0.3403</v>
+      </c>
+      <c r="CR122" t="n">
+        <v>0.34387</v>
+      </c>
+      <c r="CS122" t="n">
+        <v>0.31592</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="n">
+        <v>46144</v>
+      </c>
+      <c r="B123" t="n">
+        <v>0.3023</v>
+      </c>
+      <c r="C123" t="n">
+        <v>1.34536</v>
+      </c>
+      <c r="D123" t="n">
+        <v>0.31065</v>
+      </c>
+      <c r="E123" t="n">
+        <v>0.36286</v>
+      </c>
+      <c r="F123" t="n">
+        <v>0.32743</v>
+      </c>
+      <c r="G123" t="n">
+        <v>0.3193</v>
+      </c>
+      <c r="H123" t="n">
+        <v>0.30704</v>
+      </c>
+      <c r="I123" t="n">
+        <v>0.31462</v>
+      </c>
+      <c r="J123" t="n">
+        <v>0.30134</v>
+      </c>
+      <c r="K123" t="n">
+        <v>0.28114</v>
+      </c>
+      <c r="L123" t="n">
+        <v>0.29442</v>
+      </c>
+      <c r="M123" t="n">
+        <v>0.29069</v>
+      </c>
+      <c r="N123" t="n">
+        <v>0.28802</v>
+      </c>
+      <c r="O123" t="n">
+        <v>0.28084</v>
+      </c>
+      <c r="P123" t="n">
+        <v>0.27116</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>0.27089</v>
+      </c>
+      <c r="R123" t="n">
+        <v>0.2810299999999999</v>
+      </c>
+      <c r="S123" t="n">
+        <v>0.17236</v>
+      </c>
+      <c r="T123" t="n">
+        <v>0.1586</v>
+      </c>
+      <c r="U123" t="n">
+        <v>0.17092</v>
+      </c>
+      <c r="V123" t="n">
+        <v>0.1477</v>
+      </c>
+      <c r="W123" t="n">
+        <v>0.15943</v>
+      </c>
+      <c r="X123" t="n">
+        <v>0.15858</v>
+      </c>
+      <c r="Y123" t="n">
+        <v>0.23612</v>
+      </c>
+      <c r="Z123" t="n">
+        <v>0.214</v>
+      </c>
+      <c r="AA123" t="n">
+        <v>0.22651</v>
+      </c>
+      <c r="AB123" t="n">
+        <v>0.26883</v>
+      </c>
+      <c r="AC123" t="n">
+        <v>0.28566</v>
+      </c>
+      <c r="AD123" t="n">
+        <v>0.29075</v>
+      </c>
+      <c r="AE123" t="n">
+        <v>0.31932</v>
+      </c>
+      <c r="AF123" t="n">
+        <v>0.28069</v>
+      </c>
+      <c r="AG123" t="n">
+        <v>0.28083</v>
+      </c>
+      <c r="AH123" t="n">
+        <v>0.28102</v>
+      </c>
+      <c r="AI123" t="n">
+        <v>0.28043</v>
+      </c>
+      <c r="AJ123" t="n">
+        <v>0.27069</v>
+      </c>
+      <c r="AK123" t="n">
+        <v>0.28091</v>
+      </c>
+      <c r="AL123" t="n">
+        <v>0.32236</v>
+      </c>
+      <c r="AM123" t="n">
+        <v>0.31015</v>
+      </c>
+      <c r="AN123" t="n">
+        <v>0.30493</v>
+      </c>
+      <c r="AO123" t="n">
+        <v>0.3163</v>
+      </c>
+      <c r="AP123" t="n">
+        <v>0.30938</v>
+      </c>
+      <c r="AQ123" t="n">
+        <v>0.35894</v>
+      </c>
+      <c r="AR123" t="n">
+        <v>0.31625</v>
+      </c>
+      <c r="AS123" t="n">
+        <v>0.29728</v>
+      </c>
+      <c r="AT123" t="n">
+        <v>0.40965</v>
+      </c>
+      <c r="AU123" t="n">
+        <v>0.38234</v>
+      </c>
+      <c r="AV123" t="n">
+        <v>0.43216</v>
+      </c>
+      <c r="AW123" t="n">
+        <v>0.46309</v>
+      </c>
+      <c r="AX123" t="n">
+        <v>0.33181</v>
+      </c>
+      <c r="AY123" t="n">
+        <v>0.41843</v>
+      </c>
+      <c r="AZ123" t="n">
+        <v>0.41526</v>
+      </c>
+      <c r="BA123" t="n">
+        <v>0.40405</v>
+      </c>
+      <c r="BB123" t="n">
+        <v>0.40241</v>
+      </c>
+      <c r="BC123" t="n">
+        <v>0.30005</v>
+      </c>
+      <c r="BD123" t="n">
+        <v>0.30095</v>
+      </c>
+      <c r="BE123" t="n">
+        <v>0.29929</v>
+      </c>
+      <c r="BF123" t="n">
+        <v>0.29998</v>
+      </c>
+      <c r="BG123" t="n">
+        <v>0.15654</v>
+      </c>
+      <c r="BH123" t="n">
+        <v>0.29427</v>
+      </c>
+      <c r="BI123" t="n">
+        <v>0.31093</v>
+      </c>
+      <c r="BJ123" t="n">
+        <v>0.31342</v>
+      </c>
+      <c r="BK123" t="n">
+        <v>0.31267</v>
+      </c>
+      <c r="BL123" t="n">
+        <v>0.32184</v>
+      </c>
+      <c r="BM123" t="n">
+        <v>0.34627</v>
+      </c>
+      <c r="BN123" t="n">
+        <v>0.30067</v>
+      </c>
+      <c r="BO123" t="n">
+        <v>0.33082</v>
+      </c>
+      <c r="BP123" t="n">
+        <v>0.38545</v>
+      </c>
+      <c r="BQ123" t="n">
+        <v>0.47916</v>
+      </c>
+      <c r="BR123" t="n">
+        <v>0.5076700000000001</v>
+      </c>
+      <c r="BS123" t="n">
+        <v>0.79098</v>
+      </c>
+      <c r="BT123" t="n">
+        <v>0.6220399999999999</v>
+      </c>
+      <c r="BU123" t="n">
+        <v>0.78598</v>
+      </c>
+      <c r="BV123" t="n">
+        <v>0.40003</v>
+      </c>
+      <c r="BW123" t="n">
+        <v>0.49797</v>
+      </c>
+      <c r="BX123" t="n">
+        <v>0.7810199999999999</v>
+      </c>
+      <c r="BY123" t="n">
+        <v>0.92039</v>
+      </c>
+      <c r="BZ123" t="n">
+        <v>0.49456</v>
+      </c>
+      <c r="CA123" t="n">
+        <v>0.9142</v>
+      </c>
+      <c r="CB123" t="n">
+        <v>0.86287</v>
+      </c>
+      <c r="CC123" t="n">
+        <v>1.2962</v>
+      </c>
+      <c r="CD123" t="n">
+        <v>0.35363</v>
+      </c>
+      <c r="CE123" t="n">
+        <v>0.88749</v>
+      </c>
+      <c r="CF123" t="n">
+        <v>0.6316000000000001</v>
+      </c>
+      <c r="CG123" t="n">
+        <v>1.18707</v>
+      </c>
+      <c r="CH123" t="n">
+        <v>0.87034</v>
+      </c>
+      <c r="CI123" t="n">
+        <v>0.65504</v>
+      </c>
+      <c r="CJ123" t="n">
+        <v>1.33083</v>
+      </c>
+      <c r="CK123" t="n">
+        <v>1.0329</v>
+      </c>
+      <c r="CL123" t="n">
+        <v>0.53077</v>
+      </c>
+      <c r="CM123" t="n">
+        <v>0.7909700000000001</v>
+      </c>
+      <c r="CN123" t="n">
+        <v>0.5726599999999999</v>
+      </c>
+      <c r="CO123" t="n">
+        <v>0.7729600000000001</v>
+      </c>
+      <c r="CP123" t="n">
+        <v>0.7775299999999999</v>
+      </c>
+      <c r="CQ123" t="n">
+        <v>0.8767699999999999</v>
+      </c>
+      <c r="CR123" t="n">
+        <v>0.87386</v>
+      </c>
+      <c r="CS123" t="n">
+        <v>0.49314</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="n">
+        <v>46145</v>
+      </c>
+      <c r="B124" t="n">
+        <v>0.39866</v>
+      </c>
+      <c r="C124" t="n">
+        <v>1.39987</v>
+      </c>
+      <c r="D124" t="n">
+        <v>0.44993</v>
+      </c>
+      <c r="E124" t="n">
+        <v>1.20698</v>
+      </c>
+      <c r="F124" t="n">
+        <v>0.87883</v>
+      </c>
+      <c r="G124" t="n">
+        <v>0.55102</v>
+      </c>
+      <c r="H124" t="n">
+        <v>0.62183</v>
+      </c>
+      <c r="I124" t="n">
+        <v>0.53832</v>
+      </c>
+      <c r="J124" t="n">
+        <v>0.49768</v>
+      </c>
+      <c r="K124" t="n">
+        <v>0.45581</v>
+      </c>
+      <c r="L124" t="n">
+        <v>0.42425</v>
+      </c>
+      <c r="M124" t="n">
+        <v>0.43714</v>
+      </c>
+      <c r="N124" t="n">
+        <v>0.43617</v>
+      </c>
+      <c r="O124" t="n">
+        <v>0.38817</v>
+      </c>
+      <c r="P124" t="n">
+        <v>0.45268</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>0.41432</v>
+      </c>
+      <c r="R124" t="n">
+        <v>0.32827</v>
+      </c>
+      <c r="S124" t="n">
+        <v>0.39283</v>
+      </c>
+      <c r="T124" t="n">
+        <v>0.35347</v>
+      </c>
+      <c r="U124" t="n">
+        <v>0.37792</v>
+      </c>
+      <c r="V124" t="n">
+        <v>0.38769</v>
+      </c>
+      <c r="W124" t="n">
+        <v>0.3985</v>
+      </c>
+      <c r="X124" t="n">
+        <v>0.32391</v>
+      </c>
+      <c r="Y124" t="n">
+        <v>0.37461</v>
+      </c>
+      <c r="Z124" t="n">
+        <v>0.32781</v>
+      </c>
+      <c r="AA124" t="n">
+        <v>0.32567</v>
+      </c>
+      <c r="AB124" t="n">
+        <v>0.32038</v>
+      </c>
+      <c r="AC124" t="n">
+        <v>0.32222</v>
+      </c>
+      <c r="AD124" t="n">
+        <v>0.3157</v>
+      </c>
+      <c r="AE124" t="n">
+        <v>0.34744</v>
+      </c>
+      <c r="AF124" t="n">
+        <v>0.44373</v>
+      </c>
+      <c r="AG124" t="n">
+        <v>0.32053</v>
+      </c>
+      <c r="AH124" t="n">
+        <v>0.36392</v>
+      </c>
+      <c r="AI124" t="n">
+        <v>0.32226</v>
+      </c>
+      <c r="AJ124" t="n">
+        <v>0.45573</v>
+      </c>
+      <c r="AK124" t="n">
+        <v>0.32251</v>
+      </c>
+      <c r="AL124" t="n">
+        <v>0.55137</v>
+      </c>
+      <c r="AM124" t="n">
+        <v>0.6105700000000001</v>
+      </c>
+      <c r="AN124" t="n">
+        <v>0.8861100000000001</v>
+      </c>
+      <c r="AO124" t="n">
+        <v>0.67715</v>
+      </c>
+      <c r="AP124" t="n">
+        <v>0.29037</v>
+      </c>
+      <c r="AQ124" t="n">
+        <v>0.44069</v>
+      </c>
+      <c r="AR124" t="n">
+        <v>0.54042</v>
+      </c>
+      <c r="AS124" t="n">
+        <v>0.95536</v>
+      </c>
+      <c r="AT124" t="n">
+        <v>0.38675</v>
+      </c>
+      <c r="AU124" t="n">
+        <v>1.18708</v>
+      </c>
+      <c r="AV124" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AW124" t="n">
+        <v>0.87501</v>
+      </c>
+      <c r="AX124" t="n">
+        <v>0.32811</v>
+      </c>
+      <c r="AY124" t="n">
+        <v>0.3201</v>
+      </c>
+      <c r="AZ124" t="n">
+        <v>0.26374</v>
+      </c>
+      <c r="BA124" t="n">
+        <v>0.31075</v>
+      </c>
+      <c r="BB124" t="n">
+        <v>0.29197</v>
+      </c>
+      <c r="BC124" t="n">
+        <v>0.26613</v>
+      </c>
+      <c r="BD124" t="n">
+        <v>0.46795</v>
+      </c>
+      <c r="BE124" t="n">
+        <v>0.99375</v>
+      </c>
+      <c r="BF124" t="n">
+        <v>0.8308300000000001</v>
+      </c>
+      <c r="BG124" t="n">
+        <v>0.31052</v>
+      </c>
+      <c r="BH124" t="n">
+        <v>0.40423</v>
+      </c>
+      <c r="BI124" t="n">
+        <v>0.37038</v>
+      </c>
+      <c r="BJ124" t="n">
+        <v>0.32228</v>
+      </c>
+      <c r="BK124" t="n">
+        <v>0.40648</v>
+      </c>
+      <c r="BL124" t="n">
+        <v>0.32756</v>
+      </c>
+      <c r="BM124" t="n">
+        <v>0.32922</v>
+      </c>
+      <c r="BN124" t="n">
+        <v>0.31954</v>
+      </c>
+      <c r="BO124" t="n">
+        <v>0.31892</v>
+      </c>
+      <c r="BP124" t="n">
+        <v>0.32007</v>
+      </c>
+      <c r="BQ124" t="n">
+        <v>0.30452</v>
+      </c>
+      <c r="BR124" t="n">
+        <v>0.3302</v>
+      </c>
+      <c r="BS124" t="n">
+        <v>0.28532</v>
+      </c>
+      <c r="BT124" t="n">
+        <v>0.31544</v>
+      </c>
+      <c r="BU124" t="n">
+        <v>0.29332</v>
+      </c>
+      <c r="BV124" t="n">
+        <v>0.29592</v>
+      </c>
+      <c r="BW124" t="n">
+        <v>0.30778</v>
+      </c>
+      <c r="BX124" t="n">
+        <v>0.29487</v>
+      </c>
+      <c r="BY124" t="n">
+        <v>0.3054</v>
+      </c>
+      <c r="BZ124" t="n">
+        <v>0.18028</v>
+      </c>
+      <c r="CA124" t="n">
+        <v>0.26271</v>
+      </c>
+      <c r="CB124" t="n">
+        <v>0.26238</v>
+      </c>
+      <c r="CC124" t="n">
+        <v>0.27711</v>
+      </c>
+      <c r="CD124" t="n">
+        <v>0.26188</v>
+      </c>
+      <c r="CE124" t="n">
+        <v>0.28131</v>
+      </c>
+      <c r="CF124" t="n">
+        <v>0.32457</v>
+      </c>
+      <c r="CG124" t="n">
+        <v>0.29213</v>
+      </c>
+      <c r="CH124" t="n">
+        <v>0.31051</v>
+      </c>
+      <c r="CI124" t="n">
+        <v>0.3084</v>
+      </c>
+      <c r="CJ124" t="n">
+        <v>0.30069</v>
+      </c>
+      <c r="CK124" t="n">
+        <v>0.29412</v>
+      </c>
+      <c r="CL124" t="n">
+        <v>0.29341</v>
+      </c>
+      <c r="CM124" t="n">
+        <v>0.30305</v>
+      </c>
+      <c r="CN124" t="n">
+        <v>0.30333</v>
+      </c>
+      <c r="CO124" t="n">
+        <v>0.30769</v>
+      </c>
+      <c r="CP124" t="n">
+        <v>0.30268</v>
+      </c>
+      <c r="CQ124" t="n">
+        <v>0.30475</v>
+      </c>
+      <c r="CR124" t="n">
+        <v>0.29073</v>
+      </c>
+      <c r="CS124" t="n">
+        <v>0.32373</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n">
+        <v>46146</v>
+      </c>
+      <c r="B125" t="n">
+        <v>0.32835</v>
+      </c>
+      <c r="C125" t="n">
+        <v>0.76264</v>
+      </c>
+      <c r="D125" t="n">
+        <v>0.30809</v>
+      </c>
+      <c r="E125" t="n">
+        <v>0.33048</v>
+      </c>
+      <c r="F125" t="n">
+        <v>0.31995</v>
+      </c>
+      <c r="G125" t="n">
+        <v>0.31691</v>
+      </c>
+      <c r="H125" t="n">
+        <v>0.3142799999999999</v>
+      </c>
+      <c r="I125" t="n">
+        <v>0.3046</v>
+      </c>
+      <c r="J125" t="n">
+        <v>0.30696</v>
+      </c>
+      <c r="K125" t="n">
+        <v>0.30923</v>
+      </c>
+      <c r="L125" t="n">
+        <v>0.30844</v>
+      </c>
+      <c r="M125" t="n">
+        <v>0.30741</v>
+      </c>
+      <c r="N125" t="n">
+        <v>0.30944</v>
+      </c>
+      <c r="O125" t="n">
+        <v>0.29355</v>
+      </c>
+      <c r="P125" t="n">
+        <v>0.29936</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>0.30315</v>
+      </c>
+      <c r="R125" t="n">
+        <v>0.30022</v>
+      </c>
+      <c r="S125" t="n">
+        <v>0.2964</v>
+      </c>
+      <c r="T125" t="n">
+        <v>0.2913</v>
+      </c>
+      <c r="U125" t="n">
+        <v>0.3058999999999999</v>
+      </c>
+      <c r="V125" t="n">
+        <v>0.2999</v>
+      </c>
+      <c r="W125" t="n">
+        <v>0.29751</v>
+      </c>
+      <c r="X125" t="n">
+        <v>0.29763</v>
+      </c>
+      <c r="Y125" t="n">
+        <v>0.29796</v>
+      </c>
+      <c r="Z125" t="n">
+        <v>0.29758</v>
+      </c>
+      <c r="AA125" t="n">
+        <v>0.29777</v>
+      </c>
+      <c r="AB125" t="n">
+        <v>0.298</v>
+      </c>
+      <c r="AC125" t="n">
+        <v>0.29295</v>
+      </c>
+      <c r="AD125" t="n">
+        <v>0.27362</v>
+      </c>
+      <c r="AE125" t="n">
+        <v>0.29209</v>
+      </c>
+      <c r="AF125" t="n">
+        <v>0.29626</v>
+      </c>
+      <c r="AG125" t="n">
+        <v>0.29087</v>
+      </c>
+      <c r="AH125" t="n">
+        <v>0.30561</v>
+      </c>
+      <c r="AI125" t="n">
+        <v>0.3076</v>
+      </c>
+      <c r="AJ125" t="n">
+        <v>0.30354</v>
+      </c>
+      <c r="AK125" t="n">
+        <v>0.30355</v>
+      </c>
+      <c r="AL125" t="n">
+        <v>0.29263</v>
+      </c>
+      <c r="AM125" t="n">
+        <v>0.31216</v>
+      </c>
+      <c r="AN125" t="n">
+        <v>0.41677</v>
+      </c>
+      <c r="AO125" t="n">
+        <v>0.32653</v>
+      </c>
+      <c r="AP125" t="n">
+        <v>0.30483</v>
+      </c>
+      <c r="AQ125" t="n">
+        <v>0.30418</v>
+      </c>
+      <c r="AR125" t="n">
+        <v>0.35771</v>
+      </c>
+      <c r="AS125" t="n">
+        <v>0.37972</v>
+      </c>
+      <c r="AT125" t="n">
+        <v>0.8842300000000001</v>
+      </c>
+      <c r="AU125" t="n">
+        <v>0.45267</v>
+      </c>
+      <c r="AV125" t="n">
+        <v>0.69117</v>
+      </c>
+      <c r="AW125" t="n">
+        <v>0.29101</v>
+      </c>
+      <c r="AX125" t="n">
+        <v>0.20174</v>
+      </c>
+      <c r="AY125" t="n">
+        <v>0.31138</v>
+      </c>
+      <c r="AZ125" t="n">
+        <v>0.29888</v>
+      </c>
+      <c r="BA125" t="n">
+        <v>0.32755</v>
+      </c>
+      <c r="BB125" t="n">
+        <v>0.28679</v>
+      </c>
+      <c r="BC125" t="n">
+        <v>0.31484</v>
+      </c>
+      <c r="BD125" t="n">
+        <v>0.31718</v>
+      </c>
+      <c r="BE125" t="n">
+        <v>0.7121799999999999</v>
+      </c>
+      <c r="BF125" t="n">
+        <v>0.77661</v>
+      </c>
+      <c r="BG125" t="n">
+        <v>0.6059099999999999</v>
+      </c>
+      <c r="BH125" t="n">
+        <v>0.5655</v>
+      </c>
+      <c r="BI125" t="n">
+        <v>0.64567</v>
+      </c>
+      <c r="BJ125" t="n">
+        <v>0.61424</v>
+      </c>
+      <c r="BK125" t="n">
+        <v>0.50208</v>
+      </c>
+      <c r="BL125" t="n">
+        <v>0.5994400000000001</v>
+      </c>
+      <c r="BM125" t="n">
+        <v>0.93259</v>
+      </c>
+      <c r="BN125" t="n">
+        <v>0.69599</v>
+      </c>
+      <c r="BO125" t="n">
+        <v>0.63889</v>
+      </c>
+      <c r="BP125" t="n">
+        <v>0.7116699999999999</v>
+      </c>
+      <c r="BQ125" t="n">
+        <v>0.69441</v>
+      </c>
+      <c r="BR125" t="n">
+        <v>0.29357</v>
+      </c>
+      <c r="BS125" t="n">
+        <v>0.31114</v>
+      </c>
+      <c r="BT125" t="n">
+        <v>0.26012</v>
+      </c>
+      <c r="BU125" t="n">
+        <v>0.30729</v>
+      </c>
+      <c r="BV125" t="n">
+        <v>0.29191</v>
+      </c>
+      <c r="BW125" t="n">
+        <v>0.30957</v>
+      </c>
+      <c r="BX125" t="n">
+        <v>0.30963</v>
+      </c>
+      <c r="BY125" t="n">
+        <v>0.28132</v>
+      </c>
+      <c r="BZ125" t="n">
+        <v>0.2981</v>
+      </c>
+      <c r="CA125" t="n">
+        <v>0.30444</v>
+      </c>
+      <c r="CB125" t="n">
+        <v>0.30213</v>
+      </c>
+      <c r="CC125" t="n">
+        <v>0.28514</v>
+      </c>
+      <c r="CD125" t="n">
+        <v>0.30748</v>
+      </c>
+      <c r="CE125" t="n">
+        <v>0.31275</v>
+      </c>
+      <c r="CF125" t="n">
+        <v>0.32243</v>
+      </c>
+      <c r="CG125" t="n">
+        <v>0.31941</v>
+      </c>
+      <c r="CH125" t="n">
+        <v>0.30674</v>
+      </c>
+      <c r="CI125" t="n">
+        <v>0.31999</v>
+      </c>
+      <c r="CJ125" t="n">
+        <v>0.29155</v>
+      </c>
+      <c r="CK125" t="n">
+        <v>0.43015</v>
+      </c>
+      <c r="CL125" t="n">
+        <v>0.33131</v>
+      </c>
+      <c r="CM125" t="n">
+        <v>0.58116</v>
+      </c>
+      <c r="CN125" t="n">
+        <v>0.2815299999999999</v>
+      </c>
+      <c r="CO125" t="n">
+        <v>0.30418</v>
+      </c>
+      <c r="CP125" t="n">
+        <v>0.43055</v>
+      </c>
+      <c r="CQ125" t="n">
+        <v>0.28875</v>
+      </c>
+      <c r="CR125" t="n">
+        <v>0.28533</v>
+      </c>
+      <c r="CS125" t="n">
+        <v>0.28576</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
+        <v>46147</v>
+      </c>
+      <c r="B126" t="n">
+        <v>0.46367</v>
+      </c>
+      <c r="C126" t="n">
+        <v>1.5637</v>
+      </c>
+      <c r="D126" t="n">
+        <v>1.20191</v>
+      </c>
+      <c r="E126" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="F126" t="n">
+        <v>1.12254</v>
+      </c>
+      <c r="G126" t="n">
+        <v>0.7960700000000001</v>
+      </c>
+      <c r="H126" t="n">
+        <v>1.02971</v>
+      </c>
+      <c r="I126" t="n">
+        <v>0.47677</v>
+      </c>
+      <c r="J126" t="n">
+        <v>0.46183</v>
+      </c>
+      <c r="K126" t="n">
+        <v>0.5680599999999999</v>
+      </c>
+      <c r="L126" t="n">
+        <v>0.59611</v>
+      </c>
+      <c r="M126" t="n">
+        <v>0.32291</v>
+      </c>
+      <c r="N126" t="n">
+        <v>0.35675</v>
+      </c>
+      <c r="O126" t="n">
+        <v>0.47349</v>
+      </c>
+      <c r="P126" t="n">
+        <v>0.39743</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>0.29421</v>
+      </c>
+      <c r="R126" t="n">
+        <v>0.29193</v>
+      </c>
+      <c r="S126" t="n">
+        <v>0.44197</v>
+      </c>
+      <c r="T126" t="n">
+        <v>0.48205</v>
+      </c>
+      <c r="U126" t="n">
+        <v>0.33761</v>
+      </c>
+      <c r="V126" t="n">
+        <v>0.31175</v>
+      </c>
+      <c r="W126" t="n">
+        <v>0.40003</v>
+      </c>
+      <c r="X126" t="n">
+        <v>0.32921</v>
+      </c>
+      <c r="Y126" t="n">
+        <v>0.33605</v>
+      </c>
+      <c r="Z126" t="n">
+        <v>0.43208</v>
+      </c>
+      <c r="AA126" t="n">
+        <v>0.33186</v>
+      </c>
+      <c r="AB126" t="n">
+        <v>0.33039</v>
+      </c>
+      <c r="AC126" t="n">
+        <v>0.44376</v>
+      </c>
+      <c r="AD126" t="n">
+        <v>0.38355</v>
+      </c>
+      <c r="AE126" t="n">
+        <v>0.31046</v>
+      </c>
+      <c r="AF126" t="n">
+        <v>0.2834</v>
+      </c>
+      <c r="AG126" t="n">
+        <v>0.44065</v>
+      </c>
+      <c r="AH126" t="n">
+        <v>0.33487</v>
+      </c>
+      <c r="AI126" t="n">
+        <v>0.6618200000000001</v>
+      </c>
+      <c r="AJ126" t="n">
+        <v>0.33331</v>
+      </c>
+      <c r="AK126" t="n">
+        <v>0.31648</v>
+      </c>
+      <c r="AL126" t="n">
+        <v>0.47938</v>
+      </c>
+      <c r="AM126" t="n">
+        <v>0.5009100000000001</v>
+      </c>
+      <c r="AN126" t="n">
+        <v>0.33255</v>
+      </c>
+      <c r="AO126" t="n">
+        <v>0.32945</v>
+      </c>
+      <c r="AP126" t="n">
+        <v>0.32158</v>
+      </c>
+      <c r="AQ126" t="n">
+        <v>0.32379</v>
+      </c>
+      <c r="AR126" t="n">
+        <v>0.61487</v>
+      </c>
+      <c r="AS126" t="n">
+        <v>0.35658</v>
+      </c>
+      <c r="AT126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU126" t="n">
+        <v>0.52132</v>
+      </c>
+      <c r="AV126" t="n">
+        <v>0.4377799999999999</v>
+      </c>
+      <c r="AW126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX126" t="n">
+        <v>0.25278</v>
+      </c>
+      <c r="AY126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ126" t="n">
+        <v>0.29606</v>
+      </c>
+      <c r="BA126" t="n">
+        <v>0.14643</v>
+      </c>
+      <c r="BB126" t="n">
+        <v>0.26288</v>
+      </c>
+      <c r="BC126" t="n">
+        <v>0.27673</v>
+      </c>
+      <c r="BD126" t="n">
+        <v>-0.02789</v>
+      </c>
+      <c r="BE126" t="n">
+        <v>0.33468</v>
+      </c>
+      <c r="BF126" t="n">
+        <v>0.30069</v>
+      </c>
+      <c r="BG126" t="n">
+        <v>0.32964</v>
+      </c>
+      <c r="BH126" t="n">
+        <v>0.45055</v>
+      </c>
+      <c r="BI126" t="n">
+        <v>0.29951</v>
+      </c>
+      <c r="BJ126" t="n">
+        <v>0.28553</v>
+      </c>
+      <c r="BK126" t="n">
+        <v>0.49608</v>
+      </c>
+      <c r="BL126" t="n">
+        <v>0.46069</v>
+      </c>
+      <c r="BM126" t="n">
+        <v>0.35856</v>
+      </c>
+      <c r="BN126" t="n">
+        <v>0.46666</v>
+      </c>
+      <c r="BO126" t="n">
+        <v>0.35778</v>
+      </c>
+      <c r="BP126" t="n">
+        <v>0.34838</v>
+      </c>
+      <c r="BQ126" t="n">
+        <v>0.5904400000000001</v>
+      </c>
+      <c r="BR126" t="n">
+        <v>0.3305</v>
+      </c>
+      <c r="BS126" t="n">
+        <v>0.5314</v>
+      </c>
+      <c r="BT126" t="n">
+        <v>0.37623</v>
+      </c>
+      <c r="BU126" t="n">
+        <v>0.3369</v>
+      </c>
+      <c r="BV126" t="n">
+        <v>0.33291</v>
+      </c>
+      <c r="BW126" t="n">
+        <v>0.32917</v>
+      </c>
+      <c r="BX126" t="n">
+        <v>0.33469</v>
+      </c>
+      <c r="BY126" t="n">
+        <v>0.31669</v>
+      </c>
+      <c r="BZ126" t="n">
+        <v>0.27696</v>
+      </c>
+      <c r="CA126" t="n">
+        <v>0.33883</v>
+      </c>
+      <c r="CB126" t="n">
+        <v>0.31682</v>
+      </c>
+      <c r="CC126" t="n">
+        <v>0.28647</v>
+      </c>
+      <c r="CD126" t="n">
+        <v>0.32441</v>
+      </c>
+      <c r="CE126" t="n">
+        <v>0.31165</v>
+      </c>
+      <c r="CF126" t="n">
+        <v>0.32315</v>
+      </c>
+      <c r="CG126" t="n">
+        <v>0.42568</v>
+      </c>
+      <c r="CH126" t="n">
+        <v>0.30608</v>
+      </c>
+      <c r="CI126" t="n">
+        <v>0.46327</v>
+      </c>
+      <c r="CJ126" t="n">
+        <v>0.30698</v>
+      </c>
+      <c r="CK126" t="n">
+        <v>0.3112200000000001</v>
+      </c>
+      <c r="CL126" t="n">
+        <v>0.30891</v>
+      </c>
+      <c r="CM126" t="n">
+        <v>0.33044</v>
+      </c>
+      <c r="CN126" t="n">
+        <v>0.30011</v>
+      </c>
+      <c r="CO126" t="n">
+        <v>0.3088399999999999</v>
+      </c>
+      <c r="CP126" t="n">
+        <v>0.29523</v>
+      </c>
+      <c r="CQ126" t="n">
+        <v>0.27743</v>
+      </c>
+      <c r="CR126" t="n">
+        <v>0.29254</v>
+      </c>
+      <c r="CS126" t="n">
+        <v>0.26531</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
+        <v>46148</v>
+      </c>
+      <c r="B127" t="n">
+        <v>0.3183</v>
+      </c>
+      <c r="C127" t="n">
+        <v>0.27841</v>
+      </c>
+      <c r="D127" t="n">
+        <v>0.26226</v>
+      </c>
+      <c r="E127" t="n">
+        <v>0.258</v>
+      </c>
+      <c r="F127" t="n">
+        <v>0.16839</v>
+      </c>
+      <c r="G127" t="n">
+        <v>0.30503</v>
+      </c>
+      <c r="H127" t="n">
+        <v>0.19193</v>
+      </c>
+      <c r="I127" t="n">
+        <v>0.1881</v>
+      </c>
+      <c r="J127" t="n">
+        <v>0.18555</v>
+      </c>
+      <c r="K127" t="n">
+        <v>0.18532</v>
+      </c>
+      <c r="L127" t="n">
+        <v>0.15708</v>
+      </c>
+      <c r="M127" t="n">
+        <v>0.23875</v>
+      </c>
+      <c r="N127" t="n">
+        <v>0.26017</v>
+      </c>
+      <c r="O127" t="n">
+        <v>0.25785</v>
+      </c>
+      <c r="P127" t="n">
+        <v>0.29821</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>0.29417</v>
+      </c>
+      <c r="R127" t="n">
+        <v>0.33612</v>
+      </c>
+      <c r="S127" t="n">
+        <v>0.32421</v>
+      </c>
+      <c r="T127" t="n">
+        <v>0.49749</v>
+      </c>
+      <c r="U127" t="n">
+        <v>0.52239</v>
+      </c>
+      <c r="V127" t="n">
+        <v>0.2895</v>
+      </c>
+      <c r="W127" t="n">
+        <v>-0.03521</v>
+      </c>
+      <c r="X127" t="n">
+        <v>0.3979</v>
+      </c>
+      <c r="Y127" t="n">
+        <v>0.1887</v>
+      </c>
+      <c r="Z127" t="n">
+        <v>-0.03844</v>
+      </c>
+      <c r="AA127" t="n">
+        <v>0.36894</v>
+      </c>
+      <c r="AB127" t="n">
+        <v>0.35557</v>
+      </c>
+      <c r="AC127" t="n">
+        <v>0.18577</v>
+      </c>
+      <c r="AD127" t="n">
+        <v>0.2745</v>
+      </c>
+      <c r="AE127" t="n">
+        <v>0.43381</v>
+      </c>
+      <c r="AF127" t="n">
+        <v>0.43112</v>
+      </c>
+      <c r="AG127" t="n">
+        <v>0.27627</v>
+      </c>
+      <c r="AH127" t="n">
+        <v>0.16301</v>
+      </c>
+      <c r="AI127" t="n">
+        <v>0.32603</v>
+      </c>
+      <c r="AJ127" t="n">
+        <v>0.2942</v>
+      </c>
+      <c r="AK127" t="n">
+        <v>0.30837</v>
+      </c>
+      <c r="AL127" t="n">
+        <v>0.29777</v>
+      </c>
+      <c r="AM127" t="n">
+        <v>0.2071</v>
+      </c>
+      <c r="AN127" t="n">
+        <v>0.26616</v>
+      </c>
+      <c r="AO127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP127" t="n">
+        <v>0.26219</v>
+      </c>
+      <c r="AQ127" t="n">
+        <v>0.27279</v>
+      </c>
+      <c r="AR127" t="n">
+        <v>0.29043</v>
+      </c>
+      <c r="AS127" t="n">
+        <v>0.27785</v>
+      </c>
+      <c r="AT127" t="n">
+        <v>0.29036</v>
+      </c>
+      <c r="AU127" t="n">
+        <v>0.28254</v>
+      </c>
+      <c r="AV127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX127" t="n">
+        <v>0.26786</v>
+      </c>
+      <c r="AY127" t="n">
+        <v>0.26983</v>
+      </c>
+      <c r="AZ127" t="n">
+        <v>0.27806</v>
+      </c>
+      <c r="BA127" t="n">
+        <v>0.27146</v>
+      </c>
+      <c r="BB127" t="n">
+        <v>0.28292</v>
+      </c>
+      <c r="BC127" t="n">
+        <v>0.28049</v>
+      </c>
+      <c r="BD127" t="n">
+        <v>0.26561</v>
+      </c>
+      <c r="BE127" t="n">
+        <v>0.276</v>
+      </c>
+      <c r="BF127" t="n">
+        <v>0.30871</v>
+      </c>
+      <c r="BG127" t="n">
+        <v>0.27165</v>
+      </c>
+      <c r="BH127" t="n">
+        <v>0.29855</v>
+      </c>
+      <c r="BI127" t="n">
+        <v>0.33083</v>
+      </c>
+      <c r="BJ127" t="n">
+        <v>0.29016</v>
+      </c>
+      <c r="BK127" t="n">
+        <v>0.30574</v>
+      </c>
+      <c r="BL127" t="n">
+        <v>0.30262</v>
+      </c>
+      <c r="BM127" t="n">
+        <v>0.31055</v>
+      </c>
+      <c r="BN127" t="n">
+        <v>0.29793</v>
+      </c>
+      <c r="BO127" t="n">
+        <v>0.30574</v>
+      </c>
+      <c r="BP127" t="n">
+        <v>0.29966</v>
+      </c>
+      <c r="BQ127" t="n">
+        <v>0.29599</v>
+      </c>
+      <c r="BR127" t="n">
+        <v>0.31832</v>
+      </c>
+      <c r="BS127" t="n">
+        <v>0.302</v>
+      </c>
+      <c r="BT127" t="n">
+        <v>0.2816</v>
+      </c>
+      <c r="BU127" t="n">
+        <v>0.28265</v>
+      </c>
+      <c r="BV127" t="n">
+        <v>0.2993</v>
+      </c>
+      <c r="BW127" t="n">
+        <v>0.30377</v>
+      </c>
+      <c r="BX127" t="n">
+        <v>0.30516</v>
+      </c>
+      <c r="BY127" t="n">
+        <v>0.30661</v>
+      </c>
+      <c r="BZ127" t="n">
+        <v>0.29277</v>
+      </c>
+      <c r="CA127" t="n">
+        <v>0.31599</v>
+      </c>
+      <c r="CB127" t="n">
+        <v>0.32077</v>
+      </c>
+      <c r="CC127" t="n">
+        <v>0.31719</v>
+      </c>
+      <c r="CD127" t="n">
+        <v>0.31415</v>
+      </c>
+      <c r="CE127" t="n">
+        <v>0.317</v>
+      </c>
+      <c r="CF127" t="n">
+        <v>0.31215</v>
+      </c>
+      <c r="CG127" t="n">
+        <v>0.30893</v>
+      </c>
+      <c r="CH127" t="n">
+        <v>0.31785</v>
+      </c>
+      <c r="CI127" t="n">
+        <v>0.31538</v>
+      </c>
+      <c r="CJ127" t="n">
+        <v>0.31168</v>
+      </c>
+      <c r="CK127" t="n">
+        <v>0.38982</v>
+      </c>
+      <c r="CL127" t="n">
+        <v>0.46623</v>
+      </c>
+      <c r="CM127" t="n">
+        <v>0.44499</v>
+      </c>
+      <c r="CN127" t="n">
+        <v>0.41283</v>
+      </c>
+      <c r="CO127" t="n">
+        <v>0.40153</v>
+      </c>
+      <c r="CP127" t="n">
+        <v>0.28479</v>
+      </c>
+      <c r="CQ127" t="n">
+        <v>0.28712</v>
+      </c>
+      <c r="CR127" t="n">
+        <v>0.24984</v>
+      </c>
+      <c r="CS127" t="n">
+        <v>0.28172</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
+        <v>46149</v>
+      </c>
+      <c r="B128" t="n">
+        <v>0.28976</v>
+      </c>
+      <c r="C128" t="n">
+        <v>0.30874</v>
+      </c>
+      <c r="D128" t="n">
+        <v>0.3446</v>
+      </c>
+      <c r="E128" t="n">
+        <v>0.30611</v>
+      </c>
+      <c r="F128" t="n">
+        <v>0.30498</v>
+      </c>
+      <c r="G128" t="n">
+        <v>0.30489</v>
+      </c>
+      <c r="H128" t="n">
+        <v>0.29916</v>
+      </c>
+      <c r="I128" t="n">
+        <v>0.30136</v>
+      </c>
+      <c r="J128" t="n">
+        <v>0.30217</v>
+      </c>
+      <c r="K128" t="n">
+        <v>0.30303</v>
+      </c>
+      <c r="L128" t="n">
+        <v>0.33753</v>
+      </c>
+      <c r="M128" t="n">
+        <v>0.33038</v>
+      </c>
+      <c r="N128" t="n">
+        <v>0.30498</v>
+      </c>
+      <c r="O128" t="n">
+        <v>0.30301</v>
+      </c>
+      <c r="P128" t="n">
+        <v>0.30478</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>0.30356</v>
+      </c>
+      <c r="R128" t="n">
+        <v>0.29849</v>
+      </c>
+      <c r="S128" t="n">
+        <v>0.29627</v>
+      </c>
+      <c r="T128" t="n">
+        <v>0.29592</v>
+      </c>
+      <c r="U128" t="n">
+        <v>0.29981</v>
+      </c>
+      <c r="V128" t="n">
+        <v>0.29563</v>
+      </c>
+      <c r="W128" t="n">
+        <v>0.2945</v>
+      </c>
+      <c r="X128" t="n">
+        <v>0.29602</v>
+      </c>
+      <c r="Y128" t="n">
+        <v>0.2945</v>
+      </c>
+      <c r="Z128" t="n">
+        <v>0.30072</v>
+      </c>
+      <c r="AA128" t="n">
+        <v>0.30165</v>
+      </c>
+      <c r="AB128" t="n">
+        <v>0.29616</v>
+      </c>
+      <c r="AC128" t="n">
+        <v>0.30133</v>
+      </c>
+      <c r="AD128" t="n">
+        <v>0.30039</v>
+      </c>
+      <c r="AE128" t="n">
+        <v>0.30136</v>
+      </c>
+      <c r="AF128" t="n">
+        <v>0.29126</v>
+      </c>
+      <c r="AG128" t="n">
+        <v>0.30156</v>
+      </c>
+      <c r="AH128" t="n">
+        <v>0.29487</v>
+      </c>
+      <c r="AI128" t="n">
+        <v>0.31542</v>
+      </c>
+      <c r="AJ128" t="n">
+        <v>0.30817</v>
+      </c>
+      <c r="AK128" t="n">
+        <v>0.33079</v>
+      </c>
+      <c r="AL128" t="n">
+        <v>0.28234</v>
+      </c>
+      <c r="AM128" t="n">
+        <v>0.30503</v>
+      </c>
+      <c r="AN128" t="n">
+        <v>0.3175</v>
+      </c>
+      <c r="AO128" t="n">
+        <v>0.30318</v>
+      </c>
+      <c r="AP128" t="n">
+        <v>0.28499</v>
+      </c>
+      <c r="AQ128" t="n">
+        <v>0.30999</v>
+      </c>
+      <c r="AR128" t="n">
+        <v>0.2837</v>
+      </c>
+      <c r="AS128" t="n">
+        <v>0.41959</v>
+      </c>
+      <c r="AT128" t="n">
+        <v>0.3018</v>
+      </c>
+      <c r="AU128" t="n">
+        <v>0.28689</v>
+      </c>
+      <c r="AV128" t="n">
+        <v>0.29749</v>
+      </c>
+      <c r="AW128" t="n">
+        <v>0.29224</v>
+      </c>
+      <c r="AX128" t="n">
+        <v>0.27954</v>
+      </c>
+      <c r="AY128" t="n">
+        <v>0.2999</v>
+      </c>
+      <c r="AZ128" t="n">
+        <v>0.2987</v>
+      </c>
+      <c r="BA128" t="n">
+        <v>0.31386</v>
+      </c>
+      <c r="BB128" t="n">
+        <v>0.31521</v>
+      </c>
+      <c r="BC128" t="n">
+        <v>0.29993</v>
+      </c>
+      <c r="BD128" t="n">
+        <v>0.30116</v>
+      </c>
+      <c r="BE128" t="n">
+        <v>0.30777</v>
+      </c>
+      <c r="BF128" t="n">
+        <v>0.29445</v>
+      </c>
+      <c r="BG128" t="n">
+        <v>0.31221</v>
+      </c>
+      <c r="BH128" t="n">
+        <v>0.24799</v>
+      </c>
+      <c r="BI128" t="n">
+        <v>0.29467</v>
+      </c>
+      <c r="BJ128" t="n">
+        <v>0.28724</v>
+      </c>
+      <c r="BK128" t="n">
+        <v>0.30426</v>
+      </c>
+      <c r="BL128" t="n">
+        <v>0.28938</v>
+      </c>
+      <c r="BM128" t="n">
+        <v>0.28849</v>
+      </c>
+      <c r="BN128" t="n">
+        <v>0.29443</v>
+      </c>
+      <c r="BO128" t="n">
+        <v>0.32428</v>
+      </c>
+      <c r="BP128" t="n">
+        <v>0.32473</v>
+      </c>
+      <c r="BQ128" t="n">
+        <v>0.31682</v>
+      </c>
+      <c r="BR128" t="n">
+        <v>0.30901</v>
+      </c>
+      <c r="BS128" t="n">
+        <v>0.32948</v>
+      </c>
+      <c r="BT128" t="n">
+        <v>0.3724</v>
+      </c>
+      <c r="BU128" t="n">
+        <v>0.33475</v>
+      </c>
+      <c r="BV128" t="n">
+        <v>0.32353</v>
+      </c>
+      <c r="BW128" t="n">
+        <v>0.3161600000000001</v>
+      </c>
+      <c r="BX128" t="n">
+        <v>0.31538</v>
+      </c>
+      <c r="BY128" t="n">
+        <v>0.356</v>
+      </c>
+      <c r="BZ128" t="n">
+        <v>0.31758</v>
+      </c>
+      <c r="CA128" t="n">
+        <v>0.36294</v>
+      </c>
+      <c r="CB128" t="n">
+        <v>0.42427</v>
+      </c>
+      <c r="CC128" t="n">
+        <v>0.28959</v>
+      </c>
+      <c r="CD128" t="n">
+        <v>0.35255</v>
+      </c>
+      <c r="CE128" t="n">
+        <v>0.33141</v>
+      </c>
+      <c r="CF128" t="n">
+        <v>0.32098</v>
+      </c>
+      <c r="CG128" t="n">
+        <v>0.31311</v>
+      </c>
+      <c r="CH128" t="n">
+        <v>0.3098</v>
+      </c>
+      <c r="CI128" t="n">
+        <v>0.35067</v>
+      </c>
+      <c r="CJ128" t="n">
+        <v>0.31424</v>
+      </c>
+      <c r="CK128" t="n">
+        <v>0.31391</v>
+      </c>
+      <c r="CL128" t="n">
+        <v>0.32511</v>
+      </c>
+      <c r="CM128" t="n">
+        <v>0.3127799999999999</v>
+      </c>
+      <c r="CN128" t="n">
+        <v>0.31961</v>
+      </c>
+      <c r="CO128" t="n">
+        <v>0.2887</v>
+      </c>
+      <c r="CP128" t="n">
+        <v>0.30641</v>
+      </c>
+      <c r="CQ128" t="n">
+        <v>0.30636</v>
+      </c>
+      <c r="CR128" t="n">
+        <v>0.30264</v>
+      </c>
+      <c r="CS128" t="n">
+        <v>0.30304</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="B129" t="n">
+        <v>0.31967</v>
+      </c>
+      <c r="C129" t="n">
+        <v>0.30844</v>
+      </c>
+      <c r="D129" t="n">
+        <v>0.29953</v>
+      </c>
+      <c r="E129" t="n">
+        <v>0.33501</v>
+      </c>
+      <c r="F129" t="n">
+        <v>0.31451</v>
+      </c>
+      <c r="G129" t="n">
+        <v>0.31185</v>
+      </c>
+      <c r="H129" t="n">
+        <v>0.30434</v>
+      </c>
+      <c r="I129" t="n">
+        <v>0.28826</v>
+      </c>
+      <c r="J129" t="n">
+        <v>0.29335</v>
+      </c>
+      <c r="K129" t="n">
+        <v>0.28703</v>
+      </c>
+      <c r="L129" t="n">
+        <v>0.29252</v>
+      </c>
+      <c r="M129" t="n">
+        <v>0.29401</v>
+      </c>
+      <c r="N129" t="n">
+        <v>0.29782</v>
+      </c>
+      <c r="O129" t="n">
+        <v>0.29974</v>
+      </c>
+      <c r="P129" t="n">
+        <v>0.317</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>0.29461</v>
+      </c>
+      <c r="R129" t="n">
+        <v>0.29574</v>
+      </c>
+      <c r="S129" t="n">
+        <v>0.29558</v>
+      </c>
+      <c r="T129" t="n">
+        <v>0.31321</v>
+      </c>
+      <c r="U129" t="n">
+        <v>0.30867</v>
+      </c>
+      <c r="V129" t="n">
+        <v>0.29365</v>
+      </c>
+      <c r="W129" t="n">
+        <v>0.30999</v>
+      </c>
+      <c r="X129" t="n">
+        <v>0.30549</v>
+      </c>
+      <c r="Y129" t="n">
+        <v>0.29466</v>
+      </c>
+      <c r="Z129" t="n">
+        <v>0.29632</v>
+      </c>
+      <c r="AA129" t="n">
+        <v>0.29619</v>
+      </c>
+      <c r="AB129" t="n">
+        <v>0.28995</v>
+      </c>
+      <c r="AC129" t="n">
+        <v>0.3422</v>
+      </c>
+      <c r="AD129" t="n">
+        <v>0.30957</v>
+      </c>
+      <c r="AE129" t="n">
+        <v>0.31381</v>
+      </c>
+      <c r="AF129" t="n">
+        <v>0.30896</v>
+      </c>
+      <c r="AG129" t="n">
+        <v>0.29581</v>
+      </c>
+      <c r="AH129" t="n">
+        <v>0.30454</v>
+      </c>
+      <c r="AI129" t="n">
+        <v>0.33452</v>
+      </c>
+      <c r="AJ129" t="n">
+        <v>0.39196</v>
+      </c>
+      <c r="AK129" t="n">
+        <v>0.9700299999999999</v>
+      </c>
+      <c r="AL129" t="n">
+        <v>0.40602</v>
+      </c>
+      <c r="AM129" t="n">
+        <v>0.61553</v>
+      </c>
+      <c r="AN129" t="n">
+        <v>0.38223</v>
+      </c>
+      <c r="AO129" t="n">
+        <v>0.469</v>
+      </c>
+      <c r="AP129" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="AQ129" t="n">
+        <v>0.37521</v>
+      </c>
+      <c r="AR129" t="n">
+        <v>0.42277</v>
+      </c>
+      <c r="AS129" t="n">
+        <v>0.47561</v>
+      </c>
+      <c r="AT129" t="n">
+        <v>0.37956</v>
+      </c>
+      <c r="AU129" t="n">
+        <v>0.41724</v>
+      </c>
+      <c r="AV129" t="n">
+        <v>0.3912</v>
+      </c>
+      <c r="AW129" t="n">
+        <v>0.5237000000000001</v>
+      </c>
+      <c r="AX129" t="n">
+        <v>0.27735</v>
+      </c>
+      <c r="AY129" t="n">
+        <v>0.32345</v>
+      </c>
+      <c r="AZ129" t="n">
+        <v>0.30827</v>
+      </c>
+      <c r="BA129" t="n">
+        <v>0.42137</v>
+      </c>
+      <c r="BB129" t="n">
+        <v>0.28277</v>
+      </c>
+      <c r="BC129" t="n">
+        <v>0.3538</v>
+      </c>
+      <c r="BD129" t="n">
+        <v>0.40396</v>
+      </c>
+      <c r="BE129" t="n">
+        <v>0.68729</v>
+      </c>
+      <c r="BF129" t="n">
+        <v>0.52562</v>
+      </c>
+      <c r="BG129" t="n">
+        <v>0.43435</v>
+      </c>
+      <c r="BH129" t="n">
+        <v>0.42643</v>
+      </c>
+      <c r="BI129" t="n">
+        <v>0.4063</v>
+      </c>
+      <c r="BJ129" t="n">
+        <v>0.39169</v>
+      </c>
+      <c r="BK129" t="n">
+        <v>0.51247</v>
+      </c>
+      <c r="BL129" t="n">
+        <v>0.40624</v>
+      </c>
+      <c r="BM129" t="n">
+        <v>0.4128500000000001</v>
+      </c>
+      <c r="BN129" t="n">
+        <v>0.41732</v>
+      </c>
+      <c r="BO129" t="n">
+        <v>0.37351</v>
+      </c>
+      <c r="BP129" t="n">
+        <v>0.42098</v>
+      </c>
+      <c r="BQ129" t="n">
+        <v>0.35779</v>
+      </c>
+      <c r="BR129" t="n">
+        <v>0.43543</v>
+      </c>
+      <c r="BS129" t="n">
+        <v>0.40314</v>
+      </c>
+      <c r="BT129" t="n">
+        <v>0.33391</v>
+      </c>
+      <c r="BU129" t="n">
+        <v>0.47075</v>
+      </c>
+      <c r="BV129" t="n">
+        <v>0.36406</v>
+      </c>
+      <c r="BW129" t="n">
+        <v>0.34605</v>
+      </c>
+      <c r="BX129" t="n">
+        <v>0.65391</v>
+      </c>
+      <c r="BY129" t="n">
+        <v>0.43779</v>
+      </c>
+      <c r="BZ129" t="n">
+        <v>0.41573</v>
+      </c>
+      <c r="CA129" t="n">
+        <v>0.42119</v>
+      </c>
+      <c r="CB129" t="n">
+        <v>0.47242</v>
+      </c>
+      <c r="CC129" t="n">
+        <v>0.70989</v>
+      </c>
+      <c r="CD129" t="n">
+        <v>0.38361</v>
+      </c>
+      <c r="CE129" t="n">
+        <v>0.29474</v>
+      </c>
+      <c r="CF129" t="n">
+        <v>0.34764</v>
+      </c>
+      <c r="CG129" t="n">
+        <v>0.35968</v>
+      </c>
+      <c r="CH129" t="n">
+        <v>0.34468</v>
+      </c>
+      <c r="CI129" t="n">
+        <v>0.47532</v>
+      </c>
+      <c r="CJ129" t="n">
+        <v>0.2489</v>
+      </c>
+      <c r="CK129" t="n">
+        <v>0.32584</v>
+      </c>
+      <c r="CL129" t="n">
+        <v>0.39724</v>
+      </c>
+      <c r="CM129" t="n">
+        <v>0.33312</v>
+      </c>
+      <c r="CN129" t="n">
+        <v>0.32015</v>
+      </c>
+      <c r="CO129" t="n">
+        <v>0.31116</v>
+      </c>
+      <c r="CP129" t="n">
+        <v>0.29576</v>
+      </c>
+      <c r="CQ129" t="n">
+        <v>0.28531</v>
+      </c>
+      <c r="CR129" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CS129" t="n">
+        <v>0.23541</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="n">
+        <v>46151</v>
+      </c>
+      <c r="B130" t="n">
+        <v>0.32003</v>
+      </c>
+      <c r="C130" t="n">
+        <v>0.32171</v>
+      </c>
+      <c r="D130" t="n">
+        <v>0.30026</v>
+      </c>
+      <c r="E130" t="n">
+        <v>0.38456</v>
+      </c>
+      <c r="F130" t="n">
+        <v>0.29179</v>
+      </c>
+      <c r="G130" t="n">
+        <v>0.28062</v>
+      </c>
+      <c r="H130" t="n">
+        <v>0.28177</v>
+      </c>
+      <c r="I130" t="n">
+        <v>0.28151</v>
+      </c>
+      <c r="J130" t="n">
+        <v>0.19951</v>
+      </c>
+      <c r="K130" t="n">
+        <v>0.19171</v>
+      </c>
+      <c r="L130" t="n">
+        <v>0.27846</v>
+      </c>
+      <c r="M130" t="n">
+        <v>0.27746</v>
+      </c>
+      <c r="N130" t="n">
+        <v>0.27472</v>
+      </c>
+      <c r="O130" t="n">
+        <v>0.27819</v>
+      </c>
+      <c r="P130" t="n">
+        <v>0.27828</v>
+      </c>
+      <c r="Q130" t="n">
+        <v>0.27432</v>
+      </c>
+      <c r="R130" t="n">
+        <v>0.19352</v>
+      </c>
+      <c r="S130" t="n">
+        <v>0.29548</v>
+      </c>
+      <c r="T130" t="n">
+        <v>0.19087</v>
+      </c>
+      <c r="U130" t="n">
+        <v>0.15476</v>
+      </c>
+      <c r="V130" t="n">
+        <v>0.23572</v>
+      </c>
+      <c r="W130" t="n">
+        <v>0.29022</v>
+      </c>
+      <c r="X130" t="n">
+        <v>0.29339</v>
+      </c>
+      <c r="Y130" t="n">
+        <v>0.26258</v>
+      </c>
+      <c r="Z130" t="n">
+        <v>0.1906</v>
+      </c>
+      <c r="AA130" t="n">
+        <v>0.19631</v>
+      </c>
+      <c r="AB130" t="n">
+        <v>0.31054</v>
+      </c>
+      <c r="AC130" t="n">
+        <v>0.20313</v>
+      </c>
+      <c r="AD130" t="n">
+        <v>0.16785</v>
+      </c>
+      <c r="AE130" t="n">
+        <v>0.15922</v>
+      </c>
+      <c r="AF130" t="n">
+        <v>0.23832</v>
+      </c>
+      <c r="AG130" t="n">
+        <v>0.2531</v>
+      </c>
+      <c r="AH130" t="n">
+        <v>0.31361</v>
+      </c>
+      <c r="AI130" t="n">
+        <v>0.32606</v>
+      </c>
+      <c r="AJ130" t="n">
+        <v>0.3722</v>
+      </c>
+      <c r="AK130" t="n">
+        <v>0.41324</v>
+      </c>
+      <c r="AL130" t="n">
+        <v>0.32385</v>
+      </c>
+      <c r="AM130" t="n">
+        <v>0.38005</v>
+      </c>
+      <c r="AN130" t="n">
+        <v>0.32534</v>
+      </c>
+      <c r="AO130" t="n">
+        <v>0.32639</v>
+      </c>
+      <c r="AP130" t="n">
+        <v>0.32634</v>
+      </c>
+      <c r="AQ130" t="n">
+        <v>0.32543</v>
+      </c>
+      <c r="AR130" t="n">
+        <v>0.3248</v>
+      </c>
+      <c r="AS130" t="n">
+        <v>0.30876</v>
+      </c>
+      <c r="AT130" t="n">
+        <v>0.31928</v>
+      </c>
+      <c r="AU130" t="n">
+        <v>0.328</v>
+      </c>
+      <c r="AV130" t="n">
+        <v>0.30028</v>
+      </c>
+      <c r="AW130" t="n">
+        <v>0.3224</v>
+      </c>
+      <c r="AX130" t="n">
+        <v>0.26418</v>
+      </c>
+      <c r="AY130" t="n">
+        <v>0.30376</v>
+      </c>
+      <c r="AZ130" t="n">
+        <v>0.29651</v>
+      </c>
+      <c r="BA130" t="n">
+        <v>0.29699</v>
+      </c>
+      <c r="BB130" t="n">
+        <v>0.30431</v>
+      </c>
+      <c r="BC130" t="n">
+        <v>0.30954</v>
+      </c>
+      <c r="BD130" t="n">
+        <v>0.32023</v>
+      </c>
+      <c r="BE130" t="n">
+        <v>0.32173</v>
+      </c>
+      <c r="BF130" t="n">
+        <v>0.3227</v>
+      </c>
+      <c r="BG130" t="n">
+        <v>0.29796</v>
+      </c>
+      <c r="BH130" t="n">
+        <v>0.30246</v>
+      </c>
+      <c r="BI130" t="n">
+        <v>0.31951</v>
+      </c>
+      <c r="BJ130" t="n">
+        <v>0.32044</v>
+      </c>
+      <c r="BK130" t="n">
+        <v>0.3671</v>
+      </c>
+      <c r="BL130" t="n">
+        <v>0.32415</v>
+      </c>
+      <c r="BM130" t="n">
+        <v>0.41939</v>
+      </c>
+      <c r="BN130" t="n">
+        <v>0.43436</v>
+      </c>
+      <c r="BO130" t="n">
+        <v>0.34278</v>
+      </c>
+      <c r="BP130" t="n">
+        <v>0.33601</v>
+      </c>
+      <c r="BQ130" t="n">
+        <v>0.32711</v>
+      </c>
+      <c r="BR130" t="n">
+        <v>0.32219</v>
+      </c>
+      <c r="BS130" t="n">
+        <v>0.33984</v>
+      </c>
+      <c r="BT130" t="n">
+        <v>0.3195</v>
+      </c>
+      <c r="BU130" t="n">
+        <v>0.31891</v>
+      </c>
+      <c r="BV130" t="n">
+        <v>0.30001</v>
+      </c>
+      <c r="BW130" t="n">
+        <v>0.26535</v>
+      </c>
+      <c r="BX130" t="n">
+        <v>0.2871</v>
+      </c>
+      <c r="BY130" t="n">
+        <v>0.28164</v>
+      </c>
+      <c r="BZ130" t="n">
+        <v>0.3164</v>
+      </c>
+      <c r="CA130" t="n">
+        <v>0.29435</v>
+      </c>
+      <c r="CB130" t="n">
+        <v>0.33675</v>
+      </c>
+      <c r="CC130" t="n">
+        <v>0.32866</v>
+      </c>
+      <c r="CD130" t="n">
+        <v>0.27435</v>
+      </c>
+      <c r="CE130" t="n">
+        <v>0.32985</v>
+      </c>
+      <c r="CF130" t="n">
+        <v>0.28616</v>
+      </c>
+      <c r="CG130" t="n">
+        <v>0.33126</v>
+      </c>
+      <c r="CH130" t="n">
+        <v>0.31371</v>
+      </c>
+      <c r="CI130" t="n">
+        <v>0.28971</v>
+      </c>
+      <c r="CJ130" t="n">
+        <v>0.35286</v>
+      </c>
+      <c r="CK130" t="n">
+        <v>0.25247</v>
+      </c>
+      <c r="CL130" t="n">
+        <v>0.34469</v>
+      </c>
+      <c r="CM130" t="n">
+        <v>0.28013</v>
+      </c>
+      <c r="CN130" t="n">
+        <v>0.34744</v>
+      </c>
+      <c r="CO130" t="n">
+        <v>0.31179</v>
+      </c>
+      <c r="CP130" t="n">
+        <v>0.24078</v>
+      </c>
+      <c r="CQ130" t="n">
+        <v>0.32137</v>
+      </c>
+      <c r="CR130" t="n">
+        <v>0.23505</v>
+      </c>
+      <c r="CS130" t="n">
+        <v>0.32097</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="n">
+        <v>46152</v>
+      </c>
+      <c r="B131" t="n">
+        <v>0.29274</v>
+      </c>
+      <c r="C131" t="n">
+        <v>0.32062</v>
+      </c>
+      <c r="D131" t="n">
+        <v>0.31961</v>
+      </c>
+      <c r="E131" t="n">
+        <v>0.32064</v>
+      </c>
+      <c r="F131" t="n">
+        <v>0.32158</v>
+      </c>
+      <c r="G131" t="n">
+        <v>0.32106</v>
+      </c>
+      <c r="H131" t="n">
+        <v>0.32026</v>
+      </c>
+      <c r="I131" t="n">
+        <v>0.28111</v>
+      </c>
+      <c r="J131" t="n">
+        <v>0.31962</v>
+      </c>
+      <c r="K131" t="n">
+        <v>0.31647</v>
+      </c>
+      <c r="L131" t="n">
+        <v>-0.01436</v>
+      </c>
+      <c r="M131" t="n">
+        <v>0.31725</v>
+      </c>
+      <c r="N131" t="n">
+        <v>0.28937</v>
+      </c>
+      <c r="O131" t="n">
+        <v>0.28583</v>
+      </c>
+      <c r="P131" t="n">
+        <v>0.27401</v>
+      </c>
+      <c r="Q131" t="n">
+        <v>0.3098</v>
+      </c>
+      <c r="R131" t="n">
+        <v>0.31026</v>
+      </c>
+      <c r="S131" t="n">
+        <v>0.28588</v>
+      </c>
+      <c r="T131" t="n">
+        <v>0.28362</v>
+      </c>
+      <c r="U131" t="n">
+        <v>0.2946</v>
+      </c>
+      <c r="V131" t="n">
+        <v>0.28328</v>
+      </c>
+      <c r="W131" t="n">
+        <v>0.30982</v>
+      </c>
+      <c r="X131" t="n">
+        <v>0.28397</v>
+      </c>
+      <c r="Y131" t="n">
+        <v>0.28558</v>
+      </c>
+      <c r="Z131" t="n">
+        <v>0.27339</v>
+      </c>
+      <c r="AA131" t="n">
+        <v>0.31526</v>
+      </c>
+      <c r="AB131" t="n">
+        <v>0.28444</v>
+      </c>
+      <c r="AC131" t="n">
+        <v>0.29005</v>
+      </c>
+      <c r="AD131" t="n">
+        <v>0.28956</v>
+      </c>
+      <c r="AE131" t="n">
+        <v>0.30655</v>
+      </c>
+      <c r="AF131" t="n">
+        <v>0.28072</v>
+      </c>
+      <c r="AG131" t="n">
+        <v>0.2744</v>
+      </c>
+      <c r="AH131" t="n">
+        <v>0.28438</v>
+      </c>
+      <c r="AI131" t="n">
+        <v>0.29311</v>
+      </c>
+      <c r="AJ131" t="n">
+        <v>0.27432</v>
+      </c>
+      <c r="AK131" t="n">
+        <v>0.28494</v>
+      </c>
+      <c r="AL131" t="n">
+        <v>0.27065</v>
+      </c>
+      <c r="AM131" t="n">
+        <v>0.29154</v>
+      </c>
+      <c r="AN131" t="n">
+        <v>0.29967</v>
+      </c>
+      <c r="AO131" t="n">
+        <v>0.3069</v>
+      </c>
+      <c r="AP131" t="n">
+        <v>0.31643</v>
+      </c>
+      <c r="AQ131" t="n">
+        <v>0.30116</v>
+      </c>
+      <c r="AR131" t="n">
+        <v>0.31164</v>
+      </c>
+      <c r="AS131" t="n">
+        <v>0.30592</v>
+      </c>
+      <c r="AT131" t="n">
+        <v>0.3101</v>
+      </c>
+      <c r="AU131" t="n">
+        <v>0.30646</v>
+      </c>
+      <c r="AV131" t="n">
+        <v>0.30488</v>
+      </c>
+      <c r="AW131" t="n">
+        <v>0.329</v>
+      </c>
+      <c r="AX131" t="n">
+        <v>0.31792</v>
+      </c>
+      <c r="AY131" t="n">
+        <v>0.3701</v>
+      </c>
+      <c r="AZ131" t="n">
+        <v>0.32534</v>
+      </c>
+      <c r="BA131" t="n">
+        <v>0.31811</v>
+      </c>
+      <c r="BB131" t="n">
+        <v>0.30621</v>
+      </c>
+      <c r="BC131" t="n">
+        <v>0.35731</v>
+      </c>
+      <c r="BD131" t="n">
+        <v>0.32096</v>
+      </c>
+      <c r="BE131" t="n">
+        <v>0.32777</v>
+      </c>
+      <c r="BF131" t="n">
+        <v>0.3215</v>
+      </c>
+      <c r="BG131" t="n">
+        <v>0.32285</v>
+      </c>
+      <c r="BH131" t="n">
+        <v>0.31819</v>
+      </c>
+      <c r="BI131" t="n">
+        <v>0.31959</v>
+      </c>
+      <c r="BJ131" t="n">
+        <v>0.32116</v>
+      </c>
+      <c r="BK131" t="n">
+        <v>0.30327</v>
+      </c>
+      <c r="BL131" t="n">
+        <v>0.31995</v>
+      </c>
+      <c r="BM131" t="n">
+        <v>0.32124</v>
+      </c>
+      <c r="BN131" t="n">
+        <v>0.32108</v>
+      </c>
+      <c r="BO131" t="n">
+        <v>0.32452</v>
+      </c>
+      <c r="BP131" t="n">
+        <v>0.3247</v>
+      </c>
+      <c r="BQ131" t="n">
+        <v>0.32348</v>
+      </c>
+      <c r="BR131" t="n">
+        <v>0.32985</v>
+      </c>
+      <c r="BS131" t="n">
+        <v>0.34096</v>
+      </c>
+      <c r="BT131" t="n">
+        <v>0.32027</v>
+      </c>
+      <c r="BU131" t="n">
+        <v>0.32062</v>
+      </c>
+      <c r="BV131" t="n">
+        <v>0.3268</v>
+      </c>
+      <c r="BW131" t="n">
+        <v>0.31563</v>
+      </c>
+      <c r="BX131" t="n">
+        <v>0.32899</v>
+      </c>
+      <c r="BY131" t="n">
+        <v>0.33328</v>
+      </c>
+      <c r="BZ131" t="n">
+        <v>0.31894</v>
+      </c>
+      <c r="CA131" t="n">
+        <v>0.32761</v>
+      </c>
+      <c r="CB131" t="n">
+        <v>0.31946</v>
+      </c>
+      <c r="CC131" t="n">
+        <v>0.32553</v>
+      </c>
+      <c r="CD131" t="n">
+        <v>0.3249</v>
+      </c>
+      <c r="CE131" t="n">
+        <v>0.32702</v>
+      </c>
+      <c r="CF131" t="n">
+        <v>0.38984</v>
+      </c>
+      <c r="CG131" t="n">
+        <v>0.32201</v>
+      </c>
+      <c r="CH131" t="n">
+        <v>0.34602</v>
+      </c>
+      <c r="CI131" t="n">
+        <v>0.5588099999999999</v>
+      </c>
+      <c r="CJ131" t="n">
+        <v>0.5004700000000001</v>
+      </c>
+      <c r="CK131" t="n">
+        <v>0.32721</v>
+      </c>
+      <c r="CL131" t="n">
+        <v>0.20592</v>
+      </c>
+      <c r="CM131" t="n">
+        <v>0.34343</v>
+      </c>
+      <c r="CN131" t="n">
+        <v>0.3297</v>
+      </c>
+      <c r="CO131" t="n">
+        <v>0.32059</v>
+      </c>
+      <c r="CP131" t="n">
+        <v>0.33868</v>
+      </c>
+      <c r="CQ131" t="n">
+        <v>0.32942</v>
+      </c>
+      <c r="CR131" t="n">
+        <v>0.3098399999999999</v>
+      </c>
+      <c r="CS131" t="n">
+        <v>0.29697</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="B132" t="n">
+        <v>0.32199</v>
+      </c>
+      <c r="C132" t="n">
+        <v>0.38138</v>
+      </c>
+      <c r="D132" t="n">
+        <v>0.34652</v>
+      </c>
+      <c r="E132" t="n">
+        <v>0.32314</v>
+      </c>
+      <c r="F132" t="n">
+        <v>0.33228</v>
+      </c>
+      <c r="G132" t="n">
+        <v>0.32942</v>
+      </c>
+      <c r="H132" t="n">
+        <v>0.32909</v>
+      </c>
+      <c r="I132" t="n">
+        <v>0.33225</v>
+      </c>
+      <c r="J132" t="n">
+        <v>0.32834</v>
+      </c>
+      <c r="K132" t="n">
+        <v>0.31547</v>
+      </c>
+      <c r="L132" t="n">
+        <v>0.32921</v>
+      </c>
+      <c r="M132" t="n">
+        <v>0.32307</v>
+      </c>
+      <c r="N132" t="n">
+        <v>0.33022</v>
+      </c>
+      <c r="O132" t="n">
+        <v>0.31257</v>
+      </c>
+      <c r="P132" t="n">
+        <v>0.32636</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>0.32231</v>
+      </c>
+      <c r="R132" t="n">
+        <v>0.31157</v>
+      </c>
+      <c r="S132" t="n">
+        <v>0.32971</v>
+      </c>
+      <c r="T132" t="n">
+        <v>0.33004</v>
+      </c>
+      <c r="U132" t="n">
+        <v>0.31784</v>
+      </c>
+      <c r="V132" t="n">
+        <v>0.28451</v>
+      </c>
+      <c r="W132" t="n">
+        <v>0.32901</v>
+      </c>
+      <c r="X132" t="n">
+        <v>0.32675</v>
+      </c>
+      <c r="Y132" t="n">
+        <v>0.33031</v>
+      </c>
+      <c r="Z132" t="n">
+        <v>0.33031</v>
+      </c>
+      <c r="AA132" t="n">
+        <v>0.30914</v>
+      </c>
+      <c r="AB132" t="n">
+        <v>0.33611</v>
+      </c>
+      <c r="AC132" t="n">
+        <v>0.35012</v>
+      </c>
+      <c r="AD132" t="n">
+        <v>0.3268</v>
+      </c>
+      <c r="AE132" t="n">
+        <v>0.32671</v>
+      </c>
+      <c r="AF132" t="n">
+        <v>0.32142</v>
+      </c>
+      <c r="AG132" t="n">
+        <v>0.32211</v>
+      </c>
+      <c r="AH132" t="n">
+        <v>0.32815</v>
+      </c>
+      <c r="AI132" t="n">
+        <v>0.3183</v>
+      </c>
+      <c r="AJ132" t="n">
+        <v>0.30805</v>
+      </c>
+      <c r="AK132" t="n">
+        <v>0.40681</v>
+      </c>
+      <c r="AL132" t="n">
+        <v>0.31638</v>
+      </c>
+      <c r="AM132" t="n">
+        <v>0.31982</v>
+      </c>
+      <c r="AN132" t="n">
+        <v>0.31658</v>
+      </c>
+      <c r="AO132" t="n">
+        <v>0.3198</v>
+      </c>
+      <c r="AP132" t="n">
+        <v>0.31821</v>
+      </c>
+      <c r="AQ132" t="n">
+        <v>0.31774</v>
+      </c>
+      <c r="AR132" t="n">
+        <v>0.32494</v>
+      </c>
+      <c r="AS132" t="n">
+        <v>0.33271</v>
+      </c>
+      <c r="AT132" t="n">
+        <v>0.32612</v>
+      </c>
+      <c r="AU132" t="n">
+        <v>0.31333</v>
+      </c>
+      <c r="AV132" t="n">
+        <v>0.31713</v>
+      </c>
+      <c r="AW132" t="n">
+        <v>0.32652</v>
+      </c>
+      <c r="AX132" t="n">
+        <v>0.32285</v>
+      </c>
+      <c r="AY132" t="n">
+        <v>0.32571</v>
+      </c>
+      <c r="AZ132" t="n">
+        <v>0.32682</v>
+      </c>
+      <c r="BA132" t="n">
+        <v>0.32238</v>
+      </c>
+      <c r="BB132" t="n">
+        <v>0.31903</v>
+      </c>
+      <c r="BC132" t="n">
+        <v>0.32114</v>
+      </c>
+      <c r="BD132" t="n">
+        <v>0.31953</v>
+      </c>
+      <c r="BE132" t="n">
+        <v>0.33626</v>
+      </c>
+      <c r="BF132" t="n">
+        <v>0.33639</v>
+      </c>
+      <c r="BG132" t="n">
+        <v>0.3258</v>
+      </c>
+      <c r="BH132" t="n">
+        <v>0.32793</v>
+      </c>
+      <c r="BI132" t="n">
+        <v>0.32921</v>
+      </c>
+      <c r="BJ132" t="n">
+        <v>0.32711</v>
+      </c>
+      <c r="BK132" t="n">
+        <v>0.33139</v>
+      </c>
+      <c r="BL132" t="n">
+        <v>0.32706</v>
+      </c>
+      <c r="BM132" t="n">
+        <v>0.33468</v>
+      </c>
+      <c r="BN132" t="n">
+        <v>0.34972</v>
+      </c>
+      <c r="BO132" t="n">
+        <v>0.40571</v>
+      </c>
+      <c r="BP132" t="n">
+        <v>0.3698</v>
+      </c>
+      <c r="BQ132" t="n">
+        <v>0.34138</v>
+      </c>
+      <c r="BR132" t="n">
+        <v>0.33459</v>
+      </c>
+      <c r="BS132" t="n">
+        <v>0.38532</v>
+      </c>
+      <c r="BT132" t="n">
+        <v>0.35627</v>
+      </c>
+      <c r="BU132" t="n">
+        <v>0.34258</v>
+      </c>
+      <c r="BV132" t="n">
+        <v>0.32326</v>
+      </c>
+      <c r="BW132" t="n">
+        <v>0.33667</v>
+      </c>
+      <c r="BX132" t="n">
+        <v>0.36105</v>
+      </c>
+      <c r="BY132" t="n">
+        <v>0.43255</v>
+      </c>
+      <c r="BZ132" t="n">
+        <v>0.49867</v>
+      </c>
+      <c r="CA132" t="n">
+        <v>0.58486</v>
+      </c>
+      <c r="CB132" t="n">
+        <v>0.5510700000000001</v>
+      </c>
+      <c r="CC132" t="n">
+        <v>0.59517</v>
+      </c>
+      <c r="CD132" t="n">
+        <v>0.33185</v>
+      </c>
+      <c r="CE132" t="n">
+        <v>0.7316900000000001</v>
+      </c>
+      <c r="CF132" t="n">
+        <v>0.34456</v>
+      </c>
+      <c r="CG132" t="n">
+        <v>0.39811</v>
+      </c>
+      <c r="CH132" t="n">
+        <v>0.3678</v>
+      </c>
+      <c r="CI132" t="n">
+        <v>0.46233</v>
+      </c>
+      <c r="CJ132" t="n">
+        <v>0.3946</v>
+      </c>
+      <c r="CK132" t="n">
+        <v>0.41863</v>
+      </c>
+      <c r="CL132" t="n">
+        <v>0.342</v>
+      </c>
+      <c r="CM132" t="n">
+        <v>0.32374</v>
+      </c>
+      <c r="CN132" t="n">
+        <v>0.31766</v>
+      </c>
+      <c r="CO132" t="n">
+        <v>0.31724</v>
+      </c>
+      <c r="CP132" t="n">
+        <v>0.32058</v>
+      </c>
+      <c r="CQ132" t="n">
+        <v>0.34518</v>
+      </c>
+      <c r="CR132" t="n">
+        <v>0.31698</v>
+      </c>
+      <c r="CS132" t="n">
+        <v>0.31451</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="n">
+        <v>46156</v>
+      </c>
+      <c r="B133" t="n">
+        <v>0.3457</v>
+      </c>
+      <c r="C133" t="n">
+        <v>0.32938</v>
+      </c>
+      <c r="D133" t="n">
+        <v>0.34066</v>
+      </c>
+      <c r="E133" t="n">
+        <v>0.32836</v>
+      </c>
+      <c r="F133" t="n">
+        <v>0.34569</v>
+      </c>
+      <c r="G133" t="n">
+        <v>0.32079</v>
+      </c>
+      <c r="H133" t="n">
+        <v>0.3194</v>
+      </c>
+      <c r="I133" t="n">
+        <v>0.32038</v>
+      </c>
+      <c r="J133" t="n">
+        <v>0.31664</v>
+      </c>
+      <c r="K133" t="n">
+        <v>0.32167</v>
+      </c>
+      <c r="L133" t="n">
+        <v>0.31987</v>
+      </c>
+      <c r="M133" t="n">
+        <v>0.32133</v>
+      </c>
+      <c r="N133" t="n">
+        <v>0.36496</v>
+      </c>
+      <c r="O133" t="n">
+        <v>0.3332</v>
+      </c>
+      <c r="P133" t="n">
+        <v>0.33013</v>
+      </c>
+      <c r="Q133" t="n">
+        <v>0.3279</v>
+      </c>
+      <c r="R133" t="n">
+        <v>0.3583</v>
+      </c>
+      <c r="S133" t="n">
+        <v>0.31113</v>
+      </c>
+      <c r="T133" t="n">
+        <v>0.30987</v>
+      </c>
+      <c r="U133" t="n">
+        <v>0.31054</v>
+      </c>
+      <c r="V133" t="n">
+        <v>0.30986</v>
+      </c>
+      <c r="W133" t="n">
+        <v>0.28801</v>
+      </c>
+      <c r="X133" t="n">
+        <v>0.30396</v>
+      </c>
+      <c r="Y133" t="n">
+        <v>0.31142</v>
+      </c>
+      <c r="Z133" t="n">
+        <v>0.29549</v>
+      </c>
+      <c r="AA133" t="n">
+        <v>0.28307</v>
+      </c>
+      <c r="AB133" t="n">
+        <v>0.29803</v>
+      </c>
+      <c r="AC133" t="n">
+        <v>0.29724</v>
+      </c>
+      <c r="AD133" t="n">
+        <v>0.31023</v>
+      </c>
+      <c r="AE133" t="n">
+        <v>0.31248</v>
+      </c>
+      <c r="AF133" t="n">
+        <v>0.31153</v>
+      </c>
+      <c r="AG133" t="n">
+        <v>0.31307</v>
+      </c>
+      <c r="AH133" t="n">
+        <v>0.44957</v>
+      </c>
+      <c r="AI133" t="n">
+        <v>0.39686</v>
+      </c>
+      <c r="AJ133" t="n">
+        <v>0.42358</v>
+      </c>
+      <c r="AK133" t="n">
+        <v>0.43223</v>
+      </c>
+      <c r="AL133" t="n">
+        <v>0.4605</v>
+      </c>
+      <c r="AM133" t="n">
+        <v>0.49719</v>
+      </c>
+      <c r="AN133" t="n">
+        <v>0.57731</v>
+      </c>
+      <c r="AO133" t="n">
+        <v>0.4048</v>
+      </c>
+      <c r="AP133" t="n">
+        <v>0.31624</v>
+      </c>
+      <c r="AQ133" t="n">
+        <v>0.32481</v>
+      </c>
+      <c r="AR133" t="n">
+        <v>0.33298</v>
+      </c>
+      <c r="AS133" t="n">
+        <v>0.32764</v>
+      </c>
+      <c r="AT133" t="n">
+        <v>0.35088</v>
+      </c>
+      <c r="AU133" t="n">
+        <v>0.43994</v>
+      </c>
+      <c r="AV133" t="n">
+        <v>0.38057</v>
+      </c>
+      <c r="AW133" t="n">
+        <v>0.36092</v>
+      </c>
+      <c r="AX133" t="n">
+        <v>0.32192</v>
+      </c>
+      <c r="AY133" t="n">
+        <v>0.35156</v>
+      </c>
+      <c r="AZ133" t="n">
+        <v>0.34506</v>
+      </c>
+      <c r="BA133" t="n">
+        <v>0.4069700000000001</v>
+      </c>
+      <c r="BB133" t="n">
+        <v>0.66772</v>
+      </c>
+      <c r="BC133" t="n">
+        <v>0.40672</v>
+      </c>
+      <c r="BD133" t="n">
+        <v>0.7010700000000001</v>
+      </c>
+      <c r="BE133" t="n">
+        <v>0.39592</v>
+      </c>
+      <c r="BF133" t="n">
+        <v>0.48332</v>
+      </c>
+      <c r="BG133" t="n">
+        <v>0.34546</v>
+      </c>
+      <c r="BH133" t="n">
+        <v>0.36301</v>
+      </c>
+      <c r="BI133" t="n">
+        <v>0.34073</v>
+      </c>
+      <c r="BJ133" t="n">
+        <v>0.33961</v>
+      </c>
+      <c r="BK133" t="n">
+        <v>0.3392</v>
+      </c>
+      <c r="BL133" t="n">
+        <v>0.33503</v>
+      </c>
+      <c r="BM133" t="n">
+        <v>0.33475</v>
+      </c>
+      <c r="BN133" t="n">
+        <v>0.32669</v>
+      </c>
+      <c r="BO133" t="n">
+        <v>0.45656</v>
+      </c>
+      <c r="BP133" t="n">
+        <v>0.35025</v>
+      </c>
+      <c r="BQ133" t="n">
+        <v>0.34573</v>
+      </c>
+      <c r="BR133" t="n">
+        <v>0.32398</v>
+      </c>
+      <c r="BS133" t="n">
+        <v>0.33512</v>
+      </c>
+      <c r="BT133" t="n">
+        <v>0.33423</v>
+      </c>
+      <c r="BU133" t="n">
+        <v>0.3445</v>
+      </c>
+      <c r="BV133" t="n">
+        <v>0.33282</v>
+      </c>
+      <c r="BW133" t="n">
+        <v>0.33377</v>
+      </c>
+      <c r="BX133" t="n">
+        <v>0.33775</v>
+      </c>
+      <c r="BY133" t="n">
+        <v>0.33576</v>
+      </c>
+      <c r="BZ133" t="n">
+        <v>0.32275</v>
+      </c>
+      <c r="CA133" t="n">
+        <v>0.33253</v>
+      </c>
+      <c r="CB133" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="CC133" t="n">
+        <v>0.33825</v>
+      </c>
+      <c r="CD133" t="n">
+        <v>0.33743</v>
+      </c>
+      <c r="CE133" t="n">
+        <v>0.33713</v>
+      </c>
+      <c r="CF133" t="n">
+        <v>0.42878</v>
+      </c>
+      <c r="CG133" t="n">
+        <v>0.32277</v>
+      </c>
+      <c r="CH133" t="n">
+        <v>0.34585</v>
+      </c>
+      <c r="CI133" t="n">
+        <v>0.34217</v>
+      </c>
+      <c r="CJ133" t="n">
+        <v>0.3274</v>
+      </c>
+      <c r="CK133" t="n">
+        <v>0.33665</v>
+      </c>
+      <c r="CL133" t="n">
+        <v>0.6428400000000001</v>
+      </c>
+      <c r="CM133" t="n">
+        <v>0.5310499999999999</v>
+      </c>
+      <c r="CN133" t="n">
+        <v>0.64271</v>
+      </c>
+      <c r="CO133" t="n">
+        <v>0.33451</v>
+      </c>
+      <c r="CP133" t="n">
+        <v>0.32692</v>
+      </c>
+      <c r="CQ133" t="n">
+        <v>0.3181</v>
+      </c>
+      <c r="CR133" t="n">
+        <v>0.32161</v>
+      </c>
+      <c r="CS133" t="n">
+        <v>0.31691</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="n">
+        <v>46157</v>
+      </c>
+      <c r="B134" t="n">
+        <v>0.32278</v>
+      </c>
+      <c r="C134" t="n">
+        <v>0.32675</v>
+      </c>
+      <c r="D134" t="n">
+        <v>0.32197</v>
+      </c>
+      <c r="E134" t="n">
+        <v>0.32181</v>
+      </c>
+      <c r="F134" t="n">
+        <v>0.31906</v>
+      </c>
+      <c r="G134" t="n">
+        <v>0.40472</v>
+      </c>
+      <c r="H134" t="n">
+        <v>0.39465</v>
+      </c>
+      <c r="I134" t="n">
+        <v>0.31646</v>
+      </c>
+      <c r="J134" t="n">
+        <v>0.38638</v>
+      </c>
+      <c r="K134" t="n">
+        <v>0.31347</v>
+      </c>
+      <c r="L134" t="n">
+        <v>0.26737</v>
+      </c>
+      <c r="M134" t="n">
+        <v>0.28754</v>
+      </c>
+      <c r="N134" t="n">
+        <v>0.29173</v>
+      </c>
+      <c r="O134" t="n">
+        <v>0.31253</v>
+      </c>
+      <c r="P134" t="n">
+        <v>0.30849</v>
+      </c>
+      <c r="Q134" t="n">
+        <v>0.3142200000000001</v>
+      </c>
+      <c r="R134" t="n">
+        <v>0.30516</v>
+      </c>
+      <c r="S134" t="n">
+        <v>0.33044</v>
+      </c>
+      <c r="T134" t="n">
+        <v>0.32724</v>
+      </c>
+      <c r="U134" t="n">
+        <v>0.33622</v>
+      </c>
+      <c r="V134" t="n">
+        <v>-0.00035</v>
+      </c>
+      <c r="W134" t="n">
+        <v>0.27622</v>
+      </c>
+      <c r="X134" t="n">
+        <v>0.28425</v>
+      </c>
+      <c r="Y134" t="n">
+        <v>0.33011</v>
+      </c>
+      <c r="Z134" t="n">
+        <v>0.33622</v>
+      </c>
+      <c r="AA134" t="n">
+        <v>0.27641</v>
+      </c>
+      <c r="AB134" t="n">
+        <v>0.28355</v>
+      </c>
+      <c r="AC134" t="n">
+        <v>0.34978</v>
+      </c>
+      <c r="AD134" t="n">
+        <v>0.29186</v>
+      </c>
+      <c r="AE134" t="n">
+        <v>0.33164</v>
+      </c>
+      <c r="AF134" t="n">
+        <v>0.32541</v>
+      </c>
+      <c r="AG134" t="n">
+        <v>0.34975</v>
+      </c>
+      <c r="AH134" t="n">
+        <v>0.48579</v>
+      </c>
+      <c r="AI134" t="n">
+        <v>0.31835</v>
+      </c>
+      <c r="AJ134" t="n">
+        <v>0.36073</v>
+      </c>
+      <c r="AK134" t="n">
+        <v>0.36965</v>
+      </c>
+      <c r="AL134" t="n">
+        <v>0.3228</v>
+      </c>
+      <c r="AM134" t="n">
+        <v>0.3569</v>
+      </c>
+      <c r="AN134" t="n">
+        <v>0.35092</v>
+      </c>
+      <c r="AO134" t="n">
+        <v>0.3251</v>
+      </c>
+      <c r="AP134" t="n">
+        <v>0.32528</v>
+      </c>
+      <c r="AQ134" t="n">
+        <v>0.32858</v>
+      </c>
+      <c r="AR134" t="n">
+        <v>0.33298</v>
+      </c>
+      <c r="AS134" t="n">
+        <v>0.3486</v>
+      </c>
+      <c r="AT134" t="n">
+        <v>0.50368</v>
+      </c>
+      <c r="AU134" t="n">
+        <v>0.43292</v>
+      </c>
+      <c r="AV134" t="n">
+        <v>0.36389</v>
+      </c>
+      <c r="AW134" t="n">
+        <v>0.44692</v>
+      </c>
+      <c r="AX134" t="n">
+        <v>0.5588500000000001</v>
+      </c>
+      <c r="AY134" t="n">
+        <v>0.38987</v>
+      </c>
+      <c r="AZ134" t="n">
+        <v>0.37911</v>
+      </c>
+      <c r="BA134" t="n">
+        <v>0.41924</v>
+      </c>
+      <c r="BB134" t="n">
+        <v>0.391</v>
+      </c>
+      <c r="BC134" t="n">
+        <v>0.4279</v>
+      </c>
+      <c r="BD134" t="n">
+        <v>0.42657</v>
+      </c>
+      <c r="BE134" t="n">
+        <v>0.42228</v>
+      </c>
+      <c r="BF134" t="n">
+        <v>0.34444</v>
+      </c>
+      <c r="BG134" t="n">
+        <v>0.3473</v>
+      </c>
+      <c r="BH134" t="n">
+        <v>0.32489</v>
+      </c>
+      <c r="BI134" t="n">
+        <v>0.33081</v>
+      </c>
+      <c r="BJ134" t="n">
+        <v>0.33811</v>
+      </c>
+      <c r="BK134" t="n">
+        <v>0.31057</v>
+      </c>
+      <c r="BL134" t="n">
+        <v>0.32982</v>
+      </c>
+      <c r="BM134" t="n">
+        <v>0.32634</v>
+      </c>
+      <c r="BN134" t="n">
+        <v>0.31336</v>
+      </c>
+      <c r="BO134" t="n">
+        <v>0.32032</v>
+      </c>
+      <c r="BP134" t="n">
+        <v>0.32104</v>
+      </c>
+      <c r="BQ134" t="n">
+        <v>0.32393</v>
+      </c>
+      <c r="BR134" t="n">
+        <v>0.38337</v>
+      </c>
+      <c r="BS134" t="n">
+        <v>0.37286</v>
+      </c>
+      <c r="BT134" t="n">
+        <v>0.37749</v>
+      </c>
+      <c r="BU134" t="n">
+        <v>0.33425</v>
+      </c>
+      <c r="BV134" t="n">
+        <v>0.29398</v>
+      </c>
+      <c r="BW134" t="n">
+        <v>0.4391600000000001</v>
+      </c>
+      <c r="BX134" t="n">
+        <v>0.3877</v>
+      </c>
+      <c r="BY134" t="n">
+        <v>0.3895</v>
+      </c>
+      <c r="BZ134" t="n">
+        <v>0.3783</v>
+      </c>
+      <c r="CA134" t="n">
+        <v>0.4962</v>
+      </c>
+      <c r="CB134" t="n">
+        <v>0.34089</v>
+      </c>
+      <c r="CC134" t="n">
+        <v>0.33745</v>
+      </c>
+      <c r="CD134" t="n">
+        <v>0.36693</v>
+      </c>
+      <c r="CE134" t="n">
+        <v>0.37353</v>
+      </c>
+      <c r="CF134" t="n">
+        <v>0.36095</v>
+      </c>
+      <c r="CG134" t="n">
+        <v>0.3450299999999999</v>
+      </c>
+      <c r="CH134" t="n">
+        <v>0.37665</v>
+      </c>
+      <c r="CI134" t="n">
+        <v>0.32755</v>
+      </c>
+      <c r="CJ134" t="n">
+        <v>0.33171</v>
+      </c>
+      <c r="CK134" t="n">
+        <v>0.32869</v>
+      </c>
+      <c r="CL134" t="n">
+        <v>0.33197</v>
+      </c>
+      <c r="CM134" t="n">
+        <v>0.32546</v>
+      </c>
+      <c r="CN134" t="n">
+        <v>0.25728</v>
+      </c>
+      <c r="CO134" t="n">
+        <v>0.31659</v>
+      </c>
+      <c r="CP134" t="n">
+        <v>0.26862</v>
+      </c>
+      <c r="CQ134" t="n">
+        <v>0.26431</v>
+      </c>
+      <c r="CR134" t="n">
+        <v>0.25688</v>
+      </c>
+      <c r="CS134" t="n">
+        <v>0.32661</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="n">
+        <v>46158</v>
+      </c>
+      <c r="B135" t="n">
+        <v>0.22596</v>
+      </c>
+      <c r="C135" t="n">
+        <v>0.3155</v>
+      </c>
+      <c r="D135" t="n">
+        <v>0.3097200000000001</v>
+      </c>
+      <c r="E135" t="n">
+        <v>0.30094</v>
+      </c>
+      <c r="F135" t="n">
+        <v>0.25549</v>
+      </c>
+      <c r="G135" t="n">
+        <v>0.29149</v>
+      </c>
+      <c r="H135" t="n">
+        <v>0.23252</v>
+      </c>
+      <c r="I135" t="n">
+        <v>0.16746</v>
+      </c>
+      <c r="J135" t="n">
+        <v>-0.00219</v>
+      </c>
+      <c r="K135" t="n">
+        <v>0.27151</v>
+      </c>
+      <c r="L135" t="n">
+        <v>-0.0052</v>
+      </c>
+      <c r="M135" t="n">
+        <v>-0.004719999999999999</v>
+      </c>
+      <c r="N135" t="n">
+        <v>0.1677</v>
+      </c>
+      <c r="O135" t="n">
+        <v>-0.01615</v>
+      </c>
+      <c r="P135" t="n">
+        <v>0.20053</v>
+      </c>
+      <c r="Q135" t="n">
+        <v>0.32169</v>
+      </c>
+      <c r="R135" t="n">
+        <v>0.1665</v>
+      </c>
+      <c r="S135" t="n">
+        <v>-0.00545</v>
+      </c>
+      <c r="T135" t="n">
+        <v>0.15707</v>
+      </c>
+      <c r="U135" t="n">
+        <v>0.16161</v>
+      </c>
+      <c r="V135" t="n">
+        <v>0.19642</v>
+      </c>
+      <c r="W135" t="n">
+        <v>0.15924</v>
+      </c>
+      <c r="X135" t="n">
+        <v>0.16196</v>
+      </c>
+      <c r="Y135" t="n">
+        <v>0.16468</v>
+      </c>
+      <c r="Z135" t="n">
+        <v>-0.00609</v>
+      </c>
+      <c r="AA135" t="n">
+        <v>0.1674</v>
+      </c>
+      <c r="AB135" t="n">
+        <v>-0.00622</v>
+      </c>
+      <c r="AC135" t="n">
+        <v>-0.03126</v>
+      </c>
+      <c r="AD135" t="n">
+        <v>0.1783</v>
+      </c>
+      <c r="AE135" t="n">
+        <v>0.18231</v>
+      </c>
+      <c r="AF135" t="n">
+        <v>0.14954</v>
+      </c>
+      <c r="AG135" t="n">
+        <v>0.2836</v>
+      </c>
+      <c r="AH135" t="n">
+        <v>-0.0371</v>
+      </c>
+      <c r="AI135" t="n">
+        <v>0.32891</v>
+      </c>
+      <c r="AJ135" t="n">
+        <v>0.29361</v>
+      </c>
+      <c r="AK135" t="n">
+        <v>0.31197</v>
+      </c>
+      <c r="AL135" t="n">
+        <v>0.30105</v>
+      </c>
+      <c r="AM135" t="n">
+        <v>0.16108</v>
+      </c>
+      <c r="AN135" t="n">
+        <v>0.30579</v>
+      </c>
+      <c r="AO135" t="n">
+        <v>0.32172</v>
+      </c>
+      <c r="AP135" t="n">
+        <v>0.28902</v>
+      </c>
+      <c r="AQ135" t="n">
+        <v>0.32276</v>
+      </c>
+      <c r="AR135" t="n">
+        <v>0.30615</v>
+      </c>
+      <c r="AS135" t="n">
+        <v>0.15577</v>
+      </c>
+      <c r="AT135" t="n">
+        <v>0.37252</v>
+      </c>
+      <c r="AU135" t="n">
+        <v>0.33639</v>
+      </c>
+      <c r="AV135" t="n">
+        <v>1.23825</v>
+      </c>
+      <c r="AW135" t="n">
+        <v>0.3371499999999999</v>
+      </c>
+      <c r="AX135" t="n">
+        <v>0.0007199999999999999</v>
+      </c>
+      <c r="AY135" t="n">
+        <v>0.34475</v>
+      </c>
+      <c r="AZ135" t="n">
+        <v>0.32503</v>
+      </c>
+      <c r="BA135" t="n">
+        <v>0.29919</v>
+      </c>
+      <c r="BB135" t="n">
+        <v>0.33866</v>
+      </c>
+      <c r="BC135" t="n">
+        <v>0.3478</v>
+      </c>
+      <c r="BD135" t="n">
+        <v>0.33597</v>
+      </c>
+      <c r="BE135" t="n">
+        <v>0.33948</v>
+      </c>
+      <c r="BF135" t="n">
+        <v>0.37864</v>
+      </c>
+      <c r="BG135" t="n">
+        <v>0.33608</v>
+      </c>
+      <c r="BH135" t="n">
+        <v>0.31542</v>
+      </c>
+      <c r="BI135" t="n">
+        <v>0.31725</v>
+      </c>
+      <c r="BJ135" t="n">
+        <v>0.32713</v>
+      </c>
+      <c r="BK135" t="n">
+        <v>0.32606</v>
+      </c>
+      <c r="BL135" t="n">
+        <v>0.30469</v>
+      </c>
+      <c r="BM135" t="n">
+        <v>0.35788</v>
+      </c>
+      <c r="BN135" t="n">
+        <v>0.3456</v>
+      </c>
+      <c r="BO135" t="n">
+        <v>0.30779</v>
+      </c>
+      <c r="BP135" t="n">
+        <v>0.3257</v>
+      </c>
+      <c r="BQ135" t="n">
+        <v>0.33506</v>
+      </c>
+      <c r="BR135" t="n">
+        <v>0.31701</v>
+      </c>
+      <c r="BS135" t="n">
+        <v>0.33081</v>
+      </c>
+      <c r="BT135" t="n">
+        <v>0.35896</v>
+      </c>
+      <c r="BU135" t="n">
+        <v>0.25117</v>
+      </c>
+      <c r="BV135" t="n">
+        <v>0.32139</v>
+      </c>
+      <c r="BW135" t="n">
+        <v>0.33034</v>
+      </c>
+      <c r="BX135" t="n">
+        <v>0.33526</v>
+      </c>
+      <c r="BY135" t="n">
+        <v>0.33158</v>
+      </c>
+      <c r="BZ135" t="n">
+        <v>0.33623</v>
+      </c>
+      <c r="CA135" t="n">
+        <v>0.32582</v>
+      </c>
+      <c r="CB135" t="n">
+        <v>0.33131</v>
+      </c>
+      <c r="CC135" t="n">
+        <v>0.32624</v>
+      </c>
+      <c r="CD135" t="n">
+        <v>0.32773</v>
+      </c>
+      <c r="CE135" t="n">
+        <v>0.21993</v>
+      </c>
+      <c r="CF135" t="n">
+        <v>0.32871</v>
+      </c>
+      <c r="CG135" t="n">
+        <v>0.26749</v>
+      </c>
+      <c r="CH135" t="n">
+        <v>0.24596</v>
+      </c>
+      <c r="CI135" t="n">
+        <v>0.29948</v>
+      </c>
+      <c r="CJ135" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="CK135" t="n">
+        <v>0.26958</v>
+      </c>
+      <c r="CL135" t="n">
+        <v>0.26789</v>
+      </c>
+      <c r="CM135" t="n">
+        <v>0.21766</v>
+      </c>
+      <c r="CN135" t="n">
+        <v>0.22323</v>
+      </c>
+      <c r="CO135" t="n">
+        <v>0.26977</v>
+      </c>
+      <c r="CP135" t="n">
+        <v>0.21018</v>
+      </c>
+      <c r="CQ135" t="n">
+        <v>0.29377</v>
+      </c>
+      <c r="CR135" t="n">
+        <v>0.21852</v>
+      </c>
+      <c r="CS135" t="n">
+        <v>0.28223</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="n">
+        <v>46159</v>
+      </c>
+      <c r="B136" t="n">
+        <v>0.22904</v>
+      </c>
+      <c r="C136" t="n">
+        <v>0.3317</v>
+      </c>
+      <c r="D136" t="n">
+        <v>0.30309</v>
+      </c>
+      <c r="E136" t="n">
+        <v>0.29162</v>
+      </c>
+      <c r="F136" t="n">
+        <v>0.28442</v>
+      </c>
+      <c r="G136" t="n">
+        <v>0.27312</v>
+      </c>
+      <c r="H136" t="n">
+        <v>0.0418</v>
+      </c>
+      <c r="I136" t="n">
+        <v>0.18487</v>
+      </c>
+      <c r="J136" t="n">
+        <v>0.18191</v>
+      </c>
+      <c r="K136" t="n">
+        <v>0.2664</v>
+      </c>
+      <c r="L136" t="n">
+        <v>-0.01509</v>
+      </c>
+      <c r="M136" t="n">
+        <v>0.20163</v>
+      </c>
+      <c r="N136" t="n">
+        <v>0.22259</v>
+      </c>
+      <c r="O136" t="n">
+        <v>0.21424</v>
+      </c>
+      <c r="P136" t="n">
+        <v>0.03014</v>
+      </c>
+      <c r="Q136" t="n">
+        <v>-0.02668</v>
+      </c>
+      <c r="R136" t="n">
+        <v>-0.01284</v>
+      </c>
+      <c r="S136" t="n">
+        <v>-0.01285</v>
+      </c>
+      <c r="T136" t="n">
+        <v>-0.01325</v>
+      </c>
+      <c r="U136" t="n">
+        <v>-0.01325</v>
+      </c>
+      <c r="V136" t="n">
+        <v>-0.01301</v>
+      </c>
+      <c r="W136" t="n">
+        <v>0.19628</v>
+      </c>
+      <c r="X136" t="n">
+        <v>-0.02699</v>
+      </c>
+      <c r="Y136" t="n">
+        <v>-0.01325</v>
+      </c>
+      <c r="Z136" t="n">
+        <v>-0.01322</v>
+      </c>
+      <c r="AA136" t="n">
+        <v>0.17527</v>
+      </c>
+      <c r="AB136" t="n">
+        <v>-0.02668</v>
+      </c>
+      <c r="AC136" t="n">
+        <v>-0.02666</v>
+      </c>
+      <c r="AD136" t="n">
+        <v>0.30453</v>
+      </c>
+      <c r="AE136" t="n">
+        <v>-0.01205</v>
+      </c>
+      <c r="AF136" t="n">
+        <v>-0.01286</v>
+      </c>
+      <c r="AG136" t="n">
+        <v>0.2444</v>
+      </c>
+      <c r="AH136" t="n">
+        <v>0.02688</v>
+      </c>
+      <c r="AI136" t="n">
+        <v>-0.00734</v>
+      </c>
+      <c r="AJ136" t="n">
+        <v>0.00042</v>
+      </c>
+      <c r="AK136" t="n">
+        <v>0.00037</v>
+      </c>
+      <c r="AL136" t="n">
+        <v>-0.04958</v>
+      </c>
+      <c r="AM136" t="n">
+        <v>0.24014</v>
+      </c>
+      <c r="AN136" t="n">
+        <v>0.02205</v>
+      </c>
+      <c r="AO136" t="n">
+        <v>-0.03958</v>
+      </c>
+      <c r="AP136" t="n">
+        <v>-0.0496</v>
+      </c>
+      <c r="AQ136" t="n">
+        <v>-0.00338</v>
+      </c>
+      <c r="AR136" t="n">
+        <v>-0.04298</v>
+      </c>
+      <c r="AS136" t="n">
+        <v>-0.04089</v>
+      </c>
+      <c r="AT136" t="n">
+        <v>-0.04861</v>
+      </c>
+      <c r="AU136" t="n">
+        <v>-0.04827</v>
+      </c>
+      <c r="AV136" t="n">
+        <v>-0.02446</v>
+      </c>
+      <c r="AW136" t="n">
+        <v>-0.02936</v>
+      </c>
+      <c r="AX136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY136" t="n">
+        <v>-0.04962</v>
+      </c>
+      <c r="AZ136" t="n">
+        <v>-0.04373</v>
+      </c>
+      <c r="BA136" t="n">
+        <v>-0.0496</v>
+      </c>
+      <c r="BB136" t="n">
+        <v>-0.04961</v>
+      </c>
+      <c r="BC136" t="n">
+        <v>-0.04941</v>
+      </c>
+      <c r="BD136" t="n">
+        <v>0.02399</v>
+      </c>
+      <c r="BE136" t="n">
+        <v>0.30054</v>
+      </c>
+      <c r="BF136" t="n">
+        <v>-0.04965</v>
+      </c>
+      <c r="BG136" t="n">
+        <v>-0.04915</v>
+      </c>
+      <c r="BH136" t="n">
+        <v>-0.04961</v>
+      </c>
+      <c r="BI136" t="n">
+        <v>-0.02336</v>
+      </c>
+      <c r="BJ136" t="n">
+        <v>0.05256</v>
+      </c>
+      <c r="BK136" t="n">
+        <v>-0.04959</v>
+      </c>
+      <c r="BL136" t="n">
+        <v>-0.04965</v>
+      </c>
+      <c r="BM136" t="n">
+        <v>-0.02962</v>
+      </c>
+      <c r="BN136" t="n">
+        <v>0.25099</v>
+      </c>
+      <c r="BO136" t="n">
+        <v>0.29509</v>
+      </c>
+      <c r="BP136" t="n">
+        <v>0.32854</v>
+      </c>
+      <c r="BQ136" t="n">
+        <v>0.29981</v>
+      </c>
+      <c r="BR136" t="n">
+        <v>0.30184</v>
+      </c>
+      <c r="BS136" t="n">
+        <v>0.31156</v>
+      </c>
+      <c r="BT136" t="n">
+        <v>-0.01223</v>
+      </c>
+      <c r="BU136" t="n">
+        <v>0.31283</v>
+      </c>
+      <c r="BV136" t="n">
+        <v>0.31604</v>
+      </c>
+      <c r="BW136" t="n">
+        <v>0.40336</v>
+      </c>
+      <c r="BX136" t="n">
+        <v>0.38075</v>
+      </c>
+      <c r="BY136" t="n">
+        <v>0.36855</v>
+      </c>
+      <c r="BZ136" t="n">
+        <v>0.2809700000000001</v>
+      </c>
+      <c r="CA136" t="n">
+        <v>0.29481</v>
+      </c>
+      <c r="CB136" t="n">
+        <v>0.31171</v>
+      </c>
+      <c r="CC136" t="n">
+        <v>0.31343</v>
+      </c>
+      <c r="CD136" t="n">
+        <v>0.29363</v>
+      </c>
+      <c r="CE136" t="n">
+        <v>0.32446</v>
+      </c>
+      <c r="CF136" t="n">
+        <v>0.32738</v>
+      </c>
+      <c r="CG136" t="n">
+        <v>0.32604</v>
+      </c>
+      <c r="CH136" t="n">
+        <v>0.32179</v>
+      </c>
+      <c r="CI136" t="n">
+        <v>0.32833</v>
+      </c>
+      <c r="CJ136" t="n">
+        <v>0.33632</v>
+      </c>
+      <c r="CK136" t="n">
+        <v>0.33058</v>
+      </c>
+      <c r="CL136" t="n">
+        <v>0.32653</v>
+      </c>
+      <c r="CM136" t="n">
+        <v>0.32368</v>
+      </c>
+      <c r="CN136" t="n">
+        <v>0.31187</v>
+      </c>
+      <c r="CO136" t="n">
+        <v>0.30401</v>
+      </c>
+      <c r="CP136" t="n">
+        <v>0.29226</v>
+      </c>
+      <c r="CQ136" t="n">
+        <v>0.31237</v>
+      </c>
+      <c r="CR136" t="n">
+        <v>0.29869</v>
+      </c>
+      <c r="CS136" t="n">
+        <v>0.26899</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="n">
+        <v>46160</v>
+      </c>
+      <c r="B137" t="n">
+        <v>0.29801</v>
+      </c>
+      <c r="C137" t="n">
+        <v>0.33689</v>
+      </c>
+      <c r="D137" t="n">
+        <v>0.32334</v>
+      </c>
+      <c r="E137" t="n">
+        <v>0.29887</v>
+      </c>
+      <c r="F137" t="n">
+        <v>0.01092</v>
+      </c>
+      <c r="G137" t="n">
+        <v>0.27805</v>
+      </c>
+      <c r="H137" t="n">
+        <v>0.30354</v>
+      </c>
+      <c r="I137" t="n">
+        <v>0.28431</v>
+      </c>
+      <c r="J137" t="n">
+        <v>0.27872</v>
+      </c>
+      <c r="K137" t="n">
+        <v>0.16898</v>
+      </c>
+      <c r="L137" t="n">
+        <v>0.31803</v>
+      </c>
+      <c r="M137" t="n">
+        <v>0.16392</v>
+      </c>
+      <c r="N137" t="n">
+        <v>0.16828</v>
+      </c>
+      <c r="O137" t="n">
+        <v>0.16566</v>
+      </c>
+      <c r="P137" t="n">
+        <v>-0.03750999999999999</v>
+      </c>
+      <c r="Q137" t="n">
+        <v>0.16175</v>
+      </c>
+      <c r="R137" t="n">
+        <v>0.15069</v>
+      </c>
+      <c r="S137" t="n">
+        <v>-0.03701</v>
+      </c>
+      <c r="T137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="U137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="V137" t="n">
+        <v>-0.03833</v>
+      </c>
+      <c r="W137" t="n">
+        <v>-0.03699</v>
+      </c>
+      <c r="X137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="Y137" t="n">
+        <v>-0.00711</v>
+      </c>
+      <c r="Z137" t="n">
+        <v>-0.00546</v>
+      </c>
+      <c r="AA137" t="n">
+        <v>-0.00262</v>
+      </c>
+      <c r="AB137" t="n">
+        <v>0.41475</v>
+      </c>
+      <c r="AC137" t="n">
+        <v>0.19269</v>
+      </c>
+      <c r="AD137" t="n">
+        <v>0.2762</v>
+      </c>
+      <c r="AE137" t="n">
+        <v>0.3241</v>
+      </c>
+      <c r="AF137" t="n">
+        <v>-0.03806</v>
+      </c>
+      <c r="AG137" t="n">
+        <v>0.23547</v>
+      </c>
+      <c r="AH137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AI137" t="n">
+        <v>0.31096</v>
+      </c>
+      <c r="AJ137" t="n">
+        <v>0.85765</v>
+      </c>
+      <c r="AK137" t="n">
+        <v>0.86212</v>
+      </c>
+      <c r="AL137" t="n">
+        <v>0.32902</v>
+      </c>
+      <c r="AM137" t="n">
+        <v>0.35948</v>
+      </c>
+      <c r="AN137" t="n">
+        <v>0.09093000000000001</v>
+      </c>
+      <c r="AO137" t="n">
+        <v>-0.01266</v>
+      </c>
+      <c r="AP137" t="n">
+        <v>0.24818</v>
+      </c>
+      <c r="AQ137" t="n">
+        <v>0.31382</v>
+      </c>
+      <c r="AR137" t="n">
+        <v>0.31984</v>
+      </c>
+      <c r="AS137" t="n">
+        <v>0.32076</v>
+      </c>
+      <c r="AT137" t="n">
+        <v>0.28115</v>
+      </c>
+      <c r="AU137" t="n">
+        <v>0.29551</v>
+      </c>
+      <c r="AV137" t="n">
+        <v>0.29373</v>
+      </c>
+      <c r="AW137" t="n">
+        <v>0.32716</v>
+      </c>
+      <c r="AX137" t="n">
+        <v>0.51095</v>
+      </c>
+      <c r="AY137" t="n">
+        <v>0.30009</v>
+      </c>
+      <c r="AZ137" t="n">
+        <v>0.29349</v>
+      </c>
+      <c r="BA137" t="n">
+        <v>0.00245</v>
+      </c>
+      <c r="BB137" t="n">
+        <v>0.2928</v>
+      </c>
+      <c r="BC137" t="n">
+        <v>0.00173</v>
+      </c>
+      <c r="BD137" t="n">
+        <v>0.3166600000000001</v>
+      </c>
+      <c r="BE137" t="n">
+        <v>0.32079</v>
+      </c>
+      <c r="BF137" t="n">
+        <v>0.31363</v>
+      </c>
+      <c r="BG137" t="n">
+        <v>0.06909999999999999</v>
+      </c>
+      <c r="BH137" t="n">
+        <v>0.30801</v>
+      </c>
+      <c r="BI137" t="n">
+        <v>0.30265</v>
+      </c>
+      <c r="BJ137" t="n">
+        <v>0.30806</v>
+      </c>
+      <c r="BK137" t="n">
+        <v>0.3082</v>
+      </c>
+      <c r="BL137" t="n">
+        <v>0.25453</v>
+      </c>
+      <c r="BM137" t="n">
+        <v>0.29188</v>
+      </c>
+      <c r="BN137" t="n">
+        <v>0.4752</v>
+      </c>
+      <c r="BO137" t="n">
+        <v>0.32032</v>
+      </c>
+      <c r="BP137" t="n">
+        <v>0.31911</v>
+      </c>
+      <c r="BQ137" t="n">
+        <v>0.32589</v>
+      </c>
+      <c r="BR137" t="n">
+        <v>0.32652</v>
+      </c>
+      <c r="BS137" t="n">
+        <v>0.33036</v>
+      </c>
+      <c r="BT137" t="n">
+        <v>0.31503</v>
+      </c>
+      <c r="BU137" t="n">
+        <v>0.32861</v>
+      </c>
+      <c r="BV137" t="n">
+        <v>0.32265</v>
+      </c>
+      <c r="BW137" t="n">
+        <v>0.33198</v>
+      </c>
+      <c r="BX137" t="n">
+        <v>0.61209</v>
+      </c>
+      <c r="BY137" t="n">
+        <v>0.48911</v>
+      </c>
+      <c r="BZ137" t="n">
+        <v>0.35826</v>
+      </c>
+      <c r="CA137" t="n">
+        <v>0.41477</v>
+      </c>
+      <c r="CB137" t="n">
+        <v>0.70628</v>
+      </c>
+      <c r="CC137" t="n">
+        <v>0.8217300000000001</v>
+      </c>
+      <c r="CD137" t="n">
+        <v>0.37225</v>
+      </c>
+      <c r="CE137" t="n">
+        <v>0.55244</v>
+      </c>
+      <c r="CF137" t="n">
+        <v>0.4171</v>
+      </c>
+      <c r="CG137" t="n">
+        <v>1.59071</v>
+      </c>
+      <c r="CH137" t="n">
+        <v>0.70186</v>
+      </c>
+      <c r="CI137" t="n">
+        <v>0.70009</v>
+      </c>
+      <c r="CJ137" t="n">
+        <v>0.7031900000000001</v>
+      </c>
+      <c r="CK137" t="n">
+        <v>0.77811</v>
+      </c>
+      <c r="CL137" t="n">
+        <v>0.35722</v>
+      </c>
+      <c r="CM137" t="n">
+        <v>0.41078</v>
+      </c>
+      <c r="CN137" t="n">
+        <v>0.36656</v>
+      </c>
+      <c r="CO137" t="n">
+        <v>0.33068</v>
+      </c>
+      <c r="CP137" t="n">
+        <v>0.31852</v>
+      </c>
+      <c r="CQ137" t="n">
+        <v>0.34829</v>
+      </c>
+      <c r="CR137" t="n">
+        <v>0.30772</v>
+      </c>
+      <c r="CS137" t="n">
+        <v>0.30756</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="n">
+        <v>46161</v>
+      </c>
+      <c r="B138" t="n">
+        <v>0.33007</v>
+      </c>
+      <c r="C138" t="n">
+        <v>0.32974</v>
+      </c>
+      <c r="D138" t="n">
+        <v>0.33031</v>
+      </c>
+      <c r="E138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="F138" t="n">
+        <v>0.31515</v>
+      </c>
+      <c r="G138" t="n">
+        <v>0.43658</v>
+      </c>
+      <c r="H138" t="n">
+        <v>0.30624</v>
+      </c>
+      <c r="I138" t="n">
+        <v>0.29035</v>
+      </c>
+      <c r="J138" t="n">
+        <v>0.27017</v>
+      </c>
+      <c r="K138" t="n">
+        <v>0.35705</v>
+      </c>
+      <c r="L138" t="n">
+        <v>0.26401</v>
+      </c>
+      <c r="M138" t="n">
+        <v>0.19054</v>
+      </c>
+      <c r="N138" t="n">
+        <v>0.25881</v>
+      </c>
+      <c r="O138" t="n">
+        <v>0.25366</v>
+      </c>
+      <c r="P138" t="n">
+        <v>0.24701</v>
+      </c>
+      <c r="Q138" t="n">
+        <v>0.21488</v>
+      </c>
+      <c r="R138" t="n">
+        <v>0.25754</v>
+      </c>
+      <c r="S138" t="n">
+        <v>0.20179</v>
+      </c>
+      <c r="T138" t="n">
+        <v>0.1667</v>
+      </c>
+      <c r="U138" t="n">
+        <v>0.19739</v>
+      </c>
+      <c r="V138" t="n">
+        <v>0.16122</v>
+      </c>
+      <c r="W138" t="n">
+        <v>0.16389</v>
+      </c>
+      <c r="X138" t="n">
+        <v>-0.03808</v>
+      </c>
+      <c r="Y138" t="n">
+        <v>0.15739</v>
+      </c>
+      <c r="Z138" t="n">
+        <v>0.18143</v>
+      </c>
+      <c r="AA138" t="n">
+        <v>0.23157</v>
+      </c>
+      <c r="AB138" t="n">
+        <v>0.3118</v>
+      </c>
+      <c r="AC138" t="n">
+        <v>0.28145</v>
+      </c>
+      <c r="AD138" t="n">
+        <v>0.24075</v>
+      </c>
+      <c r="AE138" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AF138" t="n">
+        <v>0.29772</v>
+      </c>
+      <c r="AG138" t="n">
+        <v>0.25252</v>
+      </c>
+      <c r="AH138" t="n">
+        <v>0.27552</v>
+      </c>
+      <c r="AI138" t="n">
+        <v>0.30513</v>
+      </c>
+      <c r="AJ138" t="n">
+        <v>0.35506</v>
+      </c>
+      <c r="AK138" t="n">
+        <v>0.32413</v>
+      </c>
+      <c r="AL138" t="n">
+        <v>0.3287</v>
+      </c>
+      <c r="AM138" t="n">
+        <v>0.37995</v>
+      </c>
+      <c r="AN138" t="n">
+        <v>0.30173</v>
+      </c>
+      <c r="AO138" t="n">
+        <v>0.32795</v>
+      </c>
+      <c r="AP138" t="n">
+        <v>0.32611</v>
+      </c>
+      <c r="AQ138" t="n">
+        <v>0.3301</v>
+      </c>
+      <c r="AR138" t="n">
+        <v>0.28899</v>
+      </c>
+      <c r="AS138" t="n">
+        <v>0.31013</v>
+      </c>
+      <c r="AT138" t="n">
+        <v>0.3073</v>
+      </c>
+      <c r="AU138" t="n">
+        <v>0.31871</v>
+      </c>
+      <c r="AV138" t="n">
+        <v>0.32028</v>
+      </c>
+      <c r="AW138" t="n">
+        <v>0.3086</v>
+      </c>
+      <c r="AX138" t="n">
+        <v>0.2586</v>
+      </c>
+      <c r="AY138" t="n">
+        <v>0.31129</v>
+      </c>
+      <c r="AZ138" t="n">
+        <v>0.30246</v>
+      </c>
+      <c r="BA138" t="n">
+        <v>0.30222</v>
+      </c>
+      <c r="BB138" t="n">
+        <v>0.32669</v>
+      </c>
+      <c r="BC138" t="n">
+        <v>0.32047</v>
+      </c>
+      <c r="BD138" t="n">
+        <v>0.31815</v>
+      </c>
+      <c r="BE138" t="n">
+        <v>0.33671</v>
+      </c>
+      <c r="BF138" t="n">
+        <v>0.3169</v>
+      </c>
+      <c r="BG138" t="n">
+        <v>0.32822</v>
+      </c>
+      <c r="BH138" t="n">
+        <v>0.3246</v>
+      </c>
+      <c r="BI138" t="n">
+        <v>0.31563</v>
+      </c>
+      <c r="BJ138" t="n">
+        <v>0.34487</v>
+      </c>
+      <c r="BK138" t="n">
+        <v>0.3349</v>
+      </c>
+      <c r="BL138" t="n">
+        <v>0.34113</v>
+      </c>
+      <c r="BM138" t="n">
+        <v>0.34153</v>
+      </c>
+      <c r="BN138" t="n">
+        <v>0.33976</v>
+      </c>
+      <c r="BO138" t="n">
+        <v>0.3422</v>
+      </c>
+      <c r="BP138" t="n">
+        <v>0.3444</v>
+      </c>
+      <c r="BQ138" t="n">
+        <v>0.33621</v>
+      </c>
+      <c r="BR138" t="n">
+        <v>0.33125</v>
+      </c>
+      <c r="BS138" t="n">
+        <v>0.33338</v>
+      </c>
+      <c r="BT138" t="n">
+        <v>0.31781</v>
+      </c>
+      <c r="BU138" t="n">
+        <v>0.32427</v>
+      </c>
+      <c r="BV138" t="n">
+        <v>0.32775</v>
+      </c>
+      <c r="BW138" t="n">
+        <v>0.33288</v>
+      </c>
+      <c r="BX138" t="n">
+        <v>0.36935</v>
+      </c>
+      <c r="BY138" t="n">
+        <v>0.34621</v>
+      </c>
+      <c r="BZ138" t="n">
+        <v>0.33381</v>
+      </c>
+      <c r="CA138" t="n">
+        <v>0.33654</v>
+      </c>
+      <c r="CB138" t="n">
+        <v>0.3373</v>
+      </c>
+      <c r="CC138" t="n">
+        <v>0.32095</v>
+      </c>
+      <c r="CD138" t="n">
+        <v>0.39746</v>
+      </c>
+      <c r="CE138" t="n">
+        <v>0.36704</v>
+      </c>
+      <c r="CF138" t="n">
+        <v>0.4162</v>
+      </c>
+      <c r="CG138" t="n">
+        <v>0.35612</v>
+      </c>
+      <c r="CH138" t="n">
+        <v>0.43125</v>
+      </c>
+      <c r="CI138" t="n">
+        <v>0.33008</v>
+      </c>
+      <c r="CJ138" t="n">
+        <v>0.3107799999999999</v>
+      </c>
+      <c r="CK138" t="n">
+        <v>0.33771</v>
+      </c>
+      <c r="CL138" t="n">
+        <v>0.31818</v>
+      </c>
+      <c r="CM138" t="n">
+        <v>0.31932</v>
+      </c>
+      <c r="CN138" t="n">
+        <v>0.32356</v>
+      </c>
+      <c r="CO138" t="n">
+        <v>0.31358</v>
+      </c>
+      <c r="CP138" t="n">
+        <v>0.30736</v>
+      </c>
+      <c r="CQ138" t="n">
+        <v>0.29574</v>
+      </c>
+      <c r="CR138" t="n">
+        <v>0.29064</v>
+      </c>
+      <c r="CS138" t="n">
+        <v>0.29135</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="n">
+        <v>46162</v>
+      </c>
+      <c r="B139" t="n">
+        <v>0.3271</v>
+      </c>
+      <c r="C139" t="n">
+        <v>0.35811</v>
+      </c>
+      <c r="D139" t="n">
+        <v>0.35111</v>
+      </c>
+      <c r="E139" t="n">
+        <v>0.34731</v>
+      </c>
+      <c r="F139" t="n">
+        <v>0.33124</v>
+      </c>
+      <c r="G139" t="n">
+        <v>0.33282</v>
+      </c>
+      <c r="H139" t="n">
+        <v>0.33005</v>
+      </c>
+      <c r="I139" t="n">
+        <v>0.33059</v>
+      </c>
+      <c r="J139" t="n">
+        <v>0.32297</v>
+      </c>
+      <c r="K139" t="n">
+        <v>0.31874</v>
+      </c>
+      <c r="L139" t="n">
+        <v>0.31295</v>
+      </c>
+      <c r="M139" t="n">
+        <v>0.3127799999999999</v>
+      </c>
+      <c r="N139" t="n">
+        <v>0.32621</v>
+      </c>
+      <c r="O139" t="n">
+        <v>0.31501</v>
+      </c>
+      <c r="P139" t="n">
+        <v>0.31443</v>
+      </c>
+      <c r="Q139" t="n">
+        <v>0.32176</v>
+      </c>
+      <c r="R139" t="n">
+        <v>0.3129</v>
+      </c>
+      <c r="S139" t="n">
+        <v>0.30195</v>
+      </c>
+      <c r="T139" t="n">
+        <v>0.30169</v>
+      </c>
+      <c r="U139" t="n">
+        <v>0.29401</v>
+      </c>
+      <c r="V139" t="n">
+        <v>0.29779</v>
+      </c>
+      <c r="W139" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="X139" t="n">
+        <v>0.30008</v>
+      </c>
+      <c r="Y139" t="n">
+        <v>0.30631</v>
+      </c>
+      <c r="Z139" t="n">
+        <v>0.30169</v>
+      </c>
+      <c r="AA139" t="n">
+        <v>0.31191</v>
+      </c>
+      <c r="AB139" t="n">
+        <v>0.30706</v>
+      </c>
+      <c r="AC139" t="n">
+        <v>0.31262</v>
+      </c>
+      <c r="AD139" t="n">
+        <v>0.31261</v>
+      </c>
+      <c r="AE139" t="n">
+        <v>0.31884</v>
+      </c>
+      <c r="AF139" t="n">
+        <v>0.30429</v>
+      </c>
+      <c r="AG139" t="n">
+        <v>0.31575</v>
+      </c>
+      <c r="AH139" t="n">
+        <v>0.31239</v>
+      </c>
+      <c r="AI139" t="n">
+        <v>0.33686</v>
+      </c>
+      <c r="AJ139" t="n">
+        <v>0.5277000000000001</v>
+      </c>
+      <c r="AK139" t="n">
+        <v>0.31569</v>
+      </c>
+      <c r="AL139" t="n">
+        <v>0.4066</v>
+      </c>
+      <c r="AM139" t="n">
+        <v>0.35788</v>
+      </c>
+      <c r="AN139" t="n">
+        <v>0.32047</v>
+      </c>
+      <c r="AO139" t="n">
+        <v>0.30869</v>
+      </c>
+      <c r="AP139" t="n">
+        <v>0.31777</v>
+      </c>
+      <c r="AQ139" t="n">
+        <v>0.33694</v>
+      </c>
+      <c r="AR139" t="n">
+        <v>0.33164</v>
+      </c>
+      <c r="AS139" t="n">
+        <v>0.33984</v>
+      </c>
+      <c r="AT139" t="n">
+        <v>0.35315</v>
+      </c>
+      <c r="AU139" t="n">
+        <v>0.33449</v>
+      </c>
+      <c r="AV139" t="n">
+        <v>0.36312</v>
+      </c>
+      <c r="AW139" t="n">
+        <v>0.33292</v>
+      </c>
+      <c r="AX139" t="n">
+        <v>0.29611</v>
+      </c>
+      <c r="AY139" t="n">
+        <v>0.33126</v>
+      </c>
+      <c r="AZ139" t="n">
+        <v>0.3288</v>
+      </c>
+      <c r="BA139" t="n">
+        <v>0.33393</v>
+      </c>
+      <c r="BB139" t="n">
+        <v>0.31976</v>
+      </c>
+      <c r="BC139" t="n">
+        <v>0.33324</v>
+      </c>
+      <c r="BD139" t="n">
+        <v>0.33235</v>
+      </c>
+      <c r="BE139" t="n">
+        <v>0.35901</v>
+      </c>
+      <c r="BF139" t="n">
+        <v>0.32509</v>
+      </c>
+      <c r="BG139" t="n">
+        <v>0.32261</v>
+      </c>
+      <c r="BH139" t="n">
+        <v>0.32536</v>
+      </c>
+      <c r="BI139" t="n">
+        <v>0.33102</v>
+      </c>
+      <c r="BJ139" t="n">
+        <v>0.32822</v>
+      </c>
+      <c r="BK139" t="n">
+        <v>0.33268</v>
+      </c>
+      <c r="BL139" t="n">
+        <v>0.32197</v>
+      </c>
+      <c r="BM139" t="n">
+        <v>0.32817</v>
+      </c>
+      <c r="BN139" t="n">
+        <v>0.33216</v>
+      </c>
+      <c r="BO139" t="n">
+        <v>0.44164</v>
+      </c>
+      <c r="BP139" t="n">
+        <v>0.40904</v>
+      </c>
+      <c r="BQ139" t="n">
+        <v>0.44381</v>
+      </c>
+      <c r="BR139" t="n">
+        <v>0.22087</v>
+      </c>
+      <c r="BS139" t="n">
+        <v>0.70923</v>
+      </c>
+      <c r="BT139" t="n">
+        <v>0.72424</v>
+      </c>
+      <c r="BU139" t="n">
+        <v>0.40232</v>
+      </c>
+      <c r="BV139" t="n">
+        <v>0.42815</v>
+      </c>
+      <c r="BW139" t="n">
+        <v>0.49954</v>
+      </c>
+      <c r="BX139" t="n">
+        <v>0.6201599999999999</v>
+      </c>
+      <c r="BY139" t="n">
+        <v>0.74572</v>
+      </c>
+      <c r="BZ139" t="n">
+        <v>0.40516</v>
+      </c>
+      <c r="CA139" t="n">
+        <v>0.63312</v>
+      </c>
+      <c r="CB139" t="n">
+        <v>0.38392</v>
+      </c>
+      <c r="CC139" t="n">
+        <v>0.34645</v>
+      </c>
+      <c r="CD139" t="n">
+        <v>0.34084</v>
+      </c>
+      <c r="CE139" t="n">
+        <v>0.42539</v>
+      </c>
+      <c r="CF139" t="n">
+        <v>0.34516</v>
+      </c>
+      <c r="CG139" t="n">
+        <v>0.33614</v>
+      </c>
+      <c r="CH139" t="n">
+        <v>0.32308</v>
+      </c>
+      <c r="CI139" t="n">
+        <v>0.35521</v>
+      </c>
+      <c r="CJ139" t="n">
+        <v>0.33278</v>
+      </c>
+      <c r="CK139" t="n">
+        <v>0.33599</v>
+      </c>
+      <c r="CL139" t="n">
+        <v>0.32884</v>
+      </c>
+      <c r="CM139" t="n">
+        <v>0.32661</v>
+      </c>
+      <c r="CN139" t="n">
+        <v>0.33209</v>
+      </c>
+      <c r="CO139" t="n">
+        <v>0.32751</v>
+      </c>
+      <c r="CP139" t="n">
+        <v>0.20075</v>
+      </c>
+      <c r="CQ139" t="n">
+        <v>0.31933</v>
+      </c>
+      <c r="CR139" t="n">
+        <v>0.30756</v>
+      </c>
+      <c r="CS139" t="n">
+        <v>0.31645</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="n">
+        <v>46163</v>
+      </c>
+      <c r="B140" t="n">
+        <v>0.31818</v>
+      </c>
+      <c r="C140" t="n">
+        <v>0.37998</v>
+      </c>
+      <c r="D140" t="n">
+        <v>0.33385</v>
+      </c>
+      <c r="E140" t="n">
+        <v>0.32505</v>
+      </c>
+      <c r="F140" t="n">
+        <v>0.32151</v>
+      </c>
+      <c r="G140" t="n">
+        <v>0.32145</v>
+      </c>
+      <c r="H140" t="n">
+        <v>0.3158</v>
+      </c>
+      <c r="I140" t="n">
+        <v>0.3143</v>
+      </c>
+      <c r="J140" t="n">
+        <v>0.34566</v>
+      </c>
+      <c r="K140" t="n">
+        <v>0.32106</v>
+      </c>
+      <c r="L140" t="n">
+        <v>0.31959</v>
+      </c>
+      <c r="M140" t="n">
+        <v>0.31269</v>
+      </c>
+      <c r="N140" t="n">
+        <v>0.31771</v>
+      </c>
+      <c r="O140" t="n">
+        <v>0.31761</v>
+      </c>
+      <c r="P140" t="n">
+        <v>0.31457</v>
+      </c>
+      <c r="Q140" t="n">
+        <v>0.31589</v>
+      </c>
+      <c r="R140" t="n">
+        <v>0.31549</v>
+      </c>
+      <c r="S140" t="n">
+        <v>0.30513</v>
+      </c>
+      <c r="T140" t="n">
+        <v>0.30123</v>
+      </c>
+      <c r="U140" t="n">
+        <v>0.30419</v>
+      </c>
+      <c r="V140" t="n">
+        <v>0.29956</v>
+      </c>
+      <c r="W140" t="n">
+        <v>0.29752</v>
+      </c>
+      <c r="X140" t="n">
+        <v>0.29347</v>
+      </c>
+      <c r="Y140" t="n">
+        <v>0.32088</v>
+      </c>
+      <c r="Z140" t="n">
+        <v>0.29317</v>
+      </c>
+      <c r="AA140" t="n">
+        <v>0.30409</v>
+      </c>
+      <c r="AB140" t="n">
+        <v>0.30778</v>
+      </c>
+      <c r="AC140" t="n">
+        <v>0.30291</v>
+      </c>
+      <c r="AD140" t="n">
+        <v>0.33674</v>
+      </c>
+      <c r="AE140" t="n">
+        <v>0.31535</v>
+      </c>
+      <c r="AF140" t="n">
+        <v>0.33129</v>
+      </c>
+      <c r="AG140" t="n">
+        <v>0.32937</v>
+      </c>
+      <c r="AH140" t="n">
+        <v>0.31851</v>
+      </c>
+      <c r="AI140" t="n">
+        <v>0.36087</v>
+      </c>
+      <c r="AJ140" t="n">
+        <v>0.39096</v>
+      </c>
+      <c r="AK140" t="n">
+        <v>0.34499</v>
+      </c>
+      <c r="AL140" t="n">
+        <v>0.35366</v>
+      </c>
+      <c r="AM140" t="n">
+        <v>0.43459</v>
+      </c>
+      <c r="AN140" t="n">
+        <v>0.37965</v>
+      </c>
+      <c r="AO140" t="n">
+        <v>0.3425299999999999</v>
+      </c>
+      <c r="AP140" t="n">
+        <v>0.35484</v>
+      </c>
+      <c r="AQ140" t="n">
+        <v>0.33543</v>
+      </c>
+      <c r="AR140" t="n">
+        <v>0.31048</v>
+      </c>
+      <c r="AS140" t="n">
+        <v>0.3636</v>
+      </c>
+      <c r="AT140" t="n">
+        <v>0.36075</v>
+      </c>
+      <c r="AU140" t="n">
+        <v>0.34019</v>
+      </c>
+      <c r="AV140" t="n">
+        <v>0.35032</v>
+      </c>
+      <c r="AW140" t="n">
+        <v>0.3338</v>
+      </c>
+      <c r="AX140" t="n">
+        <v>0.29262</v>
+      </c>
+      <c r="AY140" t="n">
+        <v>0.3514</v>
+      </c>
+      <c r="AZ140" t="n">
+        <v>0.34095</v>
+      </c>
+      <c r="BA140" t="n">
+        <v>0.34267</v>
+      </c>
+      <c r="BB140" t="n">
+        <v>0.34168</v>
+      </c>
+      <c r="BC140" t="n">
+        <v>0.31629</v>
+      </c>
+      <c r="BD140" t="n">
+        <v>0.33671</v>
+      </c>
+      <c r="BE140" t="n">
+        <v>0.34106</v>
+      </c>
+      <c r="BF140" t="n">
+        <v>0.32533</v>
+      </c>
+      <c r="BG140" t="n">
+        <v>0.33344</v>
+      </c>
+      <c r="BH140" t="n">
+        <v>0.34152</v>
+      </c>
+      <c r="BI140" t="n">
+        <v>0.33802</v>
+      </c>
+      <c r="BJ140" t="n">
+        <v>0.32483</v>
+      </c>
+      <c r="BK140" t="n">
+        <v>0.34417</v>
+      </c>
+      <c r="BL140" t="n">
+        <v>0.3386</v>
+      </c>
+      <c r="BM140" t="n">
+        <v>0.33772</v>
+      </c>
+      <c r="BN140" t="n">
+        <v>0.34282</v>
+      </c>
+      <c r="BO140" t="n">
+        <v>0.34895</v>
+      </c>
+      <c r="BP140" t="n">
+        <v>0.37015</v>
+      </c>
+      <c r="BQ140" t="n">
+        <v>0.34897</v>
+      </c>
+      <c r="BR140" t="n">
+        <v>0.36251</v>
+      </c>
+      <c r="BS140" t="n">
+        <v>0.35174</v>
+      </c>
+      <c r="BT140" t="n">
+        <v>0.34764</v>
+      </c>
+      <c r="BU140" t="n">
+        <v>0.38352</v>
+      </c>
+      <c r="BV140" t="n">
+        <v>0.36984</v>
+      </c>
+      <c r="BW140" t="n">
+        <v>0.5479299999999999</v>
+      </c>
+      <c r="BX140" t="n">
+        <v>0.57253</v>
+      </c>
+      <c r="BY140" t="n">
+        <v>1.28916</v>
+      </c>
+      <c r="BZ140" t="n">
+        <v>0.82104</v>
+      </c>
+      <c r="CA140" t="n">
+        <v>0.60085</v>
+      </c>
+      <c r="CB140" t="n">
+        <v>0.8279</v>
+      </c>
+      <c r="CC140" t="n">
+        <v>0.51279</v>
+      </c>
+      <c r="CD140" t="n">
+        <v>0.64558</v>
+      </c>
+      <c r="CE140" t="n">
+        <v>0.5678799999999999</v>
+      </c>
+      <c r="CF140" t="n">
+        <v>0.44828</v>
+      </c>
+      <c r="CG140" t="n">
+        <v>0.7951699999999999</v>
+      </c>
+      <c r="CH140" t="n">
+        <v>0.7283099999999999</v>
+      </c>
+      <c r="CI140" t="n">
+        <v>1.20827</v>
+      </c>
+      <c r="CJ140" t="n">
+        <v>0.7099800000000001</v>
+      </c>
+      <c r="CK140" t="n">
+        <v>0.62493</v>
+      </c>
+      <c r="CL140" t="n">
+        <v>0.53388</v>
+      </c>
+      <c r="CM140" t="n">
+        <v>0.3339</v>
+      </c>
+      <c r="CN140" t="n">
+        <v>0.38946</v>
+      </c>
+      <c r="CO140" t="n">
+        <v>0.33614</v>
+      </c>
+      <c r="CP140" t="n">
+        <v>0.32494</v>
+      </c>
+      <c r="CQ140" t="n">
+        <v>0.32832</v>
+      </c>
+      <c r="CR140" t="n">
+        <v>0.31954</v>
+      </c>
+      <c r="CS140" t="n">
+        <v>0.32105</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="n">
+        <v>46164</v>
+      </c>
+      <c r="B141" t="n">
+        <v>0.28384</v>
+      </c>
+      <c r="C141" t="n">
+        <v>0.33021</v>
+      </c>
+      <c r="D141" t="n">
+        <v>0.3378</v>
+      </c>
+      <c r="E141" t="n">
+        <v>0.30971</v>
+      </c>
+      <c r="F141" t="n">
+        <v>0.33035</v>
+      </c>
+      <c r="G141" t="n">
+        <v>0.3206</v>
+      </c>
+      <c r="H141" t="n">
+        <v>0.28375</v>
+      </c>
+      <c r="I141" t="n">
+        <v>0.29543</v>
+      </c>
+      <c r="J141" t="n">
+        <v>0.28917</v>
+      </c>
+      <c r="K141" t="n">
+        <v>0.29909</v>
+      </c>
+      <c r="L141" t="n">
+        <v>0.32375</v>
+      </c>
+      <c r="M141" t="n">
+        <v>0.29005</v>
+      </c>
+      <c r="N141" t="n">
+        <v>0.30519</v>
+      </c>
+      <c r="O141" t="n">
+        <v>0.32362</v>
+      </c>
+      <c r="P141" t="n">
+        <v>0.3129</v>
+      </c>
+      <c r="Q141" t="n">
+        <v>0.30105</v>
+      </c>
+      <c r="R141" t="n">
+        <v>0.3017</v>
+      </c>
+      <c r="S141" t="n">
+        <v>-0.03938000000000001</v>
+      </c>
+      <c r="T141" t="n">
+        <v>0.28797</v>
+      </c>
+      <c r="U141" t="n">
+        <v>0.28885</v>
+      </c>
+      <c r="V141" t="n">
+        <v>0.31917</v>
+      </c>
+      <c r="W141" t="n">
+        <v>0.28331</v>
+      </c>
+      <c r="X141" t="n">
+        <v>0.3142</v>
+      </c>
+      <c r="Y141" t="n">
+        <v>0.32749</v>
+      </c>
+      <c r="Z141" t="n">
+        <v>0.29037</v>
+      </c>
+      <c r="AA141" t="n">
+        <v>0.2814700000000001</v>
+      </c>
+      <c r="AB141" t="n">
+        <v>0.35614</v>
+      </c>
+      <c r="AC141" t="n">
+        <v>0.3568</v>
+      </c>
+      <c r="AD141" t="n">
+        <v>0.3345</v>
+      </c>
+      <c r="AE141" t="n">
+        <v>0.30462</v>
+      </c>
+      <c r="AF141" t="n">
+        <v>0.30301</v>
+      </c>
+      <c r="AG141" t="n">
+        <v>0.31324</v>
+      </c>
+      <c r="AH141" t="n">
+        <v>0.30774</v>
+      </c>
+      <c r="AI141" t="n">
+        <v>0.32116</v>
+      </c>
+      <c r="AJ141" t="n">
+        <v>0.32275</v>
+      </c>
+      <c r="AK141" t="n">
+        <v>0.32656</v>
+      </c>
+      <c r="AL141" t="n">
+        <v>0.32655</v>
+      </c>
+      <c r="AM141" t="n">
+        <v>0.33025</v>
+      </c>
+      <c r="AN141" t="n">
+        <v>0.3577</v>
+      </c>
+      <c r="AO141" t="n">
+        <v>0.3802</v>
+      </c>
+      <c r="AP141" t="n">
+        <v>0.37656</v>
+      </c>
+      <c r="AQ141" t="n">
+        <v>0.33926</v>
+      </c>
+      <c r="AR141" t="n">
+        <v>0.2681</v>
+      </c>
+      <c r="AS141" t="n">
+        <v>0.42888</v>
+      </c>
+      <c r="AT141" t="n">
+        <v>0.45433</v>
+      </c>
+      <c r="AU141" t="n">
+        <v>0.55564</v>
+      </c>
+      <c r="AV141" t="n">
+        <v>0.34654</v>
+      </c>
+      <c r="AW141" t="n">
+        <v>0.34031</v>
+      </c>
+      <c r="AX141" t="n">
+        <v>0.19921</v>
+      </c>
+      <c r="AY141" t="n">
+        <v>0.46274</v>
+      </c>
+      <c r="AZ141" t="n">
+        <v>0.32832</v>
+      </c>
+      <c r="BA141" t="n">
+        <v>0.2981</v>
+      </c>
+      <c r="BB141" t="n">
+        <v>0.31558</v>
+      </c>
+      <c r="BC141" t="n">
+        <v>0.43493</v>
+      </c>
+      <c r="BD141" t="n">
+        <v>0.5255299999999999</v>
+      </c>
+      <c r="BE141" t="n">
+        <v>0.33752</v>
+      </c>
+      <c r="BF141" t="n">
+        <v>0.34435</v>
+      </c>
+      <c r="BG141" t="n">
+        <v>0.31137</v>
+      </c>
+      <c r="BH141" t="n">
+        <v>0.42719</v>
+      </c>
+      <c r="BI141" t="n">
+        <v>0.48921</v>
+      </c>
+      <c r="BJ141" t="n">
+        <v>0.32362</v>
+      </c>
+      <c r="BK141" t="n">
+        <v>0.41141</v>
+      </c>
+      <c r="BL141" t="n">
+        <v>0.36116</v>
+      </c>
+      <c r="BM141" t="n">
+        <v>0.35182</v>
+      </c>
+      <c r="BN141" t="n">
+        <v>0.37291</v>
+      </c>
+      <c r="BO141" t="n">
+        <v>0.34864</v>
+      </c>
+      <c r="BP141" t="n">
+        <v>0.34393</v>
+      </c>
+      <c r="BQ141" t="n">
+        <v>0.35493</v>
+      </c>
+      <c r="BR141" t="n">
+        <v>0.36104</v>
+      </c>
+      <c r="BS141" t="n">
+        <v>0.6759299999999999</v>
+      </c>
+      <c r="BT141" t="n">
+        <v>0.82759</v>
+      </c>
+      <c r="BU141" t="n">
+        <v>0.33614</v>
+      </c>
+      <c r="BV141" t="n">
+        <v>0.345</v>
+      </c>
+      <c r="BW141" t="n">
+        <v>0.35641</v>
+      </c>
+      <c r="BX141" t="n">
+        <v>0.42415</v>
+      </c>
+      <c r="BY141" t="n">
+        <v>1.08273</v>
+      </c>
+      <c r="BZ141" t="n">
+        <v>0.37733</v>
+      </c>
+      <c r="CA141" t="n">
+        <v>1.21948</v>
+      </c>
+      <c r="CB141" t="n">
+        <v>1.02362</v>
+      </c>
+      <c r="CC141" t="n">
+        <v>0.81113</v>
+      </c>
+      <c r="CD141" t="n">
+        <v>0.48374</v>
+      </c>
+      <c r="CE141" t="n">
+        <v>0.42148</v>
+      </c>
+      <c r="CF141" t="n">
+        <v>0.49575</v>
+      </c>
+      <c r="CG141" t="n">
+        <v>0.62659</v>
+      </c>
+      <c r="CH141" t="n">
+        <v>0.41192</v>
+      </c>
+      <c r="CI141" t="n">
+        <v>0.5104</v>
+      </c>
+      <c r="CJ141" t="n">
+        <v>0.42803</v>
+      </c>
+      <c r="CK141" t="n">
+        <v>0.44462</v>
+      </c>
+      <c r="CL141" t="n">
+        <v>0.36023</v>
+      </c>
+      <c r="CM141" t="n">
+        <v>0.35619</v>
+      </c>
+      <c r="CN141" t="n">
+        <v>0.34619</v>
+      </c>
+      <c r="CO141" t="n">
+        <v>0.33932</v>
+      </c>
+      <c r="CP141" t="n">
+        <v>0.33929</v>
+      </c>
+      <c r="CQ141" t="n">
+        <v>0.32561</v>
+      </c>
+      <c r="CR141" t="n">
+        <v>0.30865</v>
+      </c>
+      <c r="CS141" t="n">
+        <v>0.32505</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="n">
+        <v>46165</v>
+      </c>
+      <c r="B142" t="n">
+        <v>0.34291</v>
+      </c>
+      <c r="C142" t="n">
+        <v>0.6325299999999999</v>
+      </c>
+      <c r="D142" t="n">
+        <v>0.38898</v>
+      </c>
+      <c r="E142" t="n">
+        <v>0.42506</v>
+      </c>
+      <c r="F142" t="n">
+        <v>0.40788</v>
+      </c>
+      <c r="G142" t="n">
+        <v>0.40038</v>
+      </c>
+      <c r="H142" t="n">
+        <v>0.33664</v>
+      </c>
+      <c r="I142" t="n">
+        <v>0.35668</v>
+      </c>
+      <c r="J142" t="n">
+        <v>0.33867</v>
+      </c>
+      <c r="K142" t="n">
+        <v>0.33309</v>
+      </c>
+      <c r="L142" t="n">
+        <v>0.3353</v>
+      </c>
+      <c r="M142" t="n">
+        <v>0.33629</v>
+      </c>
+      <c r="N142" t="n">
+        <v>0.34072</v>
+      </c>
+      <c r="O142" t="n">
+        <v>0.33548</v>
+      </c>
+      <c r="P142" t="n">
+        <v>0.33328</v>
+      </c>
+      <c r="Q142" t="n">
+        <v>0.33307</v>
+      </c>
+      <c r="R142" t="n">
+        <v>0.33518</v>
+      </c>
+      <c r="S142" t="n">
+        <v>0.33482</v>
+      </c>
+      <c r="T142" t="n">
+        <v>0.33561</v>
+      </c>
+      <c r="U142" t="n">
+        <v>0.33073</v>
+      </c>
+      <c r="V142" t="n">
+        <v>0.32629</v>
+      </c>
+      <c r="W142" t="n">
+        <v>0.32928</v>
+      </c>
+      <c r="X142" t="n">
+        <v>0.32973</v>
+      </c>
+      <c r="Y142" t="n">
+        <v>0.33113</v>
+      </c>
+      <c r="Z142" t="n">
+        <v>0.32716</v>
+      </c>
+      <c r="AA142" t="n">
+        <v>0.32024</v>
+      </c>
+      <c r="AB142" t="n">
+        <v>0.32863</v>
+      </c>
+      <c r="AC142" t="n">
+        <v>0.32377</v>
+      </c>
+      <c r="AD142" t="n">
+        <v>0.33633</v>
+      </c>
+      <c r="AE142" t="n">
+        <v>0.33279</v>
+      </c>
+      <c r="AF142" t="n">
+        <v>0.32439</v>
+      </c>
+      <c r="AG142" t="n">
+        <v>0.32492</v>
+      </c>
+      <c r="AH142" t="n">
+        <v>0.32881</v>
+      </c>
+      <c r="AI142" t="n">
+        <v>0.33542</v>
+      </c>
+      <c r="AJ142" t="n">
+        <v>0.34034</v>
+      </c>
+      <c r="AK142" t="n">
+        <v>0.33905</v>
+      </c>
+      <c r="AL142" t="n">
+        <v>0.33473</v>
+      </c>
+      <c r="AM142" t="n">
+        <v>0.356</v>
+      </c>
+      <c r="AN142" t="n">
+        <v>0.35553</v>
+      </c>
+      <c r="AO142" t="n">
+        <v>0.33811</v>
+      </c>
+      <c r="AP142" t="n">
+        <v>0.35402</v>
+      </c>
+      <c r="AQ142" t="n">
+        <v>0.32904</v>
+      </c>
+      <c r="AR142" t="n">
+        <v>0.3467</v>
+      </c>
+      <c r="AS142" t="n">
+        <v>0.33284</v>
+      </c>
+      <c r="AT142" t="n">
+        <v>0.33338</v>
+      </c>
+      <c r="AU142" t="n">
+        <v>0.33223</v>
+      </c>
+      <c r="AV142" t="n">
+        <v>0.31565</v>
+      </c>
+      <c r="AW142" t="n">
+        <v>0.32187</v>
+      </c>
+      <c r="AX142" t="n">
+        <v>0.30948</v>
+      </c>
+      <c r="AY142" t="n">
+        <v>0.38442</v>
+      </c>
+      <c r="AZ142" t="n">
+        <v>0.3192</v>
+      </c>
+      <c r="BA142" t="n">
+        <v>0.30375</v>
+      </c>
+      <c r="BB142" t="n">
+        <v>0.27888</v>
+      </c>
+      <c r="BC142" t="n">
+        <v>0.32299</v>
+      </c>
+      <c r="BD142" t="n">
+        <v>0.38328</v>
+      </c>
+      <c r="BE142" t="n">
+        <v>0.439</v>
+      </c>
+      <c r="BF142" t="n">
+        <v>0.30451</v>
+      </c>
+      <c r="BG142" t="n">
+        <v>0.32419</v>
+      </c>
+      <c r="BH142" t="n">
+        <v>0.32603</v>
+      </c>
+      <c r="BI142" t="n">
+        <v>0.35116</v>
+      </c>
+      <c r="BJ142" t="n">
+        <v>0.32328</v>
+      </c>
+      <c r="BK142" t="n">
+        <v>0.35386</v>
+      </c>
+      <c r="BL142" t="n">
+        <v>0.35472</v>
+      </c>
+      <c r="BM142" t="n">
+        <v>0.32375</v>
+      </c>
+      <c r="BN142" t="n">
+        <v>0.34948</v>
+      </c>
+      <c r="BO142" t="n">
+        <v>0.42795</v>
+      </c>
+      <c r="BP142" t="n">
+        <v>0.48621</v>
+      </c>
+      <c r="BQ142" t="n">
+        <v>1.72007</v>
+      </c>
+      <c r="BR142" t="n">
+        <v>1.79159</v>
+      </c>
+      <c r="BS142" t="n">
+        <v>0.82927</v>
+      </c>
+      <c r="BT142" t="n">
+        <v>1.2479</v>
+      </c>
+      <c r="BU142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BV142" t="n">
+        <v>0.6023200000000001</v>
+      </c>
+      <c r="BW142" t="n">
+        <v>0.42457</v>
+      </c>
+      <c r="BX142" t="n">
+        <v>0.52608</v>
+      </c>
+      <c r="BY142" t="n">
+        <v>0.45629</v>
+      </c>
+      <c r="BZ142" t="n">
+        <v>0.35098</v>
+      </c>
+      <c r="CA142" t="n">
+        <v>0.47463</v>
+      </c>
+      <c r="CB142" t="n">
+        <v>0.9994700000000001</v>
+      </c>
+      <c r="CC142" t="n">
+        <v>1.19394</v>
+      </c>
+      <c r="CD142" t="n">
+        <v>0.47152</v>
+      </c>
+      <c r="CE142" t="n">
+        <v>0.49395</v>
+      </c>
+      <c r="CF142" t="n">
+        <v>0.46842</v>
+      </c>
+      <c r="CG142" t="n">
+        <v>0.44493</v>
+      </c>
+      <c r="CH142" t="n">
+        <v>0.46824</v>
+      </c>
+      <c r="CI142" t="n">
+        <v>0.56413</v>
+      </c>
+      <c r="CJ142" t="n">
+        <v>0.44941</v>
+      </c>
+      <c r="CK142" t="n">
+        <v>0.37934</v>
+      </c>
+      <c r="CL142" t="n">
+        <v>0.42357</v>
+      </c>
+      <c r="CM142" t="n">
+        <v>0.43147</v>
+      </c>
+      <c r="CN142" t="n">
+        <v>0.38879</v>
+      </c>
+      <c r="CO142" t="n">
+        <v>0.34205</v>
+      </c>
+      <c r="CP142" t="n">
+        <v>0.33599</v>
+      </c>
+      <c r="CQ142" t="n">
+        <v>0.33741</v>
+      </c>
+      <c r="CR142" t="n">
+        <v>0.3385</v>
+      </c>
+      <c r="CS142" t="n">
+        <v>0.33816</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="n">
+        <v>46166</v>
+      </c>
+      <c r="B143" t="n">
+        <v>0.34843</v>
+      </c>
+      <c r="C143" t="n">
+        <v>0.35385</v>
+      </c>
+      <c r="D143" t="n">
+        <v>0.36741</v>
+      </c>
+      <c r="E143" t="n">
+        <v>0.3074</v>
+      </c>
+      <c r="F143" t="n">
+        <v>0.37212</v>
+      </c>
+      <c r="G143" t="n">
+        <v>0.35849</v>
+      </c>
+      <c r="H143" t="n">
+        <v>0.35613</v>
+      </c>
+      <c r="I143" t="n">
+        <v>0.3420299999999999</v>
+      </c>
+      <c r="J143" t="n">
+        <v>0.34261</v>
+      </c>
+      <c r="K143" t="n">
+        <v>0.33913</v>
+      </c>
+      <c r="L143" t="n">
+        <v>0.3427</v>
+      </c>
+      <c r="M143" t="n">
+        <v>0.33584</v>
+      </c>
+      <c r="N143" t="n">
+        <v>0.33994</v>
+      </c>
+      <c r="O143" t="n">
+        <v>0.34723</v>
+      </c>
+      <c r="P143" t="n">
+        <v>0.31796</v>
+      </c>
+      <c r="Q143" t="n">
+        <v>0.35553</v>
+      </c>
+      <c r="R143" t="n">
+        <v>0.3454100000000001</v>
+      </c>
+      <c r="S143" t="n">
+        <v>0.33702</v>
+      </c>
+      <c r="T143" t="n">
+        <v>0.32804</v>
+      </c>
+      <c r="U143" t="n">
+        <v>0.33118</v>
+      </c>
+      <c r="V143" t="n">
+        <v>0.32917</v>
+      </c>
+      <c r="W143" t="n">
+        <v>0.32968</v>
+      </c>
+      <c r="X143" t="n">
+        <v>0.33563</v>
+      </c>
+      <c r="Y143" t="n">
+        <v>0.33297</v>
+      </c>
+      <c r="Z143" t="n">
+        <v>0.3352</v>
+      </c>
+      <c r="AA143" t="n">
+        <v>0.32462</v>
+      </c>
+      <c r="AB143" t="n">
+        <v>0.33037</v>
+      </c>
+      <c r="AC143" t="n">
+        <v>0.33246</v>
+      </c>
+      <c r="AD143" t="n">
+        <v>0.33041</v>
+      </c>
+      <c r="AE143" t="n">
+        <v>0.32908</v>
+      </c>
+      <c r="AF143" t="n">
+        <v>0.30536</v>
+      </c>
+      <c r="AG143" t="n">
+        <v>0.31858</v>
+      </c>
+      <c r="AH143" t="n">
+        <v>0.30917</v>
+      </c>
+      <c r="AI143" t="n">
+        <v>0.1761</v>
+      </c>
+      <c r="AJ143" t="n">
+        <v>0.30455</v>
+      </c>
+      <c r="AK143" t="n">
+        <v>0.29575</v>
+      </c>
+      <c r="AL143" t="n">
+        <v>0.31175</v>
+      </c>
+      <c r="AM143" t="n">
+        <v>0.14576</v>
+      </c>
+      <c r="AN143" t="n">
+        <v>0.19866</v>
+      </c>
+      <c r="AO143" t="n">
+        <v>0.14644</v>
+      </c>
+      <c r="AP143" t="n">
+        <v>0.28745</v>
+      </c>
+      <c r="AQ143" t="n">
+        <v>0.0478</v>
+      </c>
+      <c r="AR143" t="n">
+        <v>0.1217</v>
+      </c>
+      <c r="AS143" t="n">
+        <v>0.33374</v>
+      </c>
+      <c r="AT143" t="n">
+        <v>0.22618</v>
+      </c>
+      <c r="AU143" t="n">
+        <v>0.26018</v>
+      </c>
+      <c r="AV143" t="n">
+        <v>0.14364</v>
+      </c>
+      <c r="AW143" t="n">
+        <v>0.14544</v>
+      </c>
+      <c r="AX143" t="n">
+        <v>0.2836</v>
+      </c>
+      <c r="AY143" t="n">
+        <v>0.18784</v>
+      </c>
+      <c r="AZ143" t="n">
+        <v>0.3092200000000001</v>
+      </c>
+      <c r="BA143" t="n">
+        <v>0.22685</v>
+      </c>
+      <c r="BB143" t="n">
+        <v>0.312</v>
+      </c>
+      <c r="BC143" t="n">
+        <v>0.18514</v>
+      </c>
+      <c r="BD143" t="n">
+        <v>0.36762</v>
+      </c>
+      <c r="BE143" t="n">
+        <v>0.30881</v>
+      </c>
+      <c r="BF143" t="n">
+        <v>0.1971</v>
+      </c>
+      <c r="BG143" t="n">
+        <v>0.33011</v>
+      </c>
+      <c r="BH143" t="n">
+        <v>0.3279</v>
+      </c>
+      <c r="BI143" t="n">
+        <v>0.22516</v>
+      </c>
+      <c r="BJ143" t="n">
+        <v>0.29427</v>
+      </c>
+      <c r="BK143" t="n">
+        <v>0.5215700000000001</v>
+      </c>
+      <c r="BL143" t="n">
+        <v>0.79152</v>
+      </c>
+      <c r="BM143" t="n">
+        <v>0.6756599999999999</v>
+      </c>
+      <c r="BN143" t="n">
+        <v>0.5092099999999999</v>
+      </c>
+      <c r="BO143" t="n">
+        <v>0.7024900000000001</v>
+      </c>
+      <c r="BP143" t="n">
+        <v>1.76439</v>
+      </c>
+      <c r="BQ143" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BR143" t="n">
+        <v>1.1003</v>
+      </c>
+      <c r="BS143" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BT143" t="n">
+        <v>1.26488</v>
+      </c>
+      <c r="BU143" t="n">
+        <v>1.51315</v>
+      </c>
+      <c r="BV143" t="n">
+        <v>0.73351</v>
+      </c>
+      <c r="BW143" t="n">
+        <v>0.62001</v>
+      </c>
+      <c r="BX143" t="n">
+        <v>0.67506</v>
+      </c>
+      <c r="BY143" t="n">
+        <v>0.48608</v>
+      </c>
+      <c r="BZ143" t="n">
+        <v>0.41314</v>
+      </c>
+      <c r="CA143" t="n">
+        <v>1.54134</v>
+      </c>
+      <c r="CB143" t="n">
+        <v>1.43177</v>
+      </c>
+      <c r="CC143" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CD143" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CE143" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CF143" t="n">
+        <v>0.64159</v>
+      </c>
+      <c r="CG143" t="n">
+        <v>1.74665</v>
+      </c>
+      <c r="CH143" t="n">
+        <v>0.66579</v>
+      </c>
+      <c r="CI143" t="n">
+        <v>1.62408</v>
+      </c>
+      <c r="CJ143" t="n">
+        <v>1.71968</v>
+      </c>
+      <c r="CK143" t="n">
+        <v>1.10081</v>
+      </c>
+      <c r="CL143" t="n">
+        <v>0.6209199999999999</v>
+      </c>
+      <c r="CM143" t="n">
+        <v>0.61193</v>
+      </c>
+      <c r="CN143" t="n">
+        <v>0.50325</v>
+      </c>
+      <c r="CO143" t="n">
+        <v>0.56825</v>
+      </c>
+      <c r="CP143" t="n">
+        <v>0.39973</v>
+      </c>
+      <c r="CQ143" t="n">
+        <v>0.4115</v>
+      </c>
+      <c r="CR143" t="n">
+        <v>0.37932</v>
+      </c>
+      <c r="CS143" t="n">
+        <v>0.36805</v>
       </c>
     </row>
   </sheetData>
